--- a/2025-2026工程训练_0308.xlsx
+++ b/2025-2026工程训练_0308.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\工作\1实验教学部\排课\ClassSchedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF325BF8-FC65-48BC-BE03-16C056EBC0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABBEB78-9D5C-47DF-B13F-75B7AB61FDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="670" yWindow="4260" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="排课表" sheetId="49" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="402">
   <si>
     <t>教学班名称</t>
   </si>
@@ -1171,13 +1171,6 @@
 数x5-7</t>
   </si>
   <si>
-    <t>A产1-2
-B柔1-2
-B产3-4
-A柔3-4
-焊5-7</t>
-  </si>
-  <si>
     <t>A智1-2
 B机1-2
 B智3-4
@@ -1187,10 +1180,6 @@
   <si>
     <t>铣m1-4
 先t5-7</t>
-  </si>
-  <si>
-    <t>铣m1-4
-数c5-7</t>
   </si>
   <si>
     <t>讲1-3
@@ -1634,12 +1623,48 @@
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>数c5-7</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+数c1-4
+焊5-7</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>铣m1-4
+A产5-6'
+B柔5-6'
+B产6'-7
+A柔6'-7</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A产1-2
+B压1-2
+B产3-4
+A压3-4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A产1-2
+B压1-2
+B产3-4
+A压3-4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1695,8 +1720,26 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1718,6 +1761,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1748,7 +1797,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="6" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6"/>
@@ -1783,6 +1832,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2094,7 +2161,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:W159"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="2" customWidth="1"/>
     <col min="2" max="2" width="25" style="2" customWidth="1"/>
@@ -2104,7 +2171,7 @@
     <col min="24" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>128</v>
       </c>
@@ -2175,7 +2242,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -2222,7 +2289,7 @@
       <c r="V2" s="4"/>
       <c r="W2" s="6"/>
     </row>
-    <row r="3" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -2269,7 +2336,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="6"/>
     </row>
-    <row r="4" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>28</v>
       </c>
@@ -2328,7 +2395,7 @@
       <c r="V4" s="4"/>
       <c r="W4" s="6"/>
     </row>
-    <row r="5" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>61</v>
       </c>
@@ -2375,7 +2442,7 @@
       <c r="V5" s="4"/>
       <c r="W5" s="6"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -2422,7 +2489,7 @@
       <c r="V6" s="4"/>
       <c r="W6" s="6"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
@@ -2469,7 +2536,7 @@
       <c r="V7" s="4"/>
       <c r="W7" s="6"/>
     </row>
-    <row r="8" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
@@ -2499,8 +2566,8 @@
       <c r="O8" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="P8" s="4" t="s">
-        <v>151</v>
+      <c r="P8" s="17" t="s">
+        <v>400</v>
       </c>
       <c r="Q8" s="4" t="s">
         <v>155</v>
@@ -2516,7 +2583,7 @@
       <c r="V8" s="4"/>
       <c r="W8" s="6"/>
     </row>
-    <row r="9" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
@@ -2552,8 +2619,8 @@
       <c r="Q9" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="R9" s="4" t="s">
-        <v>151</v>
+      <c r="R9" s="19" t="s">
+        <v>401</v>
       </c>
       <c r="S9" s="4" t="s">
         <v>155</v>
@@ -2563,7 +2630,7 @@
       <c r="V9" s="4"/>
       <c r="W9" s="6"/>
     </row>
-    <row r="10" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
@@ -2628,7 +2695,7 @@
       </c>
       <c r="W10" s="6"/>
     </row>
-    <row r="11" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>41</v>
       </c>
@@ -2693,7 +2760,7 @@
       </c>
       <c r="W11" s="6"/>
     </row>
-    <row r="12" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>41</v>
       </c>
@@ -2758,7 +2825,7 @@
       </c>
       <c r="W12" s="6"/>
     </row>
-    <row r="13" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>41</v>
       </c>
@@ -2823,7 +2890,7 @@
       </c>
       <c r="W13" s="6"/>
     </row>
-    <row r="14" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>41</v>
       </c>
@@ -2872,7 +2939,7 @@
       <c r="V14" s="4"/>
       <c r="W14" s="6"/>
     </row>
-    <row r="15" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>41</v>
       </c>
@@ -2921,7 +2988,7 @@
       <c r="V15" s="4"/>
       <c r="W15" s="6"/>
     </row>
-    <row r="16" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>20</v>
       </c>
@@ -2972,7 +3039,7 @@
       <c r="V16" s="4"/>
       <c r="W16" s="6"/>
     </row>
-    <row r="17" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
@@ -3023,7 +3090,7 @@
       <c r="V17" s="4"/>
       <c r="W17" s="6"/>
     </row>
-    <row r="18" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>41</v>
       </c>
@@ -3082,7 +3149,7 @@
       <c r="V18" s="4"/>
       <c r="W18" s="6"/>
     </row>
-    <row r="19" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>41</v>
       </c>
@@ -3141,7 +3208,7 @@
       <c r="V19" s="4"/>
       <c r="W19" s="6"/>
     </row>
-    <row r="20" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>190</v>
       </c>
@@ -3180,11 +3247,11 @@
       <c r="V20" s="4"/>
       <c r="W20" s="6"/>
     </row>
-    <row r="21" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="14" t="s">
         <v>195</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -3219,11 +3286,11 @@
       <c r="V21" s="4"/>
       <c r="W21" s="6"/>
     </row>
-    <row r="22" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="14" t="s">
         <v>198</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -3258,9 +3325,9 @@
       <c r="V22" s="4"/>
       <c r="W22" s="6"/>
     </row>
-    <row r="23" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -3283,11 +3350,11 @@
       <c r="V23" s="7"/>
       <c r="W23" s="8"/>
     </row>
-    <row r="24" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="14" t="s">
         <v>195</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -3322,11 +3389,11 @@
       <c r="V24" s="4"/>
       <c r="W24" s="6"/>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="14" t="s">
         <v>198</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -3361,7 +3428,7 @@
       <c r="V25" s="4"/>
       <c r="W25" s="6"/>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>190</v>
       </c>
@@ -3400,7 +3467,7 @@
       <c r="V26" s="4"/>
       <c r="W26" s="6"/>
     </row>
-    <row r="27" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>190</v>
       </c>
@@ -3439,7 +3506,7 @@
       <c r="V27" s="4"/>
       <c r="W27" s="6"/>
     </row>
-    <row r="28" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>190</v>
       </c>
@@ -3478,7 +3545,7 @@
       <c r="V28" s="4"/>
       <c r="W28" s="6"/>
     </row>
-    <row r="29" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>190</v>
       </c>
@@ -3517,7 +3584,7 @@
       <c r="V29" s="4"/>
       <c r="W29" s="6"/>
     </row>
-    <row r="30" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>190</v>
       </c>
@@ -3556,7 +3623,7 @@
       <c r="V30" s="4"/>
       <c r="W30" s="6"/>
     </row>
-    <row r="31" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>190</v>
       </c>
@@ -3595,7 +3662,7 @@
       <c r="V31" s="4"/>
       <c r="W31" s="6"/>
     </row>
-    <row r="32" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>190</v>
       </c>
@@ -3634,7 +3701,7 @@
       <c r="V32" s="4"/>
       <c r="W32" s="6"/>
     </row>
-    <row r="33" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>190</v>
       </c>
@@ -3673,7 +3740,7 @@
       <c r="V33" s="4"/>
       <c r="W33" s="6"/>
     </row>
-    <row r="34" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>190</v>
       </c>
@@ -3712,7 +3779,7 @@
       <c r="V34" s="4"/>
       <c r="W34" s="6"/>
     </row>
-    <row r="35" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>190</v>
       </c>
@@ -3751,7 +3818,7 @@
       <c r="V35" s="4"/>
       <c r="W35" s="6"/>
     </row>
-    <row r="36" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>190</v>
       </c>
@@ -3790,7 +3857,7 @@
       <c r="V36" s="4"/>
       <c r="W36" s="6"/>
     </row>
-    <row r="37" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>190</v>
       </c>
@@ -3827,7 +3894,7 @@
       <c r="V37" s="4"/>
       <c r="W37" s="6"/>
     </row>
-    <row r="38" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>190</v>
       </c>
@@ -3864,7 +3931,7 @@
       <c r="V38" s="4"/>
       <c r="W38" s="6"/>
     </row>
-    <row r="39" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>190</v>
       </c>
@@ -3901,7 +3968,7 @@
       <c r="V39" s="4"/>
       <c r="W39" s="6"/>
     </row>
-    <row r="40" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>190</v>
       </c>
@@ -3938,7 +4005,7 @@
       <c r="V40" s="4"/>
       <c r="W40" s="6"/>
     </row>
-    <row r="41" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>190</v>
       </c>
@@ -3975,7 +4042,7 @@
       <c r="V41" s="4"/>
       <c r="W41" s="6"/>
     </row>
-    <row r="42" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>190</v>
       </c>
@@ -4012,7 +4079,7 @@
       </c>
       <c r="W42" s="6"/>
     </row>
-    <row r="43" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>190</v>
       </c>
@@ -4049,7 +4116,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>190</v>
       </c>
@@ -4086,7 +4153,7 @@
       </c>
       <c r="W44" s="6"/>
     </row>
-    <row r="45" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>190</v>
       </c>
@@ -4123,7 +4190,7 @@
       <c r="V45" s="4"/>
       <c r="W45" s="6"/>
     </row>
-    <row r="46" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>190</v>
       </c>
@@ -4160,7 +4227,7 @@
       <c r="V46" s="4"/>
       <c r="W46" s="6"/>
     </row>
-    <row r="47" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>190</v>
       </c>
@@ -4197,7 +4264,7 @@
       <c r="V47" s="4"/>
       <c r="W47" s="6"/>
     </row>
-    <row r="48" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>190</v>
       </c>
@@ -4234,7 +4301,7 @@
       <c r="V48" s="4"/>
       <c r="W48" s="6"/>
     </row>
-    <row r="49" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>190</v>
       </c>
@@ -4271,7 +4338,7 @@
       <c r="V49" s="4"/>
       <c r="W49" s="6"/>
     </row>
-    <row r="50" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>190</v>
       </c>
@@ -4308,7 +4375,7 @@
       <c r="V50" s="4"/>
       <c r="W50" s="6"/>
     </row>
-    <row r="51" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>190</v>
       </c>
@@ -4345,7 +4412,7 @@
       <c r="V51" s="4"/>
       <c r="W51" s="6"/>
     </row>
-    <row r="52" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>190</v>
       </c>
@@ -4382,7 +4449,7 @@
       <c r="V52" s="4"/>
       <c r="W52" s="6"/>
     </row>
-    <row r="53" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>190</v>
       </c>
@@ -4419,7 +4486,7 @@
       <c r="V53" s="4"/>
       <c r="W53" s="6"/>
     </row>
-    <row r="54" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>190</v>
       </c>
@@ -4456,7 +4523,7 @@
       <c r="V54" s="4"/>
       <c r="W54" s="6"/>
     </row>
-    <row r="55" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>190</v>
       </c>
@@ -4493,7 +4560,7 @@
       <c r="V55" s="4"/>
       <c r="W55" s="6"/>
     </row>
-    <row r="56" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>190</v>
       </c>
@@ -4530,7 +4597,7 @@
       <c r="V56" s="4"/>
       <c r="W56" s="6"/>
     </row>
-    <row r="57" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>190</v>
       </c>
@@ -4567,7 +4634,7 @@
       <c r="V57" s="4"/>
       <c r="W57" s="6"/>
     </row>
-    <row r="58" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>190</v>
       </c>
@@ -4586,7 +4653,6 @@
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
@@ -4604,7 +4670,7 @@
       <c r="V58" s="4"/>
       <c r="W58" s="6"/>
     </row>
-    <row r="59" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>190</v>
       </c>
@@ -4640,7 +4706,7 @@
       <c r="V59" s="4"/>
       <c r="W59" s="6"/>
     </row>
-    <row r="60" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>32</v>
       </c>
@@ -4699,7 +4765,7 @@
       <c r="V60" s="4"/>
       <c r="W60" s="6"/>
     </row>
-    <row r="61" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>32</v>
       </c>
@@ -4758,7 +4824,7 @@
       <c r="V61" s="4"/>
       <c r="W61" s="6"/>
     </row>
-    <row r="62" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>32</v>
       </c>
@@ -4825,7 +4891,7 @@
       </c>
       <c r="W62" s="6"/>
     </row>
-    <row r="63" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>32</v>
       </c>
@@ -4850,11 +4916,11 @@
       <c r="H63" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="I63" s="9" t="s">
+      <c r="I63" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="J63" s="18" t="s">
         <v>172</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>169</v>
@@ -4892,7 +4958,7 @@
       </c>
       <c r="W63" s="6"/>
     </row>
-    <row r="64" spans="1:23" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:23" ht="42" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>41</v>
       </c>
@@ -4915,7 +4981,7 @@
         <v>255</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>200</v>
@@ -4945,7 +5011,7 @@
       <c r="V64" s="4"/>
       <c r="W64" s="6"/>
     </row>
-    <row r="65" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>36</v>
       </c>
@@ -4990,7 +5056,7 @@
       <c r="V65" s="4"/>
       <c r="W65" s="6"/>
     </row>
-    <row r="66" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>36</v>
       </c>
@@ -5036,7 +5102,7 @@
       <c r="V66" s="4"/>
       <c r="W66" s="6"/>
     </row>
-    <row r="67" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>61</v>
       </c>
@@ -5087,7 +5153,7 @@
       <c r="V67" s="4"/>
       <c r="W67" s="6"/>
     </row>
-    <row r="68" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>36</v>
       </c>
@@ -5138,7 +5204,7 @@
       <c r="V68" s="4"/>
       <c r="W68" s="6"/>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>20</v>
       </c>
@@ -5180,7 +5246,7 @@
       <c r="V69" s="4"/>
       <c r="W69" s="6"/>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>20</v>
       </c>
@@ -5223,7 +5289,7 @@
       <c r="V70" s="4"/>
       <c r="W70" s="6"/>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>20</v>
       </c>
@@ -5266,7 +5332,7 @@
       <c r="V71" s="4"/>
       <c r="W71" s="6"/>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>20</v>
       </c>
@@ -5309,7 +5375,7 @@
       <c r="V72" s="4"/>
       <c r="W72" s="6"/>
     </row>
-    <row r="73" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>74</v>
       </c>
@@ -5353,7 +5419,7 @@
       <c r="V73" s="4"/>
       <c r="W73" s="6"/>
     </row>
-    <row r="74" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -5378,7 +5444,7 @@
       <c r="V74" s="7"/>
       <c r="W74" s="8"/>
     </row>
-    <row r="75" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>32</v>
       </c>
@@ -5437,7 +5503,7 @@
       <c r="V75" s="4"/>
       <c r="W75" s="6"/>
     </row>
-    <row r="76" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>32</v>
       </c>
@@ -5496,7 +5562,7 @@
       <c r="V76" s="4"/>
       <c r="W76" s="6"/>
     </row>
-    <row r="77" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>98</v>
       </c>
@@ -5555,7 +5621,7 @@
       </c>
       <c r="W77" s="6"/>
     </row>
-    <row r="78" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>98</v>
       </c>
@@ -5614,7 +5680,7 @@
       </c>
       <c r="W78" s="6"/>
     </row>
-    <row r="79" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>74</v>
       </c>
@@ -5665,7 +5731,7 @@
       <c r="V79" s="4"/>
       <c r="W79" s="6"/>
     </row>
-    <row r="80" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>74</v>
       </c>
@@ -5716,7 +5782,7 @@
       <c r="V80" s="4"/>
       <c r="W80" s="6"/>
     </row>
-    <row r="81" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>74</v>
       </c>
@@ -5767,7 +5833,7 @@
       <c r="V81" s="4"/>
       <c r="W81" s="6"/>
     </row>
-    <row r="82" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>74</v>
       </c>
@@ -5818,7 +5884,7 @@
       <c r="V82" s="4"/>
       <c r="W82" s="6"/>
     </row>
-    <row r="83" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>190</v>
       </c>
@@ -5859,7 +5925,7 @@
       <c r="V83" s="4"/>
       <c r="W83" s="6"/>
     </row>
-    <row r="84" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>190</v>
       </c>
@@ -5900,7 +5966,7 @@
       <c r="V84" s="4"/>
       <c r="W84" s="6"/>
     </row>
-    <row r="85" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>32</v>
       </c>
@@ -5959,7 +6025,7 @@
       <c r="V85" s="4"/>
       <c r="W85" s="6"/>
     </row>
-    <row r="86" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>32</v>
       </c>
@@ -6018,7 +6084,7 @@
       <c r="V86" s="4"/>
       <c r="W86" s="6"/>
     </row>
-    <row r="87" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>190</v>
       </c>
@@ -6059,7 +6125,7 @@
       <c r="V87" s="4"/>
       <c r="W87" s="6"/>
     </row>
-    <row r="88" spans="1:23" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>190</v>
       </c>
@@ -6100,7 +6166,7 @@
       <c r="V88" s="4"/>
       <c r="W88" s="6"/>
     </row>
-    <row r="89" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>190</v>
       </c>
@@ -6141,7 +6207,7 @@
       <c r="V89" s="4"/>
       <c r="W89" s="6"/>
     </row>
-    <row r="90" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>20</v>
       </c>
@@ -6192,7 +6258,7 @@
       <c r="V90" s="4"/>
       <c r="W90" s="6"/>
     </row>
-    <row r="91" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>20</v>
       </c>
@@ -6243,7 +6309,7 @@
       <c r="V91" s="4"/>
       <c r="W91" s="6"/>
     </row>
-    <row r="92" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>20</v>
       </c>
@@ -6286,7 +6352,7 @@
       <c r="V92" s="4"/>
       <c r="W92" s="6"/>
     </row>
-    <row r="93" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>20</v>
       </c>
@@ -6329,7 +6395,7 @@
       <c r="V93" s="4"/>
       <c r="W93" s="6"/>
     </row>
-    <row r="94" spans="1:23" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:23" ht="42" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>190</v>
       </c>
@@ -6368,11 +6434,11 @@
       <c r="V94" s="4"/>
       <c r="W94" s="6"/>
     </row>
-    <row r="95" spans="1:23" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:23" ht="42" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="14" t="s">
         <v>195</v>
       </c>
       <c r="C95" s="4" t="s">
@@ -6407,11 +6473,11 @@
       <c r="V95" s="4"/>
       <c r="W95" s="6"/>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="14" t="s">
         <v>198</v>
       </c>
       <c r="C96" s="4" t="s">
@@ -6446,9 +6512,9 @@
       <c r="V96" s="4"/>
       <c r="W96" s="6"/>
     </row>
-    <row r="97" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="7"/>
-      <c r="B97" s="7"/>
+      <c r="B97" s="15"/>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
@@ -6471,11 +6537,11 @@
       <c r="V97" s="7"/>
       <c r="W97" s="8"/>
     </row>
-    <row r="98" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="14" t="s">
         <v>195</v>
       </c>
       <c r="C98" s="4" t="s">
@@ -6510,11 +6576,11 @@
       <c r="V98" s="4"/>
       <c r="W98" s="6"/>
     </row>
-    <row r="99" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="14" t="s">
         <v>198</v>
       </c>
       <c r="C99" s="4" t="s">
@@ -6549,7 +6615,7 @@
       <c r="V99" s="4"/>
       <c r="W99" s="6"/>
     </row>
-    <row r="100" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>190</v>
       </c>
@@ -6588,7 +6654,7 @@
       <c r="V100" s="4"/>
       <c r="W100" s="6"/>
     </row>
-    <row r="101" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>9</v>
       </c>
@@ -6626,8 +6692,7 @@
       <c r="O101" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="P101" s="4"/>
-      <c r="Q101" s="4" t="s">
+      <c r="P101" s="18" t="s">
         <v>303</v>
       </c>
       <c r="R101" s="4"/>
@@ -6637,7 +6702,7 @@
       <c r="V101" s="4"/>
       <c r="W101" s="6"/>
     </row>
-    <row r="102" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>9</v>
       </c>
@@ -6686,7 +6751,7 @@
       <c r="V102" s="4"/>
       <c r="W102" s="6"/>
     </row>
-    <row r="103" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>9</v>
       </c>
@@ -6714,18 +6779,18 @@
       <c r="K103" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="L103" s="4" t="s">
-        <v>314</v>
+      <c r="L103" s="19" t="s">
+        <v>397</v>
       </c>
       <c r="M103" s="4"/>
       <c r="N103" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="O103" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="O103" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="P103" s="4" t="s">
-        <v>317</v>
+      <c r="P103" s="19" t="s">
+        <v>398</v>
       </c>
       <c r="Q103" s="4"/>
       <c r="R103" s="4"/>
@@ -6735,7 +6800,7 @@
       <c r="V103" s="4"/>
       <c r="W103" s="6"/>
     </row>
-    <row r="104" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>9</v>
       </c>
@@ -6755,26 +6820,26 @@
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="K104" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="J104" s="4" t="s">
+      <c r="L104" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="K104" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="L104" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="M104" s="4"/>
       <c r="N104" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="O104" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="P104" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="O104" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="P104" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="Q104" s="4"/>
       <c r="R104" s="4"/>
@@ -6784,7 +6849,7 @@
       <c r="V104" s="4"/>
       <c r="W104" s="6"/>
     </row>
-    <row r="105" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>9</v>
       </c>
@@ -6804,26 +6869,26 @@
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="K105" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="J105" s="4" t="s">
+      <c r="L105" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="K105" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="L105" s="4" t="s">
-        <v>328</v>
       </c>
       <c r="M105" s="4"/>
       <c r="N105" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="O105" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="P105" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="O105" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="P105" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="Q105" s="4"/>
       <c r="R105" s="4"/>
@@ -6833,12 +6898,12 @@
       <c r="V105" s="4"/>
       <c r="W105" s="6"/>
     </row>
-    <row r="106" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>10</v>
@@ -6892,7 +6957,7 @@
       <c r="V106" s="4"/>
       <c r="W106" s="6"/>
     </row>
-    <row r="107" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>32</v>
       </c>
@@ -6918,7 +6983,7 @@
         <v>162</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L107" s="4" t="s">
         <v>155</v>
@@ -6951,7 +7016,7 @@
       <c r="V107" s="4"/>
       <c r="W107" s="6"/>
     </row>
-    <row r="108" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>24</v>
       </c>
@@ -6968,13 +7033,13 @@
         <v>292</v>
       </c>
       <c r="F108" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="H108" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>335</v>
       </c>
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
@@ -6992,7 +7057,7 @@
       <c r="V108" s="4"/>
       <c r="W108" s="6"/>
     </row>
-    <row r="109" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>24</v>
       </c>
@@ -7009,13 +7074,13 @@
         <v>292</v>
       </c>
       <c r="F109" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="H109" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="H109" s="4" t="s">
-        <v>338</v>
       </c>
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
@@ -7033,7 +7098,7 @@
       <c r="V109" s="4"/>
       <c r="W109" s="6"/>
     </row>
-    <row r="110" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>36</v>
       </c>
@@ -7076,11 +7141,11 @@
         <v>158</v>
       </c>
       <c r="V110" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="W110" s="6"/>
     </row>
-    <row r="111" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>36</v>
       </c>
@@ -7114,7 +7179,7 @@
         <v>165</v>
       </c>
       <c r="S111" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="T111" s="4" t="s">
         <v>160</v>
@@ -7127,7 +7192,7 @@
       </c>
       <c r="W111" s="6"/>
     </row>
-    <row r="112" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>24</v>
       </c>
@@ -7147,10 +7212,10 @@
         <v>270</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
@@ -7168,7 +7233,7 @@
       <c r="V112" s="4"/>
       <c r="W112" s="6"/>
     </row>
-    <row r="113" spans="1:23" ht="121.5" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:23" ht="126" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>24</v>
       </c>
@@ -7188,10 +7253,10 @@
         <v>275</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
@@ -7209,7 +7274,7 @@
       <c r="V113" s="4"/>
       <c r="W113" s="6"/>
     </row>
-    <row r="114" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>24</v>
       </c>
@@ -7226,13 +7291,13 @@
         <v>292</v>
       </c>
       <c r="F114" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="H114" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>346</v>
       </c>
       <c r="I114" s="4"/>
       <c r="J114" s="4"/>
@@ -7250,7 +7315,7 @@
       <c r="V114" s="4"/>
       <c r="W114" s="6"/>
     </row>
-    <row r="115" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>24</v>
       </c>
@@ -7267,13 +7332,13 @@
         <v>292</v>
       </c>
       <c r="F115" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="H115" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>349</v>
       </c>
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
@@ -7291,7 +7356,7 @@
       <c r="V115" s="4"/>
       <c r="W115" s="6"/>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>41</v>
       </c>
@@ -7315,7 +7380,7 @@
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
       <c r="M116" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
@@ -7328,7 +7393,7 @@
       <c r="V116" s="4"/>
       <c r="W116" s="6"/>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>41</v>
       </c>
@@ -7365,7 +7430,7 @@
       <c r="V117" s="4"/>
       <c r="W117" s="6"/>
     </row>
-    <row r="118" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>41</v>
       </c>
@@ -7402,7 +7467,7 @@
       <c r="V118" s="4"/>
       <c r="W118" s="6"/>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>41</v>
       </c>
@@ -7439,7 +7504,7 @@
       <c r="V119" s="4"/>
       <c r="W119" s="6"/>
     </row>
-    <row r="120" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>20</v>
       </c>
@@ -7482,11 +7547,11 @@
         <v>151</v>
       </c>
       <c r="V120" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="W120" s="6"/>
     </row>
-    <row r="121" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>20</v>
       </c>
@@ -7517,7 +7582,7 @@
         <v>150</v>
       </c>
       <c r="R121" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S121" s="4" t="s">
         <v>155</v>
@@ -7533,7 +7598,7 @@
       </c>
       <c r="W121" s="6"/>
     </row>
-    <row r="122" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>20</v>
       </c>
@@ -7570,7 +7635,7 @@
         <v>151</v>
       </c>
       <c r="T122" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="U122" s="4" t="s">
         <v>155</v>
@@ -7580,7 +7645,7 @@
       </c>
       <c r="W122" s="6"/>
     </row>
-    <row r="123" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>20</v>
       </c>
@@ -7614,8 +7679,8 @@
       <c r="M123" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="N123" s="4" t="s">
-        <v>179</v>
+      <c r="N123" s="13" t="s">
+        <v>399</v>
       </c>
       <c r="O123" s="4" t="s">
         <v>287</v>
@@ -7631,7 +7696,7 @@
       <c r="V123" s="4"/>
       <c r="W123" s="6"/>
     </row>
-    <row r="124" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
         <v>20</v>
       </c>
@@ -7682,7 +7747,7 @@
       <c r="V124" s="4"/>
       <c r="W124" s="6"/>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>20</v>
       </c>
@@ -7725,7 +7790,7 @@
       <c r="V125" s="4"/>
       <c r="W125" s="6"/>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>20</v>
       </c>
@@ -7768,7 +7833,7 @@
       <c r="V126" s="4"/>
       <c r="W126" s="6"/>
     </row>
-    <row r="127" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>20</v>
       </c>
@@ -7811,7 +7876,7 @@
       <c r="V127" s="4"/>
       <c r="W127" s="6"/>
     </row>
-    <row r="128" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>20</v>
       </c>
@@ -7854,7 +7919,7 @@
       <c r="V128" s="4"/>
       <c r="W128" s="6"/>
     </row>
-    <row r="129" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>20</v>
       </c>
@@ -7897,7 +7962,7 @@
       <c r="V129" s="4"/>
       <c r="W129" s="6"/>
     </row>
-    <row r="130" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>20</v>
       </c>
@@ -7940,7 +8005,7 @@
       <c r="V130" s="4"/>
       <c r="W130" s="6"/>
     </row>
-    <row r="131" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>20</v>
       </c>
@@ -7974,7 +8039,7 @@
         <v>155</v>
       </c>
       <c r="S131" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="T131" s="4" t="s">
         <v>154</v>
@@ -7987,7 +8052,7 @@
       </c>
       <c r="W131" s="6"/>
     </row>
-    <row r="132" spans="1:23" ht="94.5" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:23" ht="98" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
         <v>24</v>
       </c>
@@ -8004,13 +8069,13 @@
         <v>292</v>
       </c>
       <c r="F132" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="H132" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="G132" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="H132" s="4" t="s">
-        <v>354</v>
       </c>
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
@@ -8028,7 +8093,7 @@
       <c r="V132" s="4"/>
       <c r="W132" s="6"/>
     </row>
-    <row r="133" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>24</v>
       </c>
@@ -8045,13 +8110,13 @@
         <v>292</v>
       </c>
       <c r="F133" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="H133" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="G133" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="H133" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
@@ -8069,7 +8134,7 @@
       <c r="V133" s="4"/>
       <c r="W133" s="6"/>
     </row>
-    <row r="134" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -8094,7 +8159,7 @@
       <c r="V134" s="7"/>
       <c r="W134" s="8"/>
     </row>
-    <row r="135" spans="1:23" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:23" ht="42" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>190</v>
       </c>
@@ -8108,7 +8173,7 @@
         <v>192</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
@@ -8120,10 +8185,10 @@
       <c r="M135" s="4"/>
       <c r="N135" s="4"/>
       <c r="O135" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="Q135" s="4"/>
       <c r="R135" s="4"/>
@@ -8133,11 +8198,11 @@
       <c r="V135" s="4"/>
       <c r="W135" s="6"/>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="14" t="s">
         <v>195</v>
       </c>
       <c r="C136" s="4" t="s">
@@ -8147,7 +8212,7 @@
         <v>192</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
@@ -8172,11 +8237,11 @@
       <c r="V136" s="4"/>
       <c r="W136" s="6"/>
     </row>
-    <row r="137" spans="1:23" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:23" ht="42" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="14" t="s">
         <v>198</v>
       </c>
       <c r="C137" s="4" t="s">
@@ -8186,7 +8251,7 @@
         <v>192</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
@@ -8194,10 +8259,10 @@
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
       <c r="K137" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
@@ -8211,7 +8276,7 @@
       <c r="V137" s="4"/>
       <c r="W137" s="6"/>
     </row>
-    <row r="138" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>28</v>
       </c>
@@ -8225,7 +8290,7 @@
         <v>29</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>150</v>
@@ -8234,7 +8299,7 @@
         <v>160</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>157</v>
@@ -8258,7 +8323,7 @@
       <c r="V138" s="4"/>
       <c r="W138" s="6"/>
     </row>
-    <row r="139" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>28</v>
       </c>
@@ -8272,13 +8337,13 @@
         <v>29</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>150</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>165</v>
@@ -8305,7 +8370,7 @@
       <c r="V139" s="4"/>
       <c r="W139" s="6"/>
     </row>
-    <row r="140" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>20</v>
       </c>
@@ -8319,7 +8384,7 @@
         <v>33</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
@@ -8345,18 +8410,18 @@
         <v>172</v>
       </c>
       <c r="S140" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="T140" s="4"/>
       <c r="U140" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="V140" s="4" t="s">
         <v>171</v>
       </c>
       <c r="W140" s="6"/>
     </row>
-    <row r="141" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>15</v>
       </c>
@@ -8370,7 +8435,7 @@
         <v>11</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F141" s="4"/>
       <c r="G141" s="4"/>
@@ -8390,7 +8455,7 @@
         <v>165</v>
       </c>
       <c r="Q141" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="R141" s="4" t="s">
         <v>158</v>
@@ -8403,7 +8468,7 @@
       <c r="V141" s="4"/>
       <c r="W141" s="6"/>
     </row>
-    <row r="142" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>15</v>
       </c>
@@ -8417,7 +8482,7 @@
         <v>16</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F142" s="4"/>
       <c r="G142" s="4"/>
@@ -8434,7 +8499,7 @@
         <v>165</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q142" s="4" t="s">
         <v>158</v>
@@ -8450,7 +8515,7 @@
       <c r="V142" s="4"/>
       <c r="W142" s="6"/>
     </row>
-    <row r="143" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>15</v>
       </c>
@@ -8464,7 +8529,7 @@
         <v>16</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F143" s="4"/>
       <c r="G143" s="4"/>
@@ -8484,7 +8549,7 @@
         <v>154</v>
       </c>
       <c r="Q143" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="R143" s="4" t="s">
         <v>151</v>
@@ -8497,7 +8562,7 @@
       <c r="V143" s="4"/>
       <c r="W143" s="6"/>
     </row>
-    <row r="144" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>15</v>
       </c>
@@ -8511,7 +8576,7 @@
         <v>18</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F144" s="4"/>
       <c r="G144" s="4"/>
@@ -8534,7 +8599,7 @@
         <v>151</v>
       </c>
       <c r="R144" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="S144" s="4" t="s">
         <v>153</v>
@@ -8544,7 +8609,7 @@
       <c r="V144" s="4"/>
       <c r="W144" s="6"/>
     </row>
-    <row r="145" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>36</v>
       </c>
@@ -8558,7 +8623,7 @@
         <v>37</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F145" s="4"/>
       <c r="G145" s="4"/>
@@ -8595,7 +8660,7 @@
       </c>
       <c r="W145" s="6"/>
     </row>
-    <row r="146" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>36</v>
       </c>
@@ -8609,7 +8674,7 @@
         <v>72</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
@@ -8646,7 +8711,7 @@
       </c>
       <c r="W146" s="6"/>
     </row>
-    <row r="147" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>36</v>
       </c>
@@ -8660,7 +8725,7 @@
         <v>37</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F147" s="4"/>
       <c r="G147" s="4"/>
@@ -8677,7 +8742,7 @@
         <v>164</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="Q147" s="4" t="s">
         <v>153</v>
@@ -8693,7 +8758,7 @@
       <c r="V147" s="4"/>
       <c r="W147" s="6"/>
     </row>
-    <row r="148" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>36</v>
       </c>
@@ -8707,7 +8772,7 @@
         <v>37</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F148" s="4"/>
       <c r="G148" s="4"/>
@@ -8721,7 +8786,7 @@
         <v>150</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="P148" s="4" t="s">
         <v>158</v>
@@ -8740,7 +8805,7 @@
       <c r="V148" s="4"/>
       <c r="W148" s="6"/>
     </row>
-    <row r="149" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>9</v>
       </c>
@@ -8754,28 +8819,28 @@
         <v>11</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F149" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="H149" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="G149" s="4" t="s">
+      <c r="I149" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="H149" s="4" t="s">
+      <c r="J149" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="I149" s="4" t="s">
+      <c r="K149" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="J149" s="4" t="s">
+      <c r="L149" s="5" t="s">
         <v>369</v>
-      </c>
-      <c r="K149" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="L149" s="5" t="s">
-        <v>371</v>
       </c>
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
@@ -8789,7 +8854,7 @@
       <c r="V149" s="4"/>
       <c r="W149" s="6"/>
     </row>
-    <row r="150" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>9</v>
       </c>
@@ -8803,28 +8868,28 @@
         <v>11</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F150" s="10" t="s">
         <v>254</v>
       </c>
       <c r="G150" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="I150" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="H150" s="4" t="s">
+      <c r="J150" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="I150" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="J150" s="4" t="s">
-        <v>375</v>
       </c>
       <c r="K150" s="4" t="s">
         <v>161</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
@@ -8838,7 +8903,7 @@
       <c r="V150" s="4"/>
       <c r="W150" s="6"/>
     </row>
-    <row r="151" spans="1:23" ht="108" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:23" ht="112" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>9</v>
       </c>
@@ -8852,28 +8917,28 @@
         <v>16</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>297</v>
       </c>
       <c r="G151" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="I151" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="H151" s="4" t="s">
+      <c r="J151" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="I151" s="4" t="s">
+      <c r="K151" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="J151" s="4" t="s">
+      <c r="L151" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="K151" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="L151" s="4" t="s">
-        <v>382</v>
       </c>
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
@@ -8887,7 +8952,7 @@
       <c r="V151" s="4"/>
       <c r="W151" s="6"/>
     </row>
-    <row r="152" spans="1:23" ht="121.5" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:23" ht="126" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>9</v>
       </c>
@@ -8901,28 +8966,28 @@
         <v>11</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>311</v>
       </c>
       <c r="G152" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="I152" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="H152" s="4" t="s">
+      <c r="J152" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="I152" s="4" t="s">
+      <c r="K152" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="J152" s="4" t="s">
+      <c r="L152" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="K152" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="L152" s="4" t="s">
-        <v>388</v>
       </c>
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
@@ -8936,7 +9001,7 @@
       <c r="V152" s="4"/>
       <c r="W152" s="6"/>
     </row>
-    <row r="153" spans="1:23" ht="81" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>9</v>
       </c>
@@ -8950,28 +9015,28 @@
         <v>11</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H153" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="J153" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="K153" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="I153" s="4" t="s">
+      <c r="L153" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="J153" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="K153" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="L153" s="4" t="s">
-        <v>392</v>
       </c>
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
@@ -8985,7 +9050,7 @@
       <c r="V153" s="4"/>
       <c r="W153" s="6"/>
     </row>
-    <row r="154" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>41</v>
       </c>
@@ -8999,13 +9064,13 @@
         <v>79</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>175</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H154" s="4" t="s">
         <v>168</v>
@@ -9037,7 +9102,7 @@
       <c r="V154" s="4"/>
       <c r="W154" s="6"/>
     </row>
-    <row r="155" spans="1:23" ht="27" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>41</v>
       </c>
@@ -9051,13 +9116,13 @@
         <v>81</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>173</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>186</v>
@@ -9090,7 +9155,7 @@
       <c r="V155" s="4"/>
       <c r="W155" s="6"/>
     </row>
-    <row r="156" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>20</v>
       </c>
@@ -9104,7 +9169,7 @@
         <v>52</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F156" s="4"/>
       <c r="G156" s="4"/>
@@ -9118,10 +9183,10 @@
         <v>167</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="Q156" s="4" t="s">
         <v>172</v>
@@ -9141,7 +9206,7 @@
       </c>
       <c r="W156" s="6"/>
     </row>
-    <row r="157" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>20</v>
       </c>
@@ -9155,7 +9220,7 @@
         <v>57</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
@@ -9181,7 +9246,7 @@
         <v>168</v>
       </c>
       <c r="S157" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="T157" s="4"/>
       <c r="U157" s="4" t="s">
@@ -9192,7 +9257,7 @@
       </c>
       <c r="W157" s="6"/>
     </row>
-    <row r="158" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>74</v>
       </c>
@@ -9206,7 +9271,7 @@
         <v>87</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F158" s="4"/>
       <c r="G158" s="4"/>
@@ -9232,14 +9297,14 @@
         <v>165</v>
       </c>
       <c r="S158" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="T158" s="4"/>
       <c r="U158" s="4"/>
       <c r="V158" s="4"/>
       <c r="W158" s="6"/>
     </row>
-    <row r="159" spans="1:23" ht="54" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>74</v>
       </c>
@@ -9253,7 +9318,7 @@
         <v>18</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F159" s="4"/>
       <c r="G159" s="4"/>
@@ -9276,7 +9341,7 @@
         <v>165</v>
       </c>
       <c r="R159" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="S159" s="4" t="s">
         <v>158</v>

--- a/2025-2026工程训练_0308.xlsx
+++ b/2025-2026工程训练_0308.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\工作\1实验教学部\排课\ClassSchedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABBEB78-9D5C-47DF-B13F-75B7AB61FDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AEC4B7-86C8-44D1-8F6C-E33A16E75554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="670" yWindow="4260" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,23 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排课表!$A$1:$W$160</definedName>
   </definedNames>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="417">
   <si>
     <t>教学班名称</t>
   </si>
@@ -299,6 +310,9 @@
   </si>
   <si>
     <t>38</t>
+  </si>
+  <si>
+    <t>化学工程与工艺24(1)</t>
   </si>
   <si>
     <t>化学工程与工艺24(2)</t>
@@ -559,6 +573,15 @@
 A机3-4（郭）</t>
   </si>
   <si>
+    <t>数c1-4（胡）</t>
+  </si>
+  <si>
+    <t>A产1-2
+B压1-2
+B产3-4
+A压3-4</t>
+  </si>
+  <si>
     <t>讲5-7</t>
   </si>
   <si>
@@ -588,17 +611,17 @@
 A柔5-7</t>
   </si>
   <si>
+    <t>数c5-7（胡）</t>
+  </si>
+  <si>
+    <t>B智5-7
+A机5-7</t>
+  </si>
+  <si>
     <t>A智5-7
 B机5-7</t>
   </si>
   <si>
-    <t>B智5-7
-A机5-7</t>
-  </si>
-  <si>
-    <t>数c5-7</t>
-  </si>
-  <si>
     <t>焊5-7</t>
   </si>
   <si>
@@ -621,11 +644,11 @@
 A铣5-7</t>
   </si>
   <si>
+    <t>铸5-7（莫）</t>
+  </si>
+  <si>
     <t>B磨5-7
 A机5-7</t>
-  </si>
-  <si>
-    <t>数c5-7（胡）</t>
   </si>
   <si>
     <t>A智5-6'
@@ -637,12 +660,21 @@
     <t>数c1-4（柏）</t>
   </si>
   <si>
+    <t>A智1-2
+B机1-2（郭）
+B智3-4
+A机3-4（郭）</t>
+  </si>
+  <si>
     <t>A智1-2（胡）
 B机1-2
 B智3-4（胡）
 A机3-4</t>
   </si>
   <si>
+    <t>数c1-4（余）</t>
+  </si>
+  <si>
     <t>未知学院</t>
   </si>
   <si>
@@ -658,7 +690,9 @@
 B铸5-7</t>
   </si>
   <si>
-    <t>先t1-7</t>
+    <t>A铸1-4
+B柔1-4
+先t5-7</t>
   </si>
   <si>
     <t>华师2</t>
@@ -694,16 +728,19 @@
 焊5-7</t>
   </si>
   <si>
+    <t>先t1-7</t>
+  </si>
+  <si>
     <t>数c1-7（余）</t>
   </si>
   <si>
     <t>钳1-7</t>
   </si>
   <si>
-    <t>数c1-7</t>
-  </si>
-  <si>
-    <t>数x1-7</t>
+    <t>数c1-7（胡）</t>
+  </si>
+  <si>
+    <t>数x1-7（杰）</t>
   </si>
   <si>
     <t>工程实践A01</t>
@@ -832,9 +869,6 @@
     <t>铸1-4（莫）</t>
   </si>
   <si>
-    <t>数c1-4（胡）</t>
-  </si>
-  <si>
     <t>A齿1-2
 B热1-2（胡）
 B齿3-4
@@ -847,13 +881,19 @@
 A超3-4</t>
   </si>
   <si>
-    <t>A齿5-7
+    <t>数c1-4（余、胡）</t>
+  </si>
+  <si>
+    <t>数c5-7</t>
+  </si>
+  <si>
+    <t>A齿5-7（林）
 B压5-7</t>
   </si>
   <si>
-    <t>A激②5-6'
+    <t>A激②5-6'（承）
 B装5-6'
-B激②6'-7
+B激②6'-7（承）
 A装6'-7</t>
   </si>
   <si>
@@ -863,7 +903,7 @@
 A热6'-7</t>
   </si>
   <si>
-    <t>B齿5-7
+    <t>B齿5-7（承）
 A压5-7</t>
   </si>
   <si>
@@ -873,7 +913,18 @@
 A超6'-7</t>
   </si>
   <si>
-    <t>铸5-7（莫）</t>
+    <t>A齿5-7
+B压5-7</t>
+  </si>
+  <si>
+    <t>A机5-6'
+B热5-6'（胡）
+B机6'-7
+A热6'-7（胡）</t>
+  </si>
+  <si>
+    <t>B齿5-7
+A压5-7</t>
   </si>
   <si>
     <t>讲1-3
@@ -882,6 +933,31 @@
   <si>
     <t>数c1-4
 数c5-7（胡）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>数x1-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <t>铸5-7(郭、雷)</t>
   </si>
   <si>
     <t>铸5-7（标）</t>
@@ -896,13 +972,13 @@
     <t>压5-7</t>
   </si>
   <si>
+    <t>铸5-7（郭）</t>
+  </si>
+  <si>
     <t>周三</t>
   </si>
   <si>
-    <t>A智1-2
-B机1-2（郭）
-B智3-4
-A机3-4（郭）</t>
+    <t>铸1-4（宋）</t>
   </si>
   <si>
     <t>A智1-2
@@ -927,6 +1003,9 @@
 B热5-6'（林）
 B压6'-7
 A热6'-7（林）</t>
+  </si>
+  <si>
+    <t>数x5-7（杰）</t>
   </si>
   <si>
     <t>数字媒体技术25(1)+(3)15人</t>
@@ -973,6 +1052,12 @@
 A机3-4（郭）</t>
   </si>
   <si>
+    <t>A智1-2
+B机1-2（承）
+B智3-4
+A机3-4（承）</t>
+  </si>
+  <si>
     <t>计算机科学与技术(国际班)25(1)+中英班（6人）</t>
   </si>
   <si>
@@ -1041,6 +1126,9 @@
     <t>先d5-7（莲）</t>
   </si>
   <si>
+    <t>铸5-7(标）</t>
+  </si>
+  <si>
     <t>焊1-4
 A柔5-7
 B机5-7</t>
@@ -1053,6 +1141,9 @@
   <si>
     <t>钳1-4
 铸5-7（莫）</t>
+  </si>
+  <si>
+    <t>数x1-7</t>
   </si>
   <si>
     <t>周四</t>
@@ -1073,8 +1164,8 @@
 A激②5-7</t>
   </si>
   <si>
-    <t>A铸1-4
-B柔1-4
+    <t xml:space="preserve">
+先t1-4
 B压5-7
 A机5-7</t>
   </si>
@@ -1146,7 +1237,7 @@
   </si>
   <si>
     <t>焊1-4
-数c5-7</t>
+数c5-7（胡）</t>
   </si>
   <si>
     <t>A智1-2
@@ -1171,6 +1262,11 @@
 数x5-7</t>
   </si>
   <si>
+    <t xml:space="preserve">
+数c1-4
+焊5-7</t>
+  </si>
+  <si>
     <t>A智1-2
 B机1-2
 B智3-4
@@ -1182,6 +1278,13 @@
 先t5-7</t>
   </si>
   <si>
+    <t>铣m1-4
+A产5-6'
+B柔5-6'
+B产6'-7
+A柔6'-7</t>
+  </si>
+  <si>
     <t>讲1-3
 A智5-6'
 B机5-6'
@@ -1208,15 +1311,15 @@
 先t5-7</t>
   </si>
   <si>
-    <t>数x1-4
+    <t>数x1-4（杰）
 A压5-6'
 B装5-6'
 B压6'-7
 A装6'-7</t>
   </si>
   <si>
-    <t>数c1-4
-铸5-7</t>
+    <t>数c1-4(余）
+铸5-7（莫）</t>
   </si>
   <si>
     <t>讲1-3
@@ -1253,7 +1356,19 @@
 先t5-7</t>
   </si>
   <si>
+    <t>A智1-2
+B机1-2（辛）
+B智3-4
+A机3-4（辛）</t>
+  </si>
+  <si>
     <t>数x1-4（杰）</t>
+  </si>
+  <si>
+    <t>A智1-2
+B机1-2（郭）
+B智3-4
+A机3-4郭）</t>
   </si>
   <si>
     <t>讲1-3
@@ -1365,6 +1480,15 @@
 A产3-4</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>A智5-6'（胡）
+B产5-6'
+B智6'-7（胡）
+A产6'-7</t>
+  </si>
+  <si>
     <t>讲1-3
 数x5-8</t>
   </si>
@@ -1432,6 +1556,12 @@
   <si>
     <t>B柔5-7
 A机5-7</t>
+  </si>
+  <si>
+    <t>A智1-2（胡）
+B产1-2
+B智3-4（胡）
+A产3-4</t>
   </si>
   <si>
     <t>讲1-3
@@ -1601,63 +1731,6 @@
   <si>
     <t>A产5-7
 B智5-7</t>
-  </si>
-  <si>
-    <t>化学工程与工艺24(1)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>数x1-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>数c5-7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-数c1-4
-焊5-7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>铣m1-4
-A产5-6'
-B柔5-6'
-B产6'-7
-A柔6'-7</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>A产1-2
-B压1-2
-B产3-4
-A压3-4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>A产1-2
-B压1-2
-B产3-4
-A压3-4</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1687,6 +1760,35 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1704,42 +1806,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1760,13 +1828,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1782,85 +1856,85 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="6" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 13" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="常规 15" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="常规 4" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="常规 5" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="常规 13" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 15" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="常规 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="常规 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="常规 4" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="常规 5" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2173,7 +2247,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -2182,64 +2256,64 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="56" x14ac:dyDescent="0.25">
@@ -2256,26 +2330,26 @@
         <v>5</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -2303,26 +2377,26 @@
         <v>7</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H3" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
@@ -2350,45 +2424,45 @@
         <v>69</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
@@ -2409,26 +2483,26 @@
         <v>62</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
@@ -2447,7 +2521,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>4</v>
@@ -2456,7 +2530,7 @@
         <v>47</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -2469,22 +2543,22 @@
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="S6" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="T6" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="U6" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V6" s="4"/>
       <c r="W6" s="6"/>
@@ -2494,7 +2568,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>4</v>
@@ -2503,7 +2577,7 @@
         <v>47</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -2516,22 +2590,22 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="V7" s="4"/>
       <c r="W7" s="6"/>
@@ -2550,7 +2624,7 @@
         <v>69</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -2560,23 +2634,23 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="P8" s="17" t="s">
-        <v>400</v>
+        <v>161</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="Q8" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="S8" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
@@ -2597,7 +2671,7 @@
         <v>84</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -2607,25 +2681,24 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="R9" s="19" t="s">
-        <v>401</v>
+        <v>155</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="S9" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="T9" s="4"/>
+        <v>156</v>
+      </c>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="6"/>
@@ -2634,8 +2707,8 @@
       <c r="A10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>101</v>
+      <c r="B10" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>10</v>
@@ -2644,54 +2717,54 @@
         <v>79</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>178</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="W10" s="6"/>
     </row>
@@ -2699,8 +2772,8 @@
       <c r="A11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>102</v>
+      <c r="B11" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>10</v>
@@ -2709,54 +2782,54 @@
         <v>79</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="P11" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q11" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="R11" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="T11" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="R11" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="T11" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="U11" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="V11" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="W11" s="6"/>
     </row>
@@ -2764,8 +2837,8 @@
       <c r="A12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>110</v>
+      <c r="B12" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>10</v>
@@ -2774,54 +2847,54 @@
         <v>79</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="S12" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="V12" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="W12" s="6"/>
     </row>
@@ -2829,8 +2902,8 @@
       <c r="A13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>111</v>
+      <c r="B13" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>10</v>
@@ -2839,54 +2912,54 @@
         <v>79</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q13" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="S13" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U13" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="V13" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="W13" s="6"/>
     </row>
@@ -2894,7 +2967,7 @@
       <c r="A14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="8" t="s">
         <v>78</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -2904,29 +2977,29 @@
         <v>79</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
@@ -2943,7 +3016,7 @@
       <c r="A15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="8" t="s">
         <v>80</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -2953,29 +3026,29 @@
         <v>81</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
@@ -3002,7 +3075,7 @@
         <v>33</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -3012,29 +3085,29 @@
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="V16" s="4"/>
       <c r="W16" s="6"/>
@@ -3053,7 +3126,7 @@
         <v>47</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -3063,29 +3136,29 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="P17" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="R17" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="Q17" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="R17" s="4" t="s">
-        <v>177</v>
-      </c>
       <c r="S17" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="U17" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="V17" s="4"/>
       <c r="W17" s="6"/>
@@ -3104,46 +3177,46 @@
         <v>16</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L18" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="L18" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="M18" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="4" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S18" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
@@ -3163,46 +3236,46 @@
         <v>16</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="R19" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="R19" s="4" t="s">
+      <c r="S19" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="S19" s="4" t="s">
+      <c r="T19" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="T19" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
@@ -3210,19 +3283,19 @@
     </row>
     <row r="20" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -3234,10 +3307,10 @@
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="P20" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
+      </c>
+      <c r="P20" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
@@ -3249,19 +3322,19 @@
     </row>
     <row r="21" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="14" t="s">
         <v>195</v>
       </c>
+      <c r="B21" s="11" t="s">
+        <v>200</v>
+      </c>
       <c r="C21" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -3269,10 +3342,10 @@
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
@@ -3288,19 +3361,19 @@
     </row>
     <row r="22" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>198</v>
+        <v>195</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>203</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -3308,10 +3381,10 @@
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
@@ -3326,45 +3399,45 @@
       <c r="W22" s="6"/>
     </row>
     <row r="23" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="8"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="14"/>
     </row>
     <row r="24" spans="1:23" ht="28" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B24" s="14" t="s">
         <v>195</v>
       </c>
+      <c r="B24" s="11" t="s">
+        <v>200</v>
+      </c>
       <c r="C24" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -3372,10 +3445,10 @@
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
@@ -3391,19 +3464,19 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>198</v>
+        <v>195</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>203</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -3411,10 +3484,10 @@
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
@@ -3430,19 +3503,19 @@
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -3454,10 +3527,10 @@
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
@@ -3469,29 +3542,29 @@
     </row>
     <row r="27" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -3508,28 +3581,28 @@
     </row>
     <row r="28" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -3547,29 +3620,29 @@
     </row>
     <row r="29" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -3586,28 +3659,28 @@
     </row>
     <row r="30" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -3625,26 +3698,26 @@
     </row>
     <row r="31" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -3664,19 +3737,19 @@
     </row>
     <row r="32" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
@@ -3686,12 +3759,12 @@
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
       <c r="P32" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
@@ -3703,19 +3776,19 @@
     </row>
     <row r="33" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -3726,10 +3799,10 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
@@ -3742,19 +3815,19 @@
     </row>
     <row r="34" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -3765,11 +3838,11 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="O34" s="4"/>
       <c r="P34" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q34" s="4"/>
       <c r="R34" s="4"/>
@@ -3781,19 +3854,19 @@
     </row>
     <row r="35" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
@@ -3802,12 +3875,12 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
@@ -3820,19 +3893,19 @@
     </row>
     <row r="36" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
@@ -3841,10 +3914,10 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
@@ -3859,19 +3932,19 @@
     </row>
     <row r="37" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
@@ -3885,7 +3958,7 @@
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
       <c r="Q37" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
@@ -3896,19 +3969,19 @@
     </row>
     <row r="38" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
@@ -3923,7 +3996,7 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
       <c r="R38" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="S38" s="4"/>
       <c r="T38" s="4"/>
@@ -3933,19 +4006,19 @@
     </row>
     <row r="39" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
@@ -3961,7 +4034,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
       <c r="S39" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
@@ -3970,19 +4043,19 @@
     </row>
     <row r="40" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
@@ -3999,7 +4072,7 @@
       <c r="R40" s="4"/>
       <c r="S40" s="4"/>
       <c r="T40" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
@@ -4007,19 +4080,19 @@
     </row>
     <row r="41" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
@@ -4037,26 +4110,26 @@
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
       <c r="U41" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="V41" s="4"/>
       <c r="W41" s="6"/>
     </row>
     <row r="42" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
@@ -4075,25 +4148,25 @@
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
       <c r="V42" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="W42" s="6"/>
     </row>
     <row r="43" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
@@ -4113,24 +4186,24 @@
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
       <c r="W43" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
@@ -4149,25 +4222,25 @@
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
       <c r="V44" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="W44" s="6"/>
     </row>
     <row r="45" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
@@ -4185,30 +4258,30 @@
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
       <c r="U45" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="V45" s="4"/>
       <c r="W45" s="6"/>
     </row>
     <row r="46" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F46" s="4"/>
       <c r="G46" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -4229,24 +4302,24 @@
     </row>
     <row r="47" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -4266,25 +4339,25 @@
     </row>
     <row r="48" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
@@ -4303,26 +4376,26 @@
     </row>
     <row r="49" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -4340,19 +4413,19 @@
     </row>
     <row r="50" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
@@ -4360,7 +4433,7 @@
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -4377,19 +4450,19 @@
     </row>
     <row r="51" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -4398,7 +4471,7 @@
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
@@ -4414,19 +4487,19 @@
     </row>
     <row r="52" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
@@ -4436,7 +4509,7 @@
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
@@ -4451,19 +4524,19 @@
     </row>
     <row r="53" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
@@ -4474,7 +4547,7 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="O53" s="4"/>
       <c r="P53" s="4"/>
@@ -4488,19 +4561,19 @@
     </row>
     <row r="54" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
@@ -4512,7 +4585,7 @@
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
@@ -4525,19 +4598,19 @@
     </row>
     <row r="55" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
@@ -4550,7 +4623,7 @@
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
       <c r="P55" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q55" s="4"/>
       <c r="R55" s="4"/>
@@ -4562,19 +4635,19 @@
     </row>
     <row r="56" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -4588,7 +4661,7 @@
       <c r="O56" s="4"/>
       <c r="P56" s="4"/>
       <c r="Q56" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="R56" s="4"/>
       <c r="S56" s="4"/>
@@ -4599,19 +4672,19 @@
     </row>
     <row r="57" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
@@ -4626,7 +4699,7 @@
       <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
       <c r="R57" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="S57" s="4"/>
       <c r="T57" s="4"/>
@@ -4636,19 +4709,19 @@
     </row>
     <row r="58" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
@@ -4663,7 +4736,7 @@
       <c r="Q58" s="4"/>
       <c r="R58" s="4"/>
       <c r="S58" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
@@ -4672,19 +4745,19 @@
     </row>
     <row r="59" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F59" s="4"/>
       <c r="G59" s="4"/>
@@ -4700,7 +4773,7 @@
       <c r="R59" s="4"/>
       <c r="S59" s="4"/>
       <c r="T59" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
@@ -4720,44 +4793,44 @@
         <v>33</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>245</v>
+        <v>168</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="N60" s="4"/>
       <c r="O60" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q60" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="R60" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S60" s="4"/>
       <c r="T60" s="4"/>
@@ -4779,44 +4852,44 @@
         <v>25</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G61" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="J61" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="H61" s="4" t="s">
+      <c r="K61" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="K61" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>246</v>
+      <c r="L61" s="15" t="s">
+        <v>251</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="N61" s="4"/>
       <c r="O61" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q61" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="P61" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q61" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="R61" s="4" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="S61" s="4"/>
       <c r="T61" s="4"/>
@@ -4829,7 +4902,7 @@
         <v>32</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>10</v>
@@ -4838,56 +4911,56 @@
         <v>57</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="K62" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="K62" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="M62" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="M62" s="4" t="s">
-        <v>169</v>
       </c>
       <c r="N62" s="4"/>
       <c r="O62" s="4" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q62" s="4" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="R62" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="S62" s="4" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="T62" s="4" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="U62" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="V62" s="9" t="s">
-        <v>181</v>
+        <v>259</v>
+      </c>
+      <c r="V62" s="15" t="s">
+        <v>184</v>
       </c>
       <c r="W62" s="6"/>
     </row>
@@ -4896,7 +4969,7 @@
         <v>32</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>10</v>
@@ -4905,56 +4978,56 @@
         <v>33</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="H63" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="J63" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="K63" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="I63" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="J63" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>169</v>
-      </c>
       <c r="L63" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="N63" s="4"/>
       <c r="O63" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="Q63" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="R63" s="9" t="s">
-        <v>249</v>
+        <v>181</v>
+      </c>
+      <c r="R63" s="15" t="s">
+        <v>256</v>
       </c>
       <c r="S63" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="T63" s="4" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="U63" s="4" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="V63" s="4" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="W63" s="6"/>
     </row>
@@ -4972,35 +5045,35 @@
         <v>42</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="H64" s="13" t="s">
-        <v>395</v>
+        <v>264</v>
+      </c>
+      <c r="H64" s="17" t="s">
+        <v>265</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N64" s="4"/>
       <c r="O64" s="4" t="s">
-        <v>181</v>
+        <v>266</v>
       </c>
       <c r="P64" s="4"/>
       <c r="Q64" s="4"/>
@@ -5016,7 +5089,7 @@
         <v>36</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>4</v>
@@ -5025,25 +5098,25 @@
         <v>37</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G65" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I65" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="K65" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="I65" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="K65" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="L65" s="9" t="s">
-        <v>165</v>
+      <c r="L65" s="15" t="s">
+        <v>166</v>
       </c>
       <c r="M65" s="4"/>
       <c r="O65" s="4"/>
@@ -5061,7 +5134,7 @@
         <v>36</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>4</v>
@@ -5070,25 +5143,25 @@
         <v>37</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I66" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J66" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="J66" s="4" t="s">
+      <c r="K66" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="L66" s="15" t="s">
         <v>159</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="L66" s="9" t="s">
-        <v>158</v>
       </c>
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
@@ -5116,31 +5189,31 @@
         <v>29</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
@@ -5167,31 +5240,31 @@
         <v>4</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L68" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="M68" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="M68" s="4" t="s">
-        <v>178</v>
       </c>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
@@ -5209,7 +5282,7 @@
         <v>20</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>4</v>
@@ -5218,7 +5291,7 @@
         <v>5</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F69" s="4"/>
       <c r="H69" s="4"/>
@@ -5231,16 +5304,16 @@
       <c r="O69" s="4"/>
       <c r="P69" s="4"/>
       <c r="Q69" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R69" s="4" t="s">
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="S69" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="T69" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
@@ -5251,7 +5324,7 @@
         <v>20</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>4</v>
@@ -5260,7 +5333,7 @@
         <v>5</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -5274,16 +5347,16 @@
       <c r="O70" s="4"/>
       <c r="P70" s="4"/>
       <c r="Q70" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R70" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S70" s="4" t="s">
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="T70" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
@@ -5303,7 +5376,7 @@
         <v>47</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4"/>
@@ -5317,16 +5390,16 @@
       <c r="O71" s="4"/>
       <c r="P71" s="4"/>
       <c r="Q71" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R71" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="S71" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="T71" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
@@ -5346,7 +5419,7 @@
         <v>5</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4"/>
@@ -5360,16 +5433,16 @@
       <c r="O72" s="4"/>
       <c r="P72" s="4"/>
       <c r="Q72" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R72" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="S72" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="S72" s="4" t="s">
-        <v>177</v>
-      </c>
       <c r="T72" s="4" t="s">
-        <v>181</v>
+        <v>270</v>
       </c>
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
@@ -5389,29 +5462,29 @@
         <v>4</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
       <c r="L73" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M73" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="O73" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q73" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="O73" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="P73" s="4" t="s">
+      <c r="R73" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="Q73" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="R73" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="S73" s="4"/>
       <c r="T73" s="4"/>
@@ -5420,29 +5493,29 @@
       <c r="W73" s="6"/>
     </row>
     <row r="74" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="7"/>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
-      <c r="P74" s="7"/>
-      <c r="Q74" s="7"/>
-      <c r="R74" s="7"/>
-      <c r="S74" s="7"/>
-      <c r="T74" s="7"/>
-      <c r="U74" s="7"/>
-      <c r="V74" s="7"/>
-      <c r="W74" s="8"/>
+      <c r="A74" s="12"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="12"/>
+      <c r="L74" s="12"/>
+      <c r="M74" s="12"/>
+      <c r="N74" s="12"/>
+      <c r="O74" s="12"/>
+      <c r="P74" s="12"/>
+      <c r="Q74" s="12"/>
+      <c r="R74" s="12"/>
+      <c r="S74" s="12"/>
+      <c r="T74" s="12"/>
+      <c r="U74" s="12"/>
+      <c r="V74" s="12"/>
+      <c r="W74" s="14"/>
     </row>
     <row r="75" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
@@ -5458,46 +5531,46 @@
         <v>52</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F75" s="4"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J75" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="O75" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="P75" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="K75" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="L75" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="M75" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="N75" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="O75" s="4" t="s">
+      <c r="Q75" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="R75" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="P75" s="4" t="s">
+      <c r="S75" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="Q75" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="R75" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="S75" s="4" t="s">
+      <c r="T75" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="T75" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
@@ -5517,46 +5590,46 @@
         <v>22</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J76" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="M76" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="N76" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="O76" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q76" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="R76" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="S76" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="K76" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="M76" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="N76" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="O76" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="P76" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q76" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="R76" s="4" t="s">
+      <c r="T76" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="S76" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="T76" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
@@ -5564,10 +5637,10 @@
     </row>
     <row r="77" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>10</v>
@@ -5576,57 +5649,57 @@
         <v>33</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J77" s="4"/>
       <c r="K77" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M77" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q77" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="N77" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="O77" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="P77" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q77" s="4" t="s">
+      <c r="R77" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="S77" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="R77" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="S77" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="T77" s="4" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="U77" s="4"/>
       <c r="V77" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="W77" s="6"/>
     </row>
     <row r="78" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>10</v>
@@ -5635,48 +5708,48 @@
         <v>33</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J78" s="4"/>
       <c r="K78" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q78" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="L78" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="M78" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="N78" s="4" t="s">
+      <c r="R78" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="S78" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="T78" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="O78" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="P78" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q78" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="R78" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="S78" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="T78" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="U78" s="4"/>
       <c r="V78" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="W78" s="6"/>
     </row>
@@ -5694,34 +5767,34 @@
         <v>57</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F79" s="4"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J79" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="K79" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="K79" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="L79" s="4" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="M79" s="4" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="N79" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q79" s="4"/>
       <c r="R79" s="4"/>
@@ -5745,34 +5818,34 @@
         <v>57</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="M80" s="4" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="N80" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>180</v>
+        <v>277</v>
       </c>
       <c r="Q80" s="4"/>
       <c r="R80" s="4"/>
@@ -5796,34 +5869,34 @@
         <v>57</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M81" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q81" s="4"/>
       <c r="R81" s="4"/>
@@ -5847,34 +5920,34 @@
         <v>57</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N82" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="Q82" s="4"/>
       <c r="R82" s="4"/>
@@ -5886,10 +5959,10 @@
     </row>
     <row r="83" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C83" s="4">
         <v>24</v>
@@ -5898,16 +5971,16 @@
         <v>44</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
@@ -5927,10 +6000,10 @@
     </row>
     <row r="84" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C84" s="4">
         <v>24</v>
@@ -5939,16 +6012,16 @@
         <v>44</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
@@ -5980,46 +6053,46 @@
         <v>5</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="L85" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="N85" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="M85" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="N85" s="4" t="s">
+      <c r="O85" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="O85" s="4" t="s">
+      <c r="P85" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q85" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="R85" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="P85" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q85" s="4" t="s">
+      <c r="S85" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="T85" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="R85" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="S85" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="T85" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="U85" s="4"/>
       <c r="V85" s="4"/>
@@ -6039,46 +6112,46 @@
         <v>7</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K86" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="N86" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="O86" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="L86" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="M86" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="N86" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="O86" s="4" t="s">
+      <c r="P86" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q86" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="R86" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="S86" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="T86" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="P86" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q86" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="R86" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="S86" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="T86" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="U86" s="4"/>
       <c r="V86" s="4"/>
@@ -6086,28 +6159,28 @@
     </row>
     <row r="87" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C87" s="4">
         <v>24</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
@@ -6127,28 +6200,28 @@
     </row>
     <row r="88" spans="1:23" ht="70" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C88" s="4">
         <v>24</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
@@ -6168,28 +6241,28 @@
     </row>
     <row r="89" spans="1:23" ht="84" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="C89" s="4">
         <v>24</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
@@ -6212,7 +6285,7 @@
         <v>20</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>4</v>
@@ -6221,34 +6294,34 @@
         <v>33</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N90" s="4" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="O90" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="P90" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="P90" s="4" t="s">
-        <v>178</v>
       </c>
       <c r="Q90" s="4"/>
       <c r="R90" s="4"/>
@@ -6263,7 +6336,7 @@
         <v>20</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>4</v>
@@ -6272,34 +6345,34 @@
         <v>57</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F91" s="4"/>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J91" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="K91" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="K91" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="L91" s="4" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="N91" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>181</v>
+        <v>303</v>
       </c>
       <c r="Q91" s="4"/>
       <c r="R91" s="4"/>
@@ -6314,7 +6387,7 @@
         <v>20</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>4</v>
@@ -6323,7 +6396,7 @@
         <v>22</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F92" s="4"/>
       <c r="G92" s="4"/>
@@ -6337,16 +6410,16 @@
       <c r="O92" s="4"/>
       <c r="P92" s="4"/>
       <c r="Q92" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R92" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="S92" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T92" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="U92" s="4"/>
       <c r="V92" s="4"/>
@@ -6357,7 +6430,7 @@
         <v>20</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>4</v>
@@ -6366,7 +6439,7 @@
         <v>5</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
@@ -6380,16 +6453,16 @@
       <c r="O93" s="4"/>
       <c r="P93" s="4"/>
       <c r="Q93" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R93" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S93" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="T93" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
@@ -6397,19 +6470,19 @@
     </row>
     <row r="94" spans="1:23" ht="42" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
@@ -6421,10 +6494,10 @@
       <c r="M94" s="4"/>
       <c r="N94" s="4"/>
       <c r="O94" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="Q94" s="4"/>
       <c r="R94" s="4"/>
@@ -6436,19 +6509,19 @@
     </row>
     <row r="95" spans="1:23" ht="42" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B95" s="14" t="s">
         <v>195</v>
       </c>
+      <c r="B95" s="11" t="s">
+        <v>200</v>
+      </c>
       <c r="C95" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
@@ -6456,10 +6529,10 @@
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
       <c r="K95" s="4" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="M95" s="4"/>
       <c r="N95" s="4"/>
@@ -6475,19 +6548,19 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>198</v>
+        <v>195</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>203</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
@@ -6495,10 +6568,10 @@
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
       <c r="K96" s="4" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>206</v>
+        <v>307</v>
       </c>
       <c r="M96" s="4"/>
       <c r="N96" s="4"/>
@@ -6513,45 +6586,45 @@
       <c r="W96" s="6"/>
     </row>
     <row r="97" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="7"/>
-      <c r="B97" s="15"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="7"/>
-      <c r="J97" s="7"/>
-      <c r="K97" s="7"/>
-      <c r="L97" s="7"/>
-      <c r="M97" s="7"/>
-      <c r="N97" s="7"/>
-      <c r="O97" s="7"/>
-      <c r="P97" s="7"/>
-      <c r="Q97" s="7"/>
-      <c r="R97" s="7"/>
-      <c r="S97" s="7"/>
-      <c r="T97" s="7"/>
-      <c r="U97" s="7"/>
-      <c r="V97" s="7"/>
-      <c r="W97" s="8"/>
+      <c r="A97" s="12"/>
+      <c r="B97" s="18"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12"/>
+      <c r="H97" s="12"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="12"/>
+      <c r="L97" s="12"/>
+      <c r="M97" s="12"/>
+      <c r="N97" s="12"/>
+      <c r="O97" s="12"/>
+      <c r="P97" s="12"/>
+      <c r="Q97" s="12"/>
+      <c r="R97" s="12"/>
+      <c r="S97" s="12"/>
+      <c r="T97" s="12"/>
+      <c r="U97" s="12"/>
+      <c r="V97" s="12"/>
+      <c r="W97" s="14"/>
     </row>
     <row r="98" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B98" s="14" t="s">
         <v>195</v>
       </c>
+      <c r="B98" s="11" t="s">
+        <v>200</v>
+      </c>
       <c r="C98" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F98" s="4"/>
       <c r="G98" s="4"/>
@@ -6559,10 +6632,10 @@
       <c r="I98" s="4"/>
       <c r="J98" s="4"/>
       <c r="K98" s="4" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="M98" s="4"/>
       <c r="N98" s="4"/>
@@ -6578,19 +6651,19 @@
     </row>
     <row r="99" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>198</v>
+        <v>195</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>203</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
@@ -6598,10 +6671,10 @@
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
       <c r="K99" s="4" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
@@ -6617,19 +6690,19 @@
     </row>
     <row r="100" spans="1:23" ht="56" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F100" s="4"/>
       <c r="G100" s="4"/>
@@ -6641,10 +6714,10 @@
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
       <c r="O100" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="P100" s="4" t="s">
-        <v>296</v>
+        <v>210</v>
+      </c>
+      <c r="P100" s="9" t="s">
+        <v>312</v>
       </c>
       <c r="Q100" s="4"/>
       <c r="R100" s="4"/>
@@ -6659,41 +6732,41 @@
         <v>9</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="M101" s="4"/>
       <c r="N101" s="4" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="P101" s="18" t="s">
-        <v>303</v>
+        <v>318</v>
+      </c>
+      <c r="P101" s="16" t="s">
+        <v>319</v>
       </c>
       <c r="R101" s="4"/>
       <c r="S101" s="4"/>
@@ -6707,7 +6780,7 @@
         <v>9</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>10</v>
@@ -6716,32 +6789,32 @@
         <v>52</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F102" s="4"/>
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="M102" s="4"/>
       <c r="N102" s="4" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="P102" s="4" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="Q102" s="4"/>
       <c r="R102" s="4"/>
@@ -6765,32 +6838,32 @@
         <v>7</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F103" s="4"/>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="L103" s="19" t="s">
-        <v>397</v>
+        <v>329</v>
+      </c>
+      <c r="L103" s="7" t="s">
+        <v>330</v>
       </c>
       <c r="M103" s="4"/>
       <c r="N103" s="4" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="P103" s="19" t="s">
-        <v>398</v>
+        <v>332</v>
+      </c>
+      <c r="P103" s="7" t="s">
+        <v>333</v>
       </c>
       <c r="Q103" s="4"/>
       <c r="R103" s="4"/>
@@ -6814,32 +6887,32 @@
         <v>52</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F104" s="4"/>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="M104" s="4"/>
       <c r="N104" s="4" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="P104" s="4" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="Q104" s="4"/>
       <c r="R104" s="4"/>
@@ -6863,32 +6936,32 @@
         <v>12</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="M105" s="4"/>
       <c r="N105" s="4" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="P105" s="4" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="Q105" s="4"/>
       <c r="R105" s="4"/>
@@ -6902,8 +6975,8 @@
       <c r="A106" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B106" s="11" t="s">
-        <v>394</v>
+      <c r="B106" s="17" t="s">
+        <v>92</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>10</v>
@@ -6912,46 +6985,46 @@
         <v>91</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L106" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="M106" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="N106" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="O106" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="P106" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q106" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="R106" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="S106" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="T106" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="M106" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="N106" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="O106" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="P106" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q106" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="R106" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="S106" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="T106" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="U106" s="4"/>
       <c r="V106" s="4"/>
@@ -6962,7 +7035,7 @@
         <v>32</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>10</v>
@@ -6971,46 +7044,46 @@
         <v>91</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
       <c r="I107" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J107" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="L107" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="M107" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="N107" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="O107" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="P107" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q107" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="K107" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="L107" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="M107" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="N107" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="O107" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="P107" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q107" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="R107" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="S107" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="S107" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="T107" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U107" s="4"/>
       <c r="V107" s="4"/>
@@ -7030,16 +7103,16 @@
         <v>25</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
@@ -7071,16 +7144,16 @@
         <v>7</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
@@ -7103,7 +7176,7 @@
         <v>36</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>4</v>
@@ -7112,7 +7185,7 @@
         <v>29</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="4"/>
@@ -7126,22 +7199,22 @@
       <c r="O110" s="4"/>
       <c r="P110" s="4"/>
       <c r="Q110" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R110" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="S110" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="S110" s="4" t="s">
+      <c r="T110" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="U110" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="T110" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="U110" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="V110" s="4" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="W110" s="6"/>
     </row>
@@ -7150,7 +7223,7 @@
         <v>36</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>4</v>
@@ -7159,7 +7232,7 @@
         <v>69</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4"/>
@@ -7173,22 +7246,22 @@
       <c r="O111" s="4"/>
       <c r="P111" s="4"/>
       <c r="Q111" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R111" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="S111" s="4" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="T111" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="U111" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="U111" s="4" t="s">
+      <c r="V111" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="V111" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="W111" s="6"/>
     </row>
@@ -7197,7 +7270,7 @@
         <v>24</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>4</v>
@@ -7206,16 +7279,16 @@
         <v>33</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
@@ -7238,7 +7311,7 @@
         <v>24</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>4</v>
@@ -7247,16 +7320,16 @@
         <v>57</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
@@ -7288,16 +7361,16 @@
         <v>5</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="I114" s="4"/>
       <c r="J114" s="4"/>
@@ -7329,16 +7402,16 @@
         <v>47</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
@@ -7360,8 +7433,8 @@
       <c r="A116" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B116" s="12" t="s">
-        <v>101</v>
+      <c r="B116" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>10</v>
@@ -7370,7 +7443,7 @@
         <v>79</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F116" s="4"/>
       <c r="G116" s="4"/>
@@ -7380,7 +7453,7 @@
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
       <c r="M116" s="4" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
@@ -7397,8 +7470,8 @@
       <c r="A117" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B117" s="12" t="s">
-        <v>102</v>
+      <c r="B117" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>10</v>
@@ -7407,7 +7480,7 @@
         <v>79</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F117" s="4"/>
       <c r="G117" s="4"/>
@@ -7417,7 +7490,7 @@
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
       <c r="M117" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
@@ -7434,8 +7507,8 @@
       <c r="A118" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B118" s="12" t="s">
-        <v>110</v>
+      <c r="B118" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>10</v>
@@ -7444,7 +7517,7 @@
         <v>79</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F118" s="4"/>
       <c r="G118" s="4"/>
@@ -7454,7 +7527,7 @@
       <c r="K118" s="4"/>
       <c r="L118" s="4"/>
       <c r="M118" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
@@ -7471,8 +7544,8 @@
       <c r="A119" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B119" s="12" t="s">
-        <v>111</v>
+      <c r="B119" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>10</v>
@@ -7481,7 +7554,7 @@
         <v>79</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F119" s="4"/>
       <c r="G119" s="4"/>
@@ -7491,7 +7564,7 @@
       <c r="K119" s="4"/>
       <c r="L119" s="4"/>
       <c r="M119" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
@@ -7518,7 +7591,7 @@
         <v>22</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F120" s="4"/>
       <c r="G120" s="4"/>
@@ -7532,22 +7605,22 @@
       <c r="O120" s="4"/>
       <c r="P120" s="4"/>
       <c r="Q120" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R120" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="S120" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="S120" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="T120" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="U120" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="V120" s="4" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="W120" s="6"/>
     </row>
@@ -7556,7 +7629,7 @@
         <v>20</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>4</v>
@@ -7565,7 +7638,7 @@
         <v>5</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F121" s="4"/>
       <c r="G121" s="4"/>
@@ -7579,22 +7652,22 @@
       <c r="O121" s="4"/>
       <c r="P121" s="4"/>
       <c r="Q121" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R121" s="4" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="S121" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="T121" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="U121" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="T121" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="U121" s="4" t="s">
+      <c r="V121" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="V121" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="W121" s="6"/>
     </row>
@@ -7603,7 +7676,7 @@
         <v>20</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>4</v>
@@ -7612,7 +7685,7 @@
         <v>5</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
@@ -7626,22 +7699,22 @@
       <c r="O122" s="4"/>
       <c r="P122" s="4"/>
       <c r="Q122" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R122" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S122" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="T122" s="4" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="U122" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="V122" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="V122" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="W122" s="6"/>
     </row>
@@ -7650,7 +7723,7 @@
         <v>20</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>4</v>
@@ -7659,34 +7732,34 @@
         <v>47</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
       <c r="I123" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M123" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="N123" s="13" t="s">
-        <v>399</v>
+        <v>300</v>
+      </c>
+      <c r="N123" s="17" t="s">
+        <v>370</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="P123" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q123" s="4"/>
       <c r="R123" s="4"/>
@@ -7701,7 +7774,7 @@
         <v>20</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>4</v>
@@ -7710,34 +7783,34 @@
         <v>5</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="K124" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="L124" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="M124" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="N124" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="O124" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="P124" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="L124" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="M124" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="N124" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="O124" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="P124" s="4" t="s">
-        <v>178</v>
       </c>
       <c r="Q124" s="4"/>
       <c r="R124" s="4"/>
@@ -7752,7 +7825,7 @@
         <v>20</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>4</v>
@@ -7761,7 +7834,7 @@
         <v>22</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F125" s="4"/>
       <c r="G125" s="4"/>
@@ -7775,16 +7848,16 @@
       <c r="O125" s="4"/>
       <c r="P125" s="4"/>
       <c r="Q125" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="R125" s="4" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="S125" s="4" t="s">
-        <v>181</v>
+        <v>267</v>
       </c>
       <c r="T125" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="U125" s="4"/>
       <c r="V125" s="4"/>
@@ -7795,7 +7868,7 @@
         <v>20</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>4</v>
@@ -7804,7 +7877,7 @@
         <v>5</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F126" s="4"/>
       <c r="G126" s="4"/>
@@ -7818,16 +7891,16 @@
       <c r="O126" s="4"/>
       <c r="P126" s="4"/>
       <c r="Q126" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="R126" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="R126" s="4" t="s">
-        <v>178</v>
-      </c>
       <c r="S126" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="T126" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="U126" s="4"/>
       <c r="V126" s="4"/>
@@ -7838,7 +7911,7 @@
         <v>20</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>4</v>
@@ -7847,7 +7920,7 @@
         <v>5</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F127" s="4"/>
       <c r="G127" s="4"/>
@@ -7861,16 +7934,16 @@
       <c r="O127" s="4"/>
       <c r="P127" s="4"/>
       <c r="Q127" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="R127" s="4" t="s">
-        <v>187</v>
+        <v>371</v>
       </c>
       <c r="S127" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="T127" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="T127" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="U127" s="4"/>
       <c r="V127" s="4"/>
@@ -7881,7 +7954,7 @@
         <v>20</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>4</v>
@@ -7890,7 +7963,7 @@
         <v>5</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F128" s="4"/>
       <c r="G128" s="4"/>
@@ -7904,16 +7977,16 @@
       <c r="O128" s="4"/>
       <c r="P128" s="4"/>
       <c r="Q128" s="4" t="s">
-        <v>187</v>
+        <v>371</v>
       </c>
       <c r="R128" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="S128" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="T128" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="U128" s="4"/>
       <c r="V128" s="4"/>
@@ -7933,7 +8006,7 @@
         <v>47</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
@@ -7947,16 +8020,16 @@
       <c r="O129" s="4"/>
       <c r="P129" s="4"/>
       <c r="Q129" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="R129" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="S129" s="4" t="s">
-        <v>187</v>
+        <v>371</v>
       </c>
       <c r="T129" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="U129" s="4"/>
       <c r="V129" s="4"/>
@@ -7976,7 +8049,7 @@
         <v>5</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F130" s="4"/>
       <c r="G130" s="4"/>
@@ -7990,16 +8063,16 @@
       <c r="O130" s="4"/>
       <c r="P130" s="4"/>
       <c r="Q130" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="R130" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="S130" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="T130" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="U130" s="4"/>
       <c r="V130" s="4"/>
@@ -8019,7 +8092,7 @@
         <v>5</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F131" s="4"/>
       <c r="G131" s="4"/>
@@ -8033,22 +8106,22 @@
       <c r="O131" s="4"/>
       <c r="P131" s="4"/>
       <c r="Q131" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R131" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S131" s="4" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="T131" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="U131" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="U131" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="V131" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="W131" s="6"/>
     </row>
@@ -8057,7 +8130,7 @@
         <v>24</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>4</v>
@@ -8066,16 +8139,16 @@
         <v>5</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="H132" s="4" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="I132" s="4"/>
       <c r="J132" s="4"/>
@@ -8098,7 +8171,7 @@
         <v>24</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>4</v>
@@ -8107,16 +8180,16 @@
         <v>22</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="H133" s="4" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
@@ -8135,45 +8208,45 @@
       <c r="W133" s="6"/>
     </row>
     <row r="134" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="7"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="7"/>
-      <c r="I134" s="7"/>
-      <c r="J134" s="7"/>
-      <c r="K134" s="7"/>
-      <c r="L134" s="7"/>
-      <c r="M134" s="7"/>
-      <c r="N134" s="7"/>
-      <c r="O134" s="7"/>
-      <c r="P134" s="7"/>
-      <c r="Q134" s="7"/>
-      <c r="R134" s="7"/>
-      <c r="S134" s="7"/>
-      <c r="T134" s="7"/>
-      <c r="U134" s="7"/>
-      <c r="V134" s="7"/>
-      <c r="W134" s="8"/>
+      <c r="A134" s="12"/>
+      <c r="B134" s="12"/>
+      <c r="C134" s="12"/>
+      <c r="D134" s="12"/>
+      <c r="E134" s="12"/>
+      <c r="F134" s="12"/>
+      <c r="G134" s="12"/>
+      <c r="H134" s="12"/>
+      <c r="I134" s="12"/>
+      <c r="J134" s="12"/>
+      <c r="K134" s="12"/>
+      <c r="L134" s="12"/>
+      <c r="M134" s="12"/>
+      <c r="N134" s="12"/>
+      <c r="O134" s="12"/>
+      <c r="P134" s="12"/>
+      <c r="Q134" s="12"/>
+      <c r="R134" s="12"/>
+      <c r="S134" s="12"/>
+      <c r="T134" s="12"/>
+      <c r="U134" s="12"/>
+      <c r="V134" s="12"/>
+      <c r="W134" s="14"/>
     </row>
     <row r="135" spans="1:23" ht="42" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F135" s="4"/>
       <c r="G135" s="4"/>
@@ -8185,10 +8258,10 @@
       <c r="M135" s="4"/>
       <c r="N135" s="4"/>
       <c r="O135" s="4" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="P135" s="4" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="Q135" s="4"/>
       <c r="R135" s="4"/>
@@ -8200,19 +8273,19 @@
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B136" s="14" t="s">
         <v>195</v>
       </c>
+      <c r="B136" s="11" t="s">
+        <v>200</v>
+      </c>
       <c r="C136" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F136" s="4"/>
       <c r="G136" s="4"/>
@@ -8220,10 +8293,10 @@
       <c r="I136" s="4"/>
       <c r="J136" s="4"/>
       <c r="K136" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>206</v>
+        <v>307</v>
       </c>
       <c r="M136" s="4"/>
       <c r="N136" s="4"/>
@@ -8239,19 +8312,19 @@
     </row>
     <row r="137" spans="1:23" ht="42" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B137" s="14" t="s">
-        <v>198</v>
+        <v>195</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>203</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F137" s="4"/>
       <c r="G137" s="4"/>
@@ -8259,10 +8332,10 @@
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
       <c r="K137" s="4" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
@@ -8290,25 +8363,25 @@
         <v>29</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G138" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H138" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="I138" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="J138" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="K138" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="H138" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="I138" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="J138" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="K138" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="L138" s="4"/>
       <c r="M138" s="4"/>
@@ -8337,25 +8410,25 @@
         <v>29</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I139" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J139" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="K139" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="J139" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="K139" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
@@ -8384,7 +8457,7 @@
         <v>33</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F140" s="4"/>
       <c r="G140" s="4"/>
@@ -8395,29 +8468,29 @@
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
       <c r="N140" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="P140" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q140" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="R140" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="S140" s="4" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="T140" s="4"/>
       <c r="U140" s="4" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="V140" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="W140" s="6"/>
     </row>
@@ -8426,7 +8499,7 @@
         <v>15</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>4</v>
@@ -8435,7 +8508,7 @@
         <v>11</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F141" s="4"/>
       <c r="G141" s="4"/>
@@ -8446,22 +8519,22 @@
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
       <c r="N141" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O141" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="P141" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q141" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="R141" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="P141" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q141" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="R141" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="S141" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="T141" s="4"/>
       <c r="U141" s="4"/>
@@ -8473,7 +8546,7 @@
         <v>15</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>4</v>
@@ -8482,7 +8555,7 @@
         <v>16</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F142" s="4"/>
       <c r="G142" s="4"/>
@@ -8493,22 +8566,22 @@
       <c r="L142" s="4"/>
       <c r="M142" s="4"/>
       <c r="N142" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="P142" s="4" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="Q142" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R142" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="S142" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="S142" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="T142" s="4"/>
       <c r="U142" s="4"/>
@@ -8529,7 +8602,7 @@
         <v>16</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F143" s="4"/>
       <c r="G143" s="4"/>
@@ -8540,22 +8613,22 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
       <c r="N143" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P143" s="4" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="Q143" s="4" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
       <c r="R143" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="S143" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="T143" s="4"/>
       <c r="U143" s="4"/>
@@ -8576,7 +8649,7 @@
         <v>18</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F144" s="4"/>
       <c r="G144" s="4"/>
@@ -8587,22 +8660,22 @@
       <c r="L144" s="4"/>
       <c r="M144" s="4"/>
       <c r="N144" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O144" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="P144" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q144" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="R144" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="S144" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="P144" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q144" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="R144" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="S144" s="4" t="s">
-        <v>153</v>
       </c>
       <c r="T144" s="4"/>
       <c r="U144" s="4"/>
@@ -8623,7 +8696,7 @@
         <v>37</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F145" s="4"/>
       <c r="G145" s="4"/>
@@ -8634,29 +8707,29 @@
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
       <c r="N145" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="O145" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="P145" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="P145" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="Q145" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="R145" s="4" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="S145" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="T145" s="4"/>
       <c r="U145" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="V145" s="5" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="W145" s="6"/>
     </row>
@@ -8674,7 +8747,7 @@
         <v>72</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F146" s="4"/>
       <c r="G146" s="4"/>
@@ -8685,29 +8758,29 @@
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
       <c r="N146" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="P146" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q146" s="4" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="R146" s="5" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="S146" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="T146" s="4"/>
       <c r="U146" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="V146" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="W146" s="6"/>
     </row>
@@ -8725,7 +8798,7 @@
         <v>37</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F147" s="4"/>
       <c r="G147" s="4"/>
@@ -8736,22 +8809,22 @@
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
       <c r="N147" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P147" s="4" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="Q147" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R147" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="S147" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="T147" s="4"/>
       <c r="U147" s="4"/>
@@ -8772,7 +8845,7 @@
         <v>37</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F148" s="4"/>
       <c r="G148" s="4"/>
@@ -8783,22 +8856,22 @@
       <c r="L148" s="4"/>
       <c r="M148" s="4"/>
       <c r="N148" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="P148" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q148" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="R148" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="R148" s="4" t="s">
-        <v>159</v>
-      </c>
       <c r="S148" s="4" t="s">
-        <v>165</v>
+        <v>250</v>
       </c>
       <c r="T148" s="4"/>
       <c r="U148" s="4"/>
@@ -8819,28 +8892,28 @@
         <v>11</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="J149" s="4" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="K149" s="4" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="L149" s="5" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
@@ -8868,28 +8941,28 @@
         <v>11</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="F150" s="10" t="s">
-        <v>254</v>
+        <v>378</v>
+      </c>
+      <c r="F150" s="19" t="s">
+        <v>263</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="I150" s="4" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="K150" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
@@ -8917,28 +8990,28 @@
         <v>16</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="I151" s="4" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="K151" s="4" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="L151" s="4" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
@@ -8966,28 +9039,28 @@
         <v>11</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="I152" s="4" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
@@ -9015,28 +9088,28 @@
         <v>11</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="H153" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="J153" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="I153" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="J153" s="4" t="s">
-        <v>364</v>
-      </c>
       <c r="K153" s="4" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="L153" s="4" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
@@ -9054,7 +9127,7 @@
       <c r="A154" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B154" s="12" t="s">
+      <c r="B154" s="8" t="s">
         <v>78</v>
       </c>
       <c r="C154" s="4" t="s">
@@ -9064,34 +9137,34 @@
         <v>79</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F154" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="J154" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K154" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="L154" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="N154" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="O154" s="4" t="s">
         <v>175</v>
-      </c>
-      <c r="G154" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="H154" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="I154" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="J154" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="K154" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="L154" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="N154" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="O154" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="P154" s="4"/>
       <c r="Q154" s="4"/>
@@ -9106,7 +9179,7 @@
       <c r="A155" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B155" s="12" t="s">
+      <c r="B155" s="8" t="s">
         <v>80</v>
       </c>
       <c r="C155" s="4" t="s">
@@ -9116,35 +9189,35 @@
         <v>81</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F155" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="H155" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I155" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="J155" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="K155" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="L155" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="G155" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="H155" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="I155" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J155" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="K155" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="L155" s="4" t="s">
-        <v>170</v>
       </c>
       <c r="M155" s="4"/>
       <c r="N155" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="P155" s="4"/>
       <c r="Q155" s="4"/>
@@ -9160,7 +9233,7 @@
         <v>20</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>4</v>
@@ -9169,7 +9242,7 @@
         <v>52</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F156" s="4"/>
       <c r="G156" s="4"/>
@@ -9180,29 +9253,29 @@
       <c r="L156" s="4"/>
       <c r="M156" s="4"/>
       <c r="N156" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="P156" s="4" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="Q156" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="R156" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="S156" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="T156" s="4"/>
       <c r="U156" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="V156" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="W156" s="6"/>
     </row>
@@ -9220,7 +9293,7 @@
         <v>57</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
@@ -9231,29 +9304,29 @@
       <c r="L157" s="4"/>
       <c r="M157" s="4"/>
       <c r="N157" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="P157" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q157" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="R157" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="Q157" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="R157" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="S157" s="4" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="T157" s="4"/>
       <c r="U157" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="V157" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="W157" s="6"/>
     </row>
@@ -9271,7 +9344,7 @@
         <v>87</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F158" s="4"/>
       <c r="G158" s="4"/>
@@ -9282,22 +9355,22 @@
       <c r="L158" s="4"/>
       <c r="M158" s="4"/>
       <c r="N158" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P158" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q158" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="Q158" s="4" t="s">
-        <v>159</v>
-      </c>
       <c r="R158" s="4" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
       <c r="S158" s="4" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="T158" s="4"/>
       <c r="U158" s="4"/>
@@ -9318,7 +9391,7 @@
         <v>18</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="F159" s="4"/>
       <c r="G159" s="4"/>
@@ -9329,22 +9402,22 @@
       <c r="L159" s="4"/>
       <c r="M159" s="4"/>
       <c r="N159" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O159" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="P159" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="P159" s="4" t="s">
+      <c r="Q159" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="R159" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="S159" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="Q159" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="R159" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="S159" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="T159" s="4"/>
       <c r="U159" s="4"/>
@@ -9353,8 +9426,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:W160" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/2025-2026工程训练_0308.xlsx
+++ b/2025-2026工程训练_0308.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\工作\1实验教学部\排课\ClassSchedule\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hhhyc\Desktop\新建文件夹 (6)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376788A2-03B7-4A15-BA47-454D1493231A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F43AAA7-0BB7-41BB-AD4B-976AA752D4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="550" yWindow="360" windowWidth="36750" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="排课表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排课表!$A$1:$W$177</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="290">
   <si>
     <t>星期</t>
   </si>
@@ -116,318 +130,6 @@
   </si>
   <si>
     <t>新能源汽车工程25(1)</t>
-  </si>
-  <si>
-    <t>新能源汽车工程25(2)</t>
-  </si>
-  <si>
-    <t>智能制造工程25(1)</t>
-  </si>
-  <si>
-    <t>智能制造工程25(2)</t>
-  </si>
-  <si>
-    <t>机械电子工程(创新班)25(1)</t>
-  </si>
-  <si>
-    <t>机械电子工程25(1)</t>
-  </si>
-  <si>
-    <t>机械电子工程25(2)</t>
-  </si>
-  <si>
-    <t>机械电子工程25(3)</t>
-  </si>
-  <si>
-    <t>机械电子工程25(4)</t>
-  </si>
-  <si>
-    <t>机械电子工程25(5)</t>
-  </si>
-  <si>
-    <t>机械电子工程25(6)</t>
-  </si>
-  <si>
-    <t>机械设计制造及其自动化(国际综合1班)</t>
-  </si>
-  <si>
-    <t>机械设计制造及其自动化(国际综合2班)</t>
-  </si>
-  <si>
-    <t>机械设计制造及其自动化25(1)</t>
-  </si>
-  <si>
-    <t>机械设计制造及其自动化25(2)</t>
-  </si>
-  <si>
-    <t>机械设计制造及其自动化25(3)</t>
-  </si>
-  <si>
-    <t>机械设计制造及其自动化25(4)</t>
-  </si>
-  <si>
-    <t>机械设计制造及其自动化25(5)</t>
-  </si>
-  <si>
-    <t>机械设计制造及其自动化25(6)</t>
-  </si>
-  <si>
-    <t>电子信息工程24(1)</t>
-  </si>
-  <si>
-    <t>电子信息工程24(2)</t>
-  </si>
-  <si>
-    <t>电子信息工程24(3)</t>
-  </si>
-  <si>
-    <t>电子信息工程24(4)</t>
-  </si>
-  <si>
-    <t>自动化(创新班)25(1)</t>
-  </si>
-  <si>
-    <t>自动化(卓越工程师班)25(1)</t>
-  </si>
-  <si>
-    <t>自动化25(1)</t>
-  </si>
-  <si>
-    <t>自动化25(2)</t>
-  </si>
-  <si>
-    <t>自动化25(3)</t>
-  </si>
-  <si>
-    <t>自动化25(4)</t>
-  </si>
-  <si>
-    <t>自动化25(5)</t>
-  </si>
-  <si>
-    <t>自动化25(6)</t>
-  </si>
-  <si>
-    <t>周二</t>
-  </si>
-  <si>
-    <t>信息工程24(1)</t>
-  </si>
-  <si>
-    <t>信息工程24(2)</t>
-  </si>
-  <si>
-    <t>电气工程及其自动化25(1)</t>
-  </si>
-  <si>
-    <t>电气工程及其自动化25(2)</t>
-  </si>
-  <si>
-    <t>电气工程及其自动化25(3)</t>
-  </si>
-  <si>
-    <t>电气工程及其自动化25(4)</t>
-  </si>
-  <si>
-    <t>电气工程及其自动化25(5)</t>
-  </si>
-  <si>
-    <t>电气工程及其自动化25(6)</t>
-  </si>
-  <si>
-    <t>食品科学与工程25(1)</t>
-  </si>
-  <si>
-    <t>食品科学与工程25(2)</t>
-  </si>
-  <si>
-    <t>周三</t>
-  </si>
-  <si>
-    <t>工程实践B01</t>
-  </si>
-  <si>
-    <t>工程实践B02</t>
-  </si>
-  <si>
-    <t>工程实践B03</t>
-  </si>
-  <si>
-    <t>工程实践B04</t>
-  </si>
-  <si>
-    <t>工程实践B05</t>
-  </si>
-  <si>
-    <t>工程实践B06</t>
-  </si>
-  <si>
-    <t>工程实践B07</t>
-  </si>
-  <si>
-    <t>工程实践B08</t>
-  </si>
-  <si>
-    <t>工程实践B09</t>
-  </si>
-  <si>
-    <t>工程实践B10</t>
-  </si>
-  <si>
-    <t>工程实践B11</t>
-  </si>
-  <si>
-    <t>工程实践B12</t>
-  </si>
-  <si>
-    <t>工程实践B13</t>
-  </si>
-  <si>
-    <t>工程实践B14</t>
-  </si>
-  <si>
-    <t>工程实践B15</t>
-  </si>
-  <si>
-    <t>工程实践B16</t>
-  </si>
-  <si>
-    <t>工程实践B17</t>
-  </si>
-  <si>
-    <t>工程实践B18</t>
-  </si>
-  <si>
-    <t>工程实践B19</t>
-  </si>
-  <si>
-    <t>工程实践C01</t>
-  </si>
-  <si>
-    <t>工程实践C02</t>
-  </si>
-  <si>
-    <t>工程实践C03</t>
-  </si>
-  <si>
-    <t>工程实践C04</t>
-  </si>
-  <si>
-    <t>工程实践C05</t>
-  </si>
-  <si>
-    <t>工程实践C06</t>
-  </si>
-  <si>
-    <t>工程实践C07</t>
-  </si>
-  <si>
-    <t>工程实践C08</t>
-  </si>
-  <si>
-    <t>工程实践C09</t>
-  </si>
-  <si>
-    <t>工程实践C10</t>
-  </si>
-  <si>
-    <t>工程实践C11</t>
-  </si>
-  <si>
-    <t>信息工程(卓越工程师班)24(1)</t>
-  </si>
-  <si>
-    <t>土木工程(创新班)24(1)</t>
-  </si>
-  <si>
-    <t>新能源材料与器件24(1)</t>
-  </si>
-  <si>
-    <t>新能源材料与器件24(2)</t>
-  </si>
-  <si>
-    <t>电气工程及其自动化(国际班)25(1)</t>
-  </si>
-  <si>
-    <t>电气工程及其自动化(国际班)25(2)</t>
-  </si>
-  <si>
-    <t>通信工程24(1)</t>
-  </si>
-  <si>
-    <t>通信工程24(2)</t>
-  </si>
-  <si>
-    <t>周四</t>
-  </si>
-  <si>
-    <t>信息工程24(3)</t>
-  </si>
-  <si>
-    <t>信息工程24(4)</t>
-  </si>
-  <si>
-    <t>智能感知工程25(1)</t>
-  </si>
-  <si>
-    <t>智能感知工程25(2)</t>
-  </si>
-  <si>
-    <t>材料成型及控制工程(卓越工程师班)25(1)</t>
-  </si>
-  <si>
-    <t>材料成型及控制工程25(1)</t>
-  </si>
-  <si>
-    <t>材料成型及控制工程25(2)</t>
-  </si>
-  <si>
-    <t>给排水科学与工程25(1)</t>
-  </si>
-  <si>
-    <t>通信工程24(3)</t>
-  </si>
-  <si>
-    <t>通信工程24(4)</t>
-  </si>
-  <si>
-    <t>金属材料工程25(1)</t>
-  </si>
-  <si>
-    <t>金属材料工程25(2)</t>
-  </si>
-  <si>
-    <t>周五</t>
-  </si>
-  <si>
-    <t>理论1-4</t>
-  </si>
-  <si>
-    <t>车1-4</t>
-  </si>
-  <si>
-    <t>先t1-4</t>
-  </si>
-  <si>
-    <t>数x1-4</t>
-  </si>
-  <si>
-    <t>铸1-4</t>
-  </si>
-  <si>
-    <t>先d1-4</t>
-  </si>
-  <si>
-    <t>焊1-4</t>
-  </si>
-  <si>
-    <t>钳1-4</t>
-  </si>
-  <si>
-    <t>数c1-4</t>
-  </si>
-  <si>
-    <t>铣1-4</t>
   </si>
   <si>
     <t>理论1-4
@@ -445,6 +147,9 @@
 B焊5-7</t>
   </si>
   <si>
+    <t>新能源汽车工程25(2)</t>
+  </si>
+  <si>
     <t>理论1-4
 A产5-7
 B智5-7</t>
@@ -462,6 +167,9 @@
 A热5-7</t>
   </si>
   <si>
+    <t>智能制造工程25(1)</t>
+  </si>
+  <si>
     <t>理论1-4
 A压5-7
 B焊5-7</t>
@@ -477,6 +185,9 @@
 B五5-7</t>
   </si>
   <si>
+    <t>智能制造工程25(2)</t>
+  </si>
+  <si>
     <t>理论1-4
 A激5-7
 B热5-7</t>
@@ -492,13 +203,14 @@
 B智5-7</t>
   </si>
   <si>
+    <t>机械电子工程(创新班)25(1)</t>
+  </si>
+  <si>
     <t>铸1-4
 铸5-7</t>
   </si>
   <si>
-    <t>理论1-4
-A超5-7
-B齿5-7</t>
+    <t>机械电子工程25(1)</t>
   </si>
   <si>
     <t>A压1-4
@@ -507,6 +219,9 @@
 B机5-7</t>
   </si>
   <si>
+    <t>机械电子工程25(2)</t>
+  </si>
+  <si>
     <t>数x1-4
 数x5-7</t>
   </si>
@@ -517,6 +232,9 @@
 B五5-7</t>
   </si>
   <si>
+    <t>机械电子工程25(3)</t>
+  </si>
+  <si>
     <t>理论1-4
 A装5-7
 B五5-7</t>
@@ -524,6 +242,17 @@
   <si>
     <t>先t1-4
 先t5-7</t>
+  </si>
+  <si>
+    <t>A柔1-4
+B机1-4
+A超5-6'
+B齿5-6'
+B超6'-7
+A齿6'-7</t>
+  </si>
+  <si>
+    <t>机械电子工程25(4)</t>
   </si>
   <si>
     <t>数c1-4
@@ -536,7 +265,16 @@
 B焊5-7</t>
   </si>
   <si>
-    <t>机械电子工程项目5-7</t>
+    <t>机械电子工程25(5)</t>
+  </si>
+  <si>
+    <t>理论1-4</t>
+  </si>
+  <si>
+    <t>铣m5-7</t>
+  </si>
+  <si>
+    <t>机械电子工程25(6)</t>
   </si>
   <si>
     <t>A产1-4
@@ -557,20 +295,45 @@
 B智5-7</t>
   </si>
   <si>
+    <t>机械设计制造及其自动化25(1)</t>
+  </si>
+  <si>
     <t>A压1-4
 B焊1-4
 B装5-7
 A五5-7</t>
   </si>
   <si>
+    <t>机械设计制造及其自动化25(2)</t>
+  </si>
+  <si>
     <t>B激1-4
 A热1-4
 B柔5-7
 A机5-7</t>
   </si>
   <si>
-    <t>机械设计制造及其自动化项目1-4
+    <t>机械设计制造及其自动化25(3)</t>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化25(4)</t>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化25(5)</t>
+  </si>
+  <si>
+    <t>铣m1-4
 机械设计制造及其自动化项目5-7</t>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化25(6)</t>
+  </si>
+  <si>
+    <t>理论1-4
+A超5-6'
+B齿5-6'
+B超6'-7
+A齿6'-7</t>
   </si>
   <si>
     <t>A柔1-4
@@ -579,10 +342,22 @@
 B热5-7</t>
   </si>
   <si>
+    <t>电子信息工程24(1)</t>
+  </si>
+  <si>
     <t>理论5-7</t>
   </si>
   <si>
-    <t>铣5-7</t>
+    <t>A智5-6'
+B压5-6'
+B智6'-7
+A压6'-7</t>
+  </si>
+  <si>
+    <t>A柔5-6'
+B超5-6'
+B柔6'-7
+A超6'-7</t>
   </si>
   <si>
     <t>焊5-7</t>
@@ -597,16 +372,106 @@
     <t>钳5-7</t>
   </si>
   <si>
+    <t>电子信息工程24(2)</t>
+  </si>
+  <si>
+    <t>电子信息工程24(3)</t>
+  </si>
+  <si>
+    <t>车1-4</t>
+  </si>
+  <si>
+    <t>A产1-2
+B机1-2
+B产3-4
+A机3-4</t>
+  </si>
+  <si>
+    <t>先t1-4</t>
+  </si>
+  <si>
+    <t>数x1-4</t>
+  </si>
+  <si>
+    <t>铸1-4</t>
+  </si>
+  <si>
+    <t>电子信息工程24(4)</t>
+  </si>
+  <si>
+    <t>自动化(创新班)25(1)</t>
+  </si>
+  <si>
     <t>车5-7</t>
   </si>
   <si>
     <t>数x5-7</t>
   </si>
   <si>
+    <t>A柔5-6'
+B齿5-6'
+B柔6'-7
+A齿6'-7</t>
+  </si>
+  <si>
+    <t>A产5-6'
+B机5-6'
+B产6'-7
+A机6'-7</t>
+  </si>
+  <si>
     <t>铸5-7</t>
   </si>
   <si>
     <t>先t5-7</t>
+  </si>
+  <si>
+    <t>自动化(卓越工程师班)25(1)</t>
+  </si>
+  <si>
+    <t>自动化25(1)</t>
+  </si>
+  <si>
+    <t>自动化25(2)</t>
+  </si>
+  <si>
+    <t>自动化25(3)</t>
+  </si>
+  <si>
+    <t>自动化25(4)</t>
+  </si>
+  <si>
+    <t>自动化25(5)</t>
+  </si>
+  <si>
+    <t>自动化25(6)</t>
+  </si>
+  <si>
+    <t>周二</t>
+  </si>
+  <si>
+    <t>信息工程24(1)</t>
+  </si>
+  <si>
+    <t>先d1-4</t>
+  </si>
+  <si>
+    <t>A智1-2
+B压1-2
+B智3-4
+A压3-4</t>
+  </si>
+  <si>
+    <t>焊1-4</t>
+  </si>
+  <si>
+    <t>钳1-4</t>
+  </si>
+  <si>
+    <t>数c1-4</t>
+  </si>
+  <si>
+    <t>信息工程24(2)</t>
   </si>
   <si>
     <t>A激1-4
@@ -650,397 +515,11 @@
 A机5-7</t>
   </si>
   <si>
-    <t>B装1-4
-A五1-4
-钳5-7</t>
-  </si>
-  <si>
-    <t>A柔1-4
-B机1-4
-铣m5-7</t>
-  </si>
-  <si>
-    <t>A产1-4
-B智1-4
-B压5-7
-A焊5-7</t>
-  </si>
-  <si>
-    <t>A柔1-4
-B机1-4
-B装5-7
-A五5-7</t>
-  </si>
-  <si>
-    <t>A产1-4
-B柔1-4
-B产5-7
-A柔5-7</t>
-  </si>
-  <si>
-    <t>A智1-4
-B先d1-4
-B智5-7
-A先d5-7</t>
-  </si>
-  <si>
-    <t>A齿1-4
-B智1-4
-B齿5-7
-A智5-7</t>
-  </si>
-  <si>
-    <t>A机1-4
-B超1-4
-B机5-7
-A超5-7</t>
-  </si>
-  <si>
-    <t>理论1-4
-A智5-7
-B产5-7</t>
-  </si>
-  <si>
-    <t>铸1-4
-铣5-7</t>
-  </si>
-  <si>
-    <t>B智1-4
-A产1-4
-数x5-7</t>
-  </si>
-  <si>
-    <t>车1-4
-焊5-7</t>
-  </si>
-  <si>
-    <t>钳1-4
-先t5-7</t>
-  </si>
-  <si>
-    <t>理论1-4
-A柔5-7
-B压5-7</t>
-  </si>
-  <si>
-    <t>先d1-4
-焊5-7</t>
-  </si>
-  <si>
-    <t>B柔1-4
-A压1-4
-先t5-7</t>
-  </si>
-  <si>
-    <t>数c1-4
-钳5-7</t>
-  </si>
-  <si>
-    <t>铸1-4
-数x5-7</t>
-  </si>
-  <si>
-    <t>A装1-4
-B五1-4
-B装5-7
-A五5-7</t>
-  </si>
-  <si>
-    <t>车1-4
-B激5-7
-A热5-7</t>
-  </si>
-  <si>
-    <t>B压1-4
-A焊1-4
-B装5-7
-A五5-7</t>
-  </si>
-  <si>
-    <t>B激1-4
-A热1-4
-铣m5-7</t>
-  </si>
-  <si>
-    <t>铣m1-4
-智能制造工程项目5-7</t>
-  </si>
-  <si>
-    <t>B压1-4
-A焊1-4
-钳5-7</t>
-  </si>
-  <si>
-    <t>A压1-4
-B焊1-4
-B压5-7
-A焊5-7</t>
-  </si>
-  <si>
-    <t>钳1-4
-A激5-7
-B热5-7</t>
-  </si>
-  <si>
-    <t>B装1-4
-A五1-4
-机械电子工程项目5-7</t>
-  </si>
-  <si>
     <t>机械电子工程项目1-4
-A压5-7
-B焊5-7</t>
-  </si>
-  <si>
-    <t>B激1-4
-A热1-4
-机械电子工程项目5-7</t>
-  </si>
-  <si>
-    <t>机械电子工程项目1-4
-机械电子工程项目5-7</t>
-  </si>
-  <si>
-    <t>铣m1-4
-A柔5-7
-B机5-7</t>
-  </si>
-  <si>
-    <t>B柔1-4
-A机1-4
-B产5-7
-A智5-7</t>
-  </si>
-  <si>
-    <t>理论1-4
-先d5-7</t>
-  </si>
-  <si>
-    <t>焊1-4
-数c5-7</t>
-  </si>
-  <si>
-    <t>焊1-4
-先d5-7</t>
-  </si>
-  <si>
-    <t>铣m1-4
-A产5-7
-B智5-7</t>
-  </si>
-  <si>
-    <t>B产1-4
-A智1-4
-新能源汽车工程项目5-7</t>
-  </si>
-  <si>
-    <t>车1-4
-新能源汽车工程项目5-7</t>
-  </si>
-  <si>
-    <t>智能制造工程项目1-4
-智能制造工程项目5-7</t>
-  </si>
-  <si>
-    <t>B激1-4
-A热1-4
-A压5-7
-B焊5-7</t>
-  </si>
-  <si>
-    <t>B柔1-4
-A机1-4
-智能制造工程项目5-7</t>
-  </si>
-  <si>
-    <t>A智5-7
-B产5-7</t>
-  </si>
-  <si>
-    <t>B柔5-7
-A压5-7</t>
-  </si>
-  <si>
-    <t>A机5-7
-B齿5-7</t>
-  </si>
-  <si>
-    <t>B机5-7
-A齿5-7</t>
-  </si>
-  <si>
-    <t>B智5-7
-A产5-7</t>
-  </si>
-  <si>
-    <t>B压1-4
-A焊1-4
-机械电子工程创新项目5-7</t>
-  </si>
-  <si>
-    <t>B柔1-4
-A机1-4
-B压5-7
-A焊5-7</t>
-  </si>
-  <si>
-    <t>B柔1-4
-A机1-4
-A产5-7
-B智5-7</t>
-  </si>
-  <si>
-    <t>B激1-4
-A热1-4
-A柔5-7
-B机5-7</t>
-  </si>
-  <si>
-    <t>B产1-4
-A智1-4
-A装5-7
-B五5-7</t>
-  </si>
-  <si>
-    <t>B柔1-4
-A机1-4
-数c5-7</t>
-  </si>
-  <si>
-    <t>B柔1-4
-A机1-4
-机械设计制造及其自动化项目5-7</t>
-  </si>
-  <si>
-    <t>A装1-4
-B五1-4
-A柔5-7
-B机5-7</t>
-  </si>
-  <si>
-    <t>B产1-4
-A智1-4
-A压5-7
-B激5-7</t>
-  </si>
-  <si>
-    <t>焊1-4
-A热5-7
-B齿5-7</t>
-  </si>
-  <si>
-    <t>铣m1-4
-焊5-7</t>
-  </si>
-  <si>
-    <t>B产1-4
-A智1-4
-钳5-7</t>
-  </si>
-  <si>
-    <t>A压1-4
-B激1-4
-B压5-7
-A激5-7</t>
-  </si>
-  <si>
-    <t>B热1-4
-A齿1-4
-B柔5-7
-A机5-7</t>
-  </si>
-  <si>
-    <t>新能源汽车工程项目1-4
-新能源汽车工程项目5-7</t>
-  </si>
-  <si>
-    <t>A柔5-7
-B压5-7</t>
-  </si>
-  <si>
-    <t>机械电子工程创新项目1-4
-机械电子工程创新项目5-7</t>
-  </si>
-  <si>
-    <t>A装1-4
-B五1-4
-B超5-7
-A齿5-7</t>
-  </si>
-  <si>
-    <t>数c1-4
-先d5-7</t>
-  </si>
-  <si>
-    <t>A超1-4
-B齿1-4
-B产5-7
-A智5-7</t>
-  </si>
-  <si>
-    <t>先d1-4
-数c5-7</t>
-  </si>
-  <si>
-    <t>A压1-4
-B焊1-4
-A激5-7
-B热5-7</t>
-  </si>
-  <si>
-    <t>机械设计制造及其自动化国际综合项目1-4
-机械设计制造及其自动化国际综合项目5-7</t>
-  </si>
-  <si>
-    <t>A装1-4
-B五1-4
-B柔5-7
-A机5-7</t>
-  </si>
-  <si>
-    <t>B柔1-4
-A机1-4
-A装5-7
-B五5-7</t>
-  </si>
-  <si>
-    <t>B热1-4
-A齿1-4
-B压5-7
-A激5-7</t>
-  </si>
-  <si>
-    <t>理论1-4
-A热5-7
-B齿5-7</t>
-  </si>
-  <si>
-    <t>B热1-4
-A齿1-4
-A产5-7
-B智5-7</t>
-  </si>
-  <si>
-    <t>理论1-4
-铣m5-7</t>
-  </si>
-  <si>
-    <t>A柔1-4
-B机1-4
-A热5-7
-B齿5-7</t>
-  </si>
-  <si>
-    <t>A产1-2
-B机1-2
-B产3-4
-A机3-4</t>
-  </si>
-  <si>
-    <t>A智1-2
-B压1-2
-B智3-4
-A压3-4</t>
+A超5-6'
+B齿5-6'
+B超6'-7
+A齿6'-7</t>
   </si>
   <si>
     <t>A超1-2
@@ -1051,6 +530,318 @@
 A焊5-7</t>
   </si>
   <si>
+    <t>机械设计制造及其自动化(国际综合1班)</t>
+  </si>
+  <si>
+    <t>B装1-4
+A五1-4
+钳5-7</t>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化(国际综合2班)</t>
+  </si>
+  <si>
+    <t>A柔1-4
+B机1-4
+铣m5-7</t>
+  </si>
+  <si>
+    <t>A产1-4
+B智1-4
+B压5-7
+A焊5-7</t>
+  </si>
+  <si>
+    <t>B装1-4
+A五1-4
+A超5-6'
+B齿5-6'
+B超6'-7
+A齿6'-7</t>
+  </si>
+  <si>
+    <t>A柔1-4
+B机1-4
+B装5-7
+A五5-7</t>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化项目1-4
+机械设计制造及其自动化项目5-7</t>
+  </si>
+  <si>
+    <t>电气工程及其自动化25(1)</t>
+  </si>
+  <si>
+    <t>电气工程及其自动化25(2)</t>
+  </si>
+  <si>
+    <t>电气工程及其自动化25(3)</t>
+  </si>
+  <si>
+    <t>电气工程及其自动化25(4)</t>
+  </si>
+  <si>
+    <t>电气工程及其自动化25(5)</t>
+  </si>
+  <si>
+    <t>电气工程及其自动化25(6)</t>
+  </si>
+  <si>
+    <t>食品科学与工程25(1)</t>
+  </si>
+  <si>
+    <t>食品科学与工程25(2)</t>
+  </si>
+  <si>
+    <t>周三</t>
+  </si>
+  <si>
+    <t>工程实践B01</t>
+  </si>
+  <si>
+    <t>A产1-4
+B柔1-4
+B产5-7
+A柔5-7</t>
+  </si>
+  <si>
+    <t>工程实践B02</t>
+  </si>
+  <si>
+    <t>工程实践B03</t>
+  </si>
+  <si>
+    <t>工程实践B04</t>
+  </si>
+  <si>
+    <t>工程实践B05</t>
+  </si>
+  <si>
+    <t>工程实践B06</t>
+  </si>
+  <si>
+    <t>工程实践B07</t>
+  </si>
+  <si>
+    <t>工程实践B08</t>
+  </si>
+  <si>
+    <t>工程实践B09</t>
+  </si>
+  <si>
+    <t>工程实践B10</t>
+  </si>
+  <si>
+    <t>工程实践B11</t>
+  </si>
+  <si>
+    <t>工程实践B12</t>
+  </si>
+  <si>
+    <t>工程实践B13</t>
+  </si>
+  <si>
+    <t>工程实践B14</t>
+  </si>
+  <si>
+    <t>A智1-4
+B先d1-4
+B智5-7
+A先d5-7</t>
+  </si>
+  <si>
+    <t>工程实践B15</t>
+  </si>
+  <si>
+    <t>工程实践B16</t>
+  </si>
+  <si>
+    <t>工程实践B17</t>
+  </si>
+  <si>
+    <t>工程实践B18</t>
+  </si>
+  <si>
+    <t>工程实践B19</t>
+  </si>
+  <si>
+    <t>工程实践C01</t>
+  </si>
+  <si>
+    <t>A齿1-4
+B智1-4
+B齿5-7
+A智5-7</t>
+  </si>
+  <si>
+    <t>工程实践C02</t>
+  </si>
+  <si>
+    <t>工程实践C03</t>
+  </si>
+  <si>
+    <t>工程实践C04</t>
+  </si>
+  <si>
+    <t>工程实践C05</t>
+  </si>
+  <si>
+    <t>工程实践C06</t>
+  </si>
+  <si>
+    <t>A机1-4
+B超1-4
+B机5-7
+A超5-7</t>
+  </si>
+  <si>
+    <t>工程实践C07</t>
+  </si>
+  <si>
+    <t>工程实践C08</t>
+  </si>
+  <si>
+    <t>工程实践C09</t>
+  </si>
+  <si>
+    <t>工程实践C10</t>
+  </si>
+  <si>
+    <t>工程实践C11</t>
+  </si>
+  <si>
+    <t>信息工程(卓越工程师班)24(1)</t>
+  </si>
+  <si>
+    <t>土木工程(创新班)24(1)</t>
+  </si>
+  <si>
+    <t>新能源材料与器件24(1)</t>
+  </si>
+  <si>
+    <t>理论1-4
+A智5-7
+B产5-7</t>
+  </si>
+  <si>
+    <t>车1-4
+焊5-7</t>
+  </si>
+  <si>
+    <t>钳1-4
+先t5-7</t>
+  </si>
+  <si>
+    <t>新能源材料与器件24(2)</t>
+  </si>
+  <si>
+    <t>理论1-4
+A柔5-7
+B压5-7</t>
+  </si>
+  <si>
+    <t>先d1-4
+焊5-7</t>
+  </si>
+  <si>
+    <t>B柔1-4
+A压1-4
+先t5-7</t>
+  </si>
+  <si>
+    <t>数c1-4
+钳5-7</t>
+  </si>
+  <si>
+    <t>铸1-4
+数x5-7</t>
+  </si>
+  <si>
+    <t>铣m1-4</t>
+  </si>
+  <si>
+    <t>A装1-4
+B五1-4
+B装5-7
+A五5-7</t>
+  </si>
+  <si>
+    <t>车1-4
+B激5-7
+A热5-7</t>
+  </si>
+  <si>
+    <t>B压1-4
+A焊1-4
+B装5-7
+A五5-7</t>
+  </si>
+  <si>
+    <t>B激1-4
+A热1-4
+铣m5-7</t>
+  </si>
+  <si>
+    <t>铣m1-4
+智能制造工程项目5-7</t>
+  </si>
+  <si>
+    <t>B压1-4
+A焊1-4
+钳5-7</t>
+  </si>
+  <si>
+    <t>A压1-4
+B焊1-4
+B压5-7
+A焊5-7</t>
+  </si>
+  <si>
+    <t>钳1-4
+A激5-7
+B热5-7</t>
+  </si>
+  <si>
+    <t>B装1-4
+A五1-4
+机械电子工程项目5-7</t>
+  </si>
+  <si>
+    <t>铣m1-4
+A压5-7
+B焊5-7</t>
+  </si>
+  <si>
+    <t>机械电子工程项目1-4
+机械电子工程项目5-7</t>
+  </si>
+  <si>
+    <t>铣m1-4
+A柔5-7
+B机5-7</t>
+  </si>
+  <si>
+    <t>B柔1-4
+A机1-4
+B产5-7
+A智5-7</t>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化项目1-4
+铣m5-7</t>
+  </si>
+  <si>
+    <t>缺失</t>
+  </si>
+  <si>
+    <t>电气工程及其自动化(国际班)25(1)</t>
+  </si>
+  <si>
+    <t>理论1-4
+先d5-7</t>
+  </si>
+  <si>
     <t>A智1-2
 B压1-2
 B智3-4
@@ -1058,11 +849,132 @@
 钳5-7</t>
   </si>
   <si>
+    <t>焊1-4
+数c5-7</t>
+  </si>
+  <si>
+    <t>电气工程及其自动化(国际班)25(2)</t>
+  </si>
+  <si>
+    <t>理论1-4
+A智5-6'
+B压5-6'
+B智6'-7
+A压6'-7</t>
+  </si>
+  <si>
+    <t>焊1-4
+先d5-7</t>
+  </si>
+  <si>
+    <t>通信工程24(1)</t>
+  </si>
+  <si>
+    <t>通信工程24(2)</t>
+  </si>
+  <si>
+    <t>周四</t>
+  </si>
+  <si>
+    <t>信息工程24(3)</t>
+  </si>
+  <si>
+    <t>信息工程24(4)</t>
+  </si>
+  <si>
+    <t>铣m1-4
+A产5-7
+B智5-7</t>
+  </si>
+  <si>
+    <t>B产1-4
+A智1-4
+新能源汽车工程项目5-7</t>
+  </si>
+  <si>
+    <t>车1-4
+新能源汽车工程项目5-7</t>
+  </si>
+  <si>
+    <t>智能制造工程项目1-4
+智能制造工程项目5-7</t>
+  </si>
+  <si>
+    <t>B激1-4
+A热1-4
+A压5-7
+B焊5-7</t>
+  </si>
+  <si>
+    <t>B柔1-4
+A机1-4
+智能制造工程项目5-7</t>
+  </si>
+  <si>
+    <t>智能感知工程25(1)</t>
+  </si>
+  <si>
+    <t>A智5-7
+B产5-7</t>
+  </si>
+  <si>
+    <t>B柔5-7
+A压5-7</t>
+  </si>
+  <si>
+    <t>A机5-7
+B齿5-7</t>
+  </si>
+  <si>
+    <t>智能感知工程25(2)</t>
+  </si>
+  <si>
+    <t>B机5-7
+A齿5-7</t>
+  </si>
+  <si>
+    <t>B智5-7
+A产5-7</t>
+  </si>
+  <si>
+    <t>B柔1-4
+A机1-4
+B压5-7
+A焊5-7</t>
+  </si>
+  <si>
+    <t>B柔1-4
+A机1-4
+A产5-7
+B智5-7</t>
+  </si>
+  <si>
     <t>A超1-2
 B齿1-2
 B超3-4
 A齿3-4
 机械电子工程项目5-7</t>
+  </si>
+  <si>
+    <t>B激1-4
+A热1-4
+A柔5-7
+B机5-7</t>
+  </si>
+  <si>
+    <t>铣m1-4
+机械电子工程项目5-7</t>
+  </si>
+  <si>
+    <t>B产1-4
+A智1-4
+A装5-7
+B五5-7</t>
+  </si>
+  <si>
+    <t>B柔1-4
+A机1-4
+数c5-7</t>
   </si>
   <si>
     <t>A超1-2
@@ -1073,86 +985,6 @@
 A智5-7</t>
   </si>
   <si>
-    <t>A柔1-2
-B压1-2
-B柔3-4
-A压3-4</t>
-  </si>
-  <si>
-    <t>A智1-2
-B产1-2
-B智3-4
-A产3-4</t>
-  </si>
-  <si>
-    <t>A超1-2
-B齿1-2
-B超3-4
-A齿3-4
-机械设计制造及其自动化项目5-7</t>
-  </si>
-  <si>
-    <t>A柔1-4
-B机1-4
-A超5-6'
-B齿5-6'
-B超6'-7
-A齿6'-7</t>
-  </si>
-  <si>
-    <t>理论1-4
-A超5-6'
-B齿5-6'
-B超6'-7
-A齿6'-7</t>
-  </si>
-  <si>
-    <t>A智5-6'
-B压5-6'
-B智6'-7
-A压6'-7</t>
-  </si>
-  <si>
-    <t>A柔5-6'
-B超5-6'
-B柔6'-7
-A超6'-7</t>
-  </si>
-  <si>
-    <t>A柔5-6'
-B齿5-6'
-B柔6'-7
-A齿6'-7</t>
-  </si>
-  <si>
-    <t>A产5-6'
-B机5-6'
-B产6'-7
-A机6'-7</t>
-  </si>
-  <si>
-    <t>机械电子工程项目1-4
-A超5-6'
-B齿5-6'
-B超6'-7
-A齿6'-7</t>
-  </si>
-  <si>
-    <t>B装1-4
-A五1-4
-A超5-6'
-B齿5-6'
-B超6'-7
-A齿6'-7</t>
-  </si>
-  <si>
-    <t>理论1-4
-A智5-6'
-B压5-6'
-B智6'-7
-A压6'-7</t>
-  </si>
-  <si>
     <t>B产1-4
 A智1-4
 A超5-6'
@@ -1160,17 +992,309 @@
 B超6'-7
 A齿6'-7</t>
   </si>
+  <si>
+    <t>B柔1-4
+A机1-4
+铣m5-7</t>
+  </si>
+  <si>
+    <t>A装1-4
+B五1-4
+A柔5-7
+B机5-7</t>
+  </si>
+  <si>
+    <t>材料成型及控制工程(卓越工程师班)25(1)</t>
+  </si>
+  <si>
+    <t>B产1-4
+A智1-4
+A压5-7
+B激5-7</t>
+  </si>
+  <si>
+    <t>焊1-4
+A热5-7
+B齿5-7</t>
+  </si>
+  <si>
+    <t>铣m1-4
+焊5-7</t>
+  </si>
+  <si>
+    <t>材料成型及控制工程25(1)</t>
+  </si>
+  <si>
+    <t>B产1-4
+A智1-4
+钳5-7</t>
+  </si>
+  <si>
+    <t>A压1-4
+B激1-4
+B压5-7
+A激5-7</t>
+  </si>
+  <si>
+    <t>材料成型及控制工程25(2)</t>
+  </si>
+  <si>
+    <t>B热1-4
+A齿1-4
+B柔5-7
+A机5-7</t>
+  </si>
+  <si>
+    <t>给排水科学与工程25(1)</t>
+  </si>
+  <si>
+    <t>通信工程24(3)</t>
+  </si>
+  <si>
+    <t>通信工程24(4)</t>
+  </si>
+  <si>
+    <t>金属材料工程25(1)</t>
+  </si>
+  <si>
+    <t>A柔1-2
+B压1-2
+B柔3-4
+A压3-4</t>
+  </si>
+  <si>
+    <t>金属材料工程25(2)</t>
+  </si>
+  <si>
+    <t>A智1-2
+B产1-2
+B智3-4
+A产3-4</t>
+  </si>
+  <si>
+    <t>周五</t>
+  </si>
+  <si>
+    <t>新能源汽车工程项目1-4
+新能源汽车工程项目5-7</t>
+  </si>
+  <si>
+    <t>A柔5-7
+B压5-7</t>
+  </si>
+  <si>
+    <t>A装1-4
+B五1-4
+B超5-7
+A齿5-7</t>
+  </si>
+  <si>
+    <t>数c1-4
+先d5-7</t>
+  </si>
+  <si>
+    <t>A超1-4
+B齿1-4
+B产5-7
+A智5-7</t>
+  </si>
+  <si>
+    <t>先d1-4
+数c5-7</t>
+  </si>
+  <si>
+    <t>A压1-4
+B焊1-4
+A激5-7
+B热5-7</t>
+  </si>
+  <si>
+    <t>A装1-4
+B五1-4
+B柔5-7
+A机5-7</t>
+  </si>
+  <si>
+    <t>B柔1-4
+A机1-4
+A装5-7
+B五5-7</t>
+  </si>
+  <si>
+    <t>B热1-4
+A齿1-4
+B压5-7
+A激5-7</t>
+  </si>
+  <si>
+    <t>理论1-4
+A热5-7
+B齿5-7</t>
+  </si>
+  <si>
+    <t>B热1-4
+A齿1-4
+A产5-7
+B智5-7</t>
+  </si>
+  <si>
+    <t>理论1-4
+铣m5-7</t>
+  </si>
+  <si>
+    <t>A柔1-4
+B机1-4
+A热5-7
+B齿5-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B压1-4
+A焊1-4
+A压5-7
+B焊5-7 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>专题项目1-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A激1-4
+B热1-4
+B激5-7
+A热5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A产1-4
+B智1-4
+B产5-7
+A智5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>先t1-4
+先t5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>铸1-4
+铸5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>理论1-4
+A超5-7
+B齿5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>先d1-4
+先d5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B柔1-4
+A机1-4
+A压5-7
+B焊5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A柔1-4
+B机1-4
+B柔5-7
+A机5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>数c1-4
+数c5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化项目1-4
+机械设计制造及其自动化项目5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A超1-2
+B齿1-2
+B超3-4
+A齿3-4
+机械设计制造及其自动化项目5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化(国际综合1班)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化(国际综合2班)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>先d1-4
+钳5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>钳1-4
+先d5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>理论1-4
+智能制造工程项目5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>智能制造工程项目1-4
+A压5-7
+B焊5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>智能制造工程项目1-4
+A激5-7
+B热5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>焊5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B智5-7
+A产5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>铣m1-4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>铸1-4
+先d5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B智1-4
+A产1-4
+数x5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1193,13 +1317,33 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1214,7 +1358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1222,7 +1366,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1528,7 +1693,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X177"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1626,13 +1791,13 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
@@ -1649,7 +1814,7 @@
         <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1662,13 +1827,13 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
@@ -1685,7 +1850,7 @@
         <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1697,14 +1862,14 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="1" t="s">
-        <v>135</v>
+      <c r="M4" s="5" t="s">
+        <v>282</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -1721,7 +1886,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1733,14 +1898,14 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="1" t="s">
-        <v>138</v>
+      <c r="M5" s="5" t="s">
+        <v>282</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -1752,36 +1917,38 @@
       <c r="W5" s="1"/>
       <c r="X5" s="2"/>
     </row>
-    <row r="6" spans="1:24" ht="56" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:24" ht="42" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="U6" s="1"/>
+      <c r="B6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>266</v>
+      </c>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="2"/>
@@ -1791,7 +1958,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -1809,14 +1976,14 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="1" t="s">
-        <v>142</v>
+      <c r="S7" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -1827,7 +1994,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -1846,13 +2013,13 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
@@ -1863,7 +2030,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -1882,13 +2049,13 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>147</v>
+        <v>48</v>
+      </c>
+      <c r="T9" s="5" t="s">
+        <v>269</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>260</v>
+        <v>50</v>
       </c>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
@@ -1899,7 +2066,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -1918,13 +2085,13 @@
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
@@ -1935,7 +2102,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -1954,13 +2121,13 @@
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
@@ -1971,7 +2138,7 @@
         <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -1990,13 +2157,13 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>130</v>
+        <v>37</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>272</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
@@ -2006,17 +2173,17 @@
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
+      <c r="B13" s="5" t="s">
+        <v>278</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -2042,17 +2209,17 @@
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
+      <c r="B14" s="5" t="s">
+        <v>279</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -2079,7 +2246,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -2095,13 +2262,13 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -2115,7 +2282,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2131,13 +2298,13 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1" t="s">
-        <v>135</v>
+        <v>33</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -2151,7 +2318,7 @@
         <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -2167,13 +2334,13 @@
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1" t="s">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>149</v>
+        <v>53</v>
       </c>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -2187,7 +2354,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -2203,13 +2370,13 @@
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
@@ -2218,12 +2385,12 @@
       <c r="W18" s="1"/>
       <c r="X18" s="2"/>
     </row>
-    <row r="19" spans="1:24" ht="70" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -2239,13 +2406,13 @@
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -2259,7 +2426,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -2275,13 +2442,13 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1" t="s">
-        <v>261</v>
+        <v>70</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>157</v>
+        <v>71</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
@@ -2295,36 +2462,36 @@
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -2341,36 +2508,36 @@
         <v>23</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -2387,7 +2554,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -2397,23 +2564,23 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -2429,7 +2596,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -2439,23 +2606,23 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -2471,32 +2638,32 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>264</v>
+        <v>91</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>265</v>
+        <v>92</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2517,7 +2684,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -2527,22 +2694,22 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -2559,26 +2726,26 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2601,26 +2768,26 @@
         <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2643,32 +2810,32 @@
         <v>23</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>264</v>
+        <v>91</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>265</v>
+        <v>92</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2689,32 +2856,32 @@
         <v>23</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>265</v>
+        <v>92</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>264</v>
+        <v>91</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2735,29 +2902,29 @@
         <v>23</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -2777,29 +2944,29 @@
         <v>23</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -2816,31 +2983,31 @@
     </row>
     <row r="33" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -2858,31 +3025,31 @@
     </row>
     <row r="34" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -2900,7 +3067,7 @@
     </row>
     <row r="35" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>24</v>
@@ -2916,13 +3083,13 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
@@ -2936,10 +3103,10 @@
     </row>
     <row r="36" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -2952,13 +3119,13 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -2972,10 +3139,10 @@
     </row>
     <row r="37" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -2988,13 +3155,13 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -3008,10 +3175,10 @@
     </row>
     <row r="38" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -3024,13 +3191,13 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -3043,45 +3210,47 @@
       <c r="X38" s="2"/>
     </row>
     <row r="39" spans="1:24" ht="42" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-      <c r="S39" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="U39" s="1"/>
+      <c r="A39" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="T39" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>266</v>
+      </c>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
       <c r="X39" s="2"/>
     </row>
     <row r="40" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -3100,13 +3269,13 @@
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
@@ -3114,10 +3283,10 @@
     </row>
     <row r="41" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -3136,13 +3305,13 @@
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
@@ -3150,10 +3319,10 @@
     </row>
     <row r="42" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -3172,13 +3341,13 @@
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
@@ -3186,10 +3355,10 @@
     </row>
     <row r="43" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -3208,13 +3377,13 @@
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
@@ -3222,10 +3391,10 @@
     </row>
     <row r="44" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -3244,13 +3413,13 @@
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>266</v>
+        <v>117</v>
       </c>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
@@ -3258,10 +3427,10 @@
     </row>
     <row r="45" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -3280,13 +3449,13 @@
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
@@ -3294,19 +3463,19 @@
     </row>
     <row r="46" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>35</v>
+        <v>102</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>278</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -3330,19 +3499,19 @@
     </row>
     <row r="47" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>176</v>
+        <v>122</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -3366,10 +3535,10 @@
     </row>
     <row r="48" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -3385,13 +3554,13 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
@@ -3402,10 +3571,10 @@
     </row>
     <row r="49" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -3421,13 +3590,13 @@
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>267</v>
+        <v>124</v>
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
@@ -3438,10 +3607,10 @@
     </row>
     <row r="50" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3457,13 +3626,13 @@
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
       <c r="P50" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
@@ -3474,10 +3643,10 @@
     </row>
     <row r="51" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -3493,13 +3662,13 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
@@ -3510,10 +3679,10 @@
     </row>
     <row r="52" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -3529,13 +3698,13 @@
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
@@ -3546,10 +3715,10 @@
     </row>
     <row r="53" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -3565,13 +3734,13 @@
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
@@ -3582,34 +3751,34 @@
     </row>
     <row r="54" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -3628,34 +3797,34 @@
     </row>
     <row r="55" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -3674,28 +3843,28 @@
     </row>
     <row r="56" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="D56" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -3716,28 +3885,28 @@
     </row>
     <row r="57" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="D57" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -3758,31 +3927,31 @@
     </row>
     <row r="58" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -3800,31 +3969,31 @@
     </row>
     <row r="59" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -3842,10 +4011,10 @@
     </row>
     <row r="60" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -3858,22 +4027,22 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
@@ -3884,10 +4053,10 @@
     </row>
     <row r="61" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -3900,22 +4069,22 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
@@ -3926,17 +4095,17 @@
     </row>
     <row r="62" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="3" t="s">
-        <v>179</v>
+      <c r="G62" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -3958,10 +4127,10 @@
     </row>
     <row r="63" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -3969,8 +4138,8 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="3" t="s">
-        <v>179</v>
+      <c r="I63" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -3990,10 +4159,10 @@
     </row>
     <row r="64" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -4002,8 +4171,8 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-      <c r="J64" s="3" t="s">
-        <v>179</v>
+      <c r="J64" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -4022,10 +4191,10 @@
     </row>
     <row r="65" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -4035,8 +4204,8 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
-      <c r="K65" s="3" t="s">
-        <v>179</v>
+      <c r="K65" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
@@ -4054,10 +4223,10 @@
     </row>
     <row r="66" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -4072,8 +4241,8 @@
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
-      <c r="P66" s="3" t="s">
-        <v>179</v>
+      <c r="P66" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
@@ -4086,10 +4255,10 @@
     </row>
     <row r="67" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -4105,8 +4274,8 @@
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
-      <c r="Q67" s="3" t="s">
-        <v>179</v>
+      <c r="Q67" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
@@ -4118,10 +4287,10 @@
     </row>
     <row r="68" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -4138,8 +4307,8 @@
       <c r="O68" s="1"/>
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
-      <c r="R68" s="3" t="s">
-        <v>179</v>
+      <c r="R68" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
@@ -4150,10 +4319,10 @@
     </row>
     <row r="69" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -4171,8 +4340,8 @@
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
-      <c r="S69" s="3" t="s">
-        <v>179</v>
+      <c r="S69" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
@@ -4182,10 +4351,10 @@
     </row>
     <row r="70" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -4204,8 +4373,8 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
-      <c r="T70" s="3" t="s">
-        <v>179</v>
+      <c r="T70" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
@@ -4214,10 +4383,10 @@
     </row>
     <row r="71" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -4228,8 +4397,8 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
-      <c r="L71" s="3" t="s">
-        <v>179</v>
+      <c r="L71" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
@@ -4246,10 +4415,10 @@
     </row>
     <row r="72" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -4261,8 +4430,8 @@
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
-      <c r="M72" s="3" t="s">
-        <v>179</v>
+      <c r="M72" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
@@ -4278,10 +4447,10 @@
     </row>
     <row r="73" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -4294,8 +4463,8 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
-      <c r="N73" s="3" t="s">
-        <v>179</v>
+      <c r="N73" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
@@ -4310,10 +4479,10 @@
     </row>
     <row r="74" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -4327,8 +4496,8 @@
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
-      <c r="O74" s="3" t="s">
-        <v>179</v>
+      <c r="O74" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
@@ -4342,10 +4511,10 @@
     </row>
     <row r="75" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -4357,8 +4526,8 @@
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
-      <c r="M75" s="3" t="s">
-        <v>180</v>
+      <c r="M75" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
@@ -4374,10 +4543,10 @@
     </row>
     <row r="76" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -4388,8 +4557,8 @@
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
-      <c r="L76" s="3" t="s">
-        <v>180</v>
+      <c r="L76" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
@@ -4406,10 +4575,10 @@
     </row>
     <row r="77" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -4418,8 +4587,8 @@
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="3" t="s">
-        <v>180</v>
+      <c r="J77" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -4438,10 +4607,10 @@
     </row>
     <row r="78" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -4449,8 +4618,8 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
-      <c r="I78" s="3" t="s">
-        <v>180</v>
+      <c r="I78" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -4470,10 +4639,10 @@
     </row>
     <row r="79" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -4486,8 +4655,8 @@
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
-      <c r="N79" s="3" t="s">
-        <v>180</v>
+      <c r="N79" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
@@ -4502,10 +4671,10 @@
     </row>
     <row r="80" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -4515,8 +4684,8 @@
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
-      <c r="K80" s="3" t="s">
-        <v>180</v>
+      <c r="K80" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
@@ -4534,10 +4703,10 @@
     </row>
     <row r="81" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -4552,11 +4721,11 @@
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
-      <c r="P81" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>130</v>
+      <c r="P81" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q81" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
@@ -4568,10 +4737,10 @@
     </row>
     <row r="82" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -4587,11 +4756,11 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
-      <c r="Q82" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="R82" s="3" t="s">
-        <v>130</v>
+      <c r="Q82" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="R82" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="S82" s="1"/>
       <c r="T82" s="1"/>
@@ -4602,10 +4771,10 @@
     </row>
     <row r="83" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -4622,11 +4791,11 @@
       <c r="O83" s="1"/>
       <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
-      <c r="R83" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>130</v>
+      <c r="R83" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="S83" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
@@ -4636,10 +4805,10 @@
     </row>
     <row r="84" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -4658,11 +4827,11 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
-      <c r="T84" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="U84" s="3" t="s">
-        <v>179</v>
+      <c r="T84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U84" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
@@ -4670,10 +4839,10 @@
     </row>
     <row r="85" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -4693,21 +4862,21 @@
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
       <c r="T85" s="1"/>
-      <c r="U85" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="V85" s="3" t="s">
-        <v>179</v>
+      <c r="U85" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="V85" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="W85" s="1"/>
       <c r="X85" s="2"/>
     </row>
     <row r="86" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -4722,11 +4891,11 @@
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
-      <c r="P86" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q86" s="3" t="s">
-        <v>130</v>
+      <c r="P86" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q86" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
@@ -4738,10 +4907,10 @@
     </row>
     <row r="87" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -4756,11 +4925,11 @@
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
-      <c r="P87" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q87" s="3" t="s">
-        <v>182</v>
+      <c r="P87" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q87" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
@@ -4772,10 +4941,10 @@
     </row>
     <row r="88" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>93</v>
+        <v>166</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
@@ -4792,11 +4961,11 @@
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
-      <c r="R88" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="S88" s="3" t="s">
-        <v>130</v>
+      <c r="R88" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="S88" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
@@ -4806,10 +4975,10 @@
     </row>
     <row r="89" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
@@ -4826,11 +4995,11 @@
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
-      <c r="R89" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>182</v>
+      <c r="R89" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="S89" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
@@ -4840,10 +5009,10 @@
     </row>
     <row r="90" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>95</v>
+        <v>168</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -4862,11 +5031,11 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
-      <c r="T90" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="U90" s="3" t="s">
-        <v>130</v>
+      <c r="T90" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="U90" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
@@ -4874,10 +5043,10 @@
     </row>
     <row r="91" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -4896,11 +5065,11 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
-      <c r="T91" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>182</v>
+      <c r="T91" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U91" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
@@ -4908,28 +5077,28 @@
     </row>
     <row r="92" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -4948,28 +5117,28 @@
     </row>
     <row r="93" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
@@ -4988,33 +5157,35 @@
     </row>
     <row r="94" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
-      <c r="F94" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>185</v>
+      <c r="F94" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>289</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="L94" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="L94" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
@@ -5030,34 +5201,34 @@
     </row>
     <row r="95" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
@@ -5074,7 +5245,7 @@
     </row>
     <row r="96" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>24</v>
@@ -5090,13 +5261,13 @@
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
       <c r="M96" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="P96" s="1"/>
       <c r="Q96" s="1"/>
@@ -5110,10 +5281,10 @@
     </row>
     <row r="97" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -5126,13 +5297,13 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="N97" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
@@ -5146,10 +5317,10 @@
     </row>
     <row r="98" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -5162,13 +5333,13 @@
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
       <c r="M98" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
@@ -5182,10 +5353,10 @@
     </row>
     <row r="99" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
@@ -5198,13 +5369,13 @@
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
       <c r="M99" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
@@ -5217,45 +5388,47 @@
       <c r="X99" s="2"/>
     </row>
     <row r="100" spans="1:24" ht="42" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
-      <c r="L100" s="1"/>
-      <c r="M100" s="1"/>
-      <c r="N100" s="1"/>
-      <c r="O100" s="1"/>
-      <c r="P100" s="1"/>
-      <c r="Q100" s="1"/>
-      <c r="R100" s="1"/>
-      <c r="S100" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="T100" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="U100" s="1"/>
+      <c r="A100" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="6"/>
+      <c r="N100" s="6"/>
+      <c r="O100" s="6"/>
+      <c r="P100" s="6"/>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="T100" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="U100" s="7" t="s">
+        <v>266</v>
+      </c>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
       <c r="X100" s="2"/>
     </row>
     <row r="101" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
@@ -5274,13 +5447,13 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
       <c r="S101" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="T101" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="U101" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
@@ -5288,10 +5461,10 @@
     </row>
     <row r="102" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
@@ -5310,13 +5483,13 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
       <c r="S102" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="T102" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="U102" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
@@ -5324,10 +5497,10 @@
     </row>
     <row r="103" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
@@ -5346,24 +5519,24 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
       <c r="S103" s="1" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="T103" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="U103" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
       <c r="X103" s="2"/>
     </row>
-    <row r="104" spans="1:24" ht="70" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
@@ -5382,13 +5555,13 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
       <c r="S104" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="T104" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="U104" s="1" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
@@ -5396,10 +5569,10 @@
     </row>
     <row r="105" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
@@ -5418,13 +5591,13 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
       <c r="S105" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="T105" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="U105" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
@@ -5432,10 +5605,10 @@
     </row>
     <row r="106" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
@@ -5454,13 +5627,13 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
       <c r="S106" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="U106" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
@@ -5468,19 +5641,19 @@
     </row>
     <row r="107" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
@@ -5504,19 +5677,19 @@
     </row>
     <row r="108" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
@@ -5538,12 +5711,12 @@
       <c r="W108" s="1"/>
       <c r="X108" s="2"/>
     </row>
-    <row r="109" spans="1:24" ht="70" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
@@ -5559,13 +5732,13 @@
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
       <c r="P109" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="S109" s="1"/>
       <c r="T109" s="1"/>
@@ -5576,10 +5749,10 @@
     </row>
     <row r="110" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
@@ -5595,13 +5768,13 @@
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
       <c r="P110" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="Q110" s="1" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>156</v>
+        <v>196</v>
       </c>
       <c r="S110" s="1"/>
       <c r="T110" s="1"/>
@@ -5612,10 +5785,10 @@
     </row>
     <row r="111" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
@@ -5631,13 +5804,13 @@
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
       <c r="P111" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="S111" s="1"/>
       <c r="T111" s="1"/>
@@ -5648,10 +5821,10 @@
     </row>
     <row r="112" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
@@ -5667,13 +5840,13 @@
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
       <c r="P112" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="Q112" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="S112" s="1"/>
       <c r="T112" s="1"/>
@@ -5684,10 +5857,10 @@
     </row>
     <row r="113" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
@@ -5703,13 +5876,13 @@
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
       <c r="P113" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="Q113" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="S113" s="1"/>
       <c r="T113" s="1"/>
@@ -5720,10 +5893,10 @@
     </row>
     <row r="114" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
@@ -5739,12 +5912,14 @@
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
       <c r="P114" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="Q114" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="R114" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="R114" s="3" t="s">
+        <v>197</v>
+      </c>
       <c r="S114" s="1"/>
       <c r="T114" s="1"/>
       <c r="U114" s="1"/>
@@ -5754,19 +5929,19 @@
     </row>
     <row r="115" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>101</v>
+        <v>198</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>254</v>
+        <v>200</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
@@ -5790,19 +5965,19 @@
     </row>
     <row r="116" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>102</v>
+        <v>202</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>268</v>
+        <v>203</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
@@ -5826,34 +6001,34 @@
     </row>
     <row r="117" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>265</v>
+        <v>92</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="M117" s="1"/>
       <c r="N117" s="1"/>
@@ -5870,34 +6045,34 @@
     </row>
     <row r="118" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>264</v>
+        <v>91</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>166</v>
+        <v>93</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
@@ -5914,29 +6089,29 @@
     </row>
     <row r="119" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="L119" s="1"/>
       <c r="M119" s="1"/>
@@ -5954,29 +6129,29 @@
     </row>
     <row r="120" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="J120" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
@@ -5994,7 +6169,7 @@
     </row>
     <row r="121" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>24</v>
@@ -6010,7 +6185,7 @@
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
       <c r="M121" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="N121" s="1" t="s">
         <v>210</v>
@@ -6030,10 +6205,10 @@
     </row>
     <row r="122" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
@@ -6046,10 +6221,10 @@
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
       <c r="M122" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="N122" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="O122" s="1" t="s">
         <v>212</v>
@@ -6066,10 +6241,10 @@
     </row>
     <row r="123" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
@@ -6082,10 +6257,10 @@
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
       <c r="M123" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="O123" s="1" t="s">
         <v>213</v>
@@ -6102,10 +6277,10 @@
     </row>
     <row r="124" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
@@ -6118,7 +6293,7 @@
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
       <c r="M124" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="N124" s="1" t="s">
         <v>214</v>
@@ -6138,35 +6313,35 @@
     </row>
     <row r="125" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>108</v>
+        <v>207</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>216</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G125" s="1"/>
       <c r="H125" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
@@ -6184,35 +6359,35 @@
     </row>
     <row r="126" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>109</v>
+        <v>207</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>220</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>285</v>
       </c>
       <c r="G126" s="1"/>
       <c r="H126" s="1" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>160</v>
+        <v>94</v>
+      </c>
+      <c r="J126" s="5" t="s">
+        <v>286</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
@@ -6229,45 +6404,47 @@
       <c r="X126" s="2"/>
     </row>
     <row r="127" spans="1:24" ht="70" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
-      <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
-      <c r="J127" s="1"/>
-      <c r="K127" s="1"/>
-      <c r="L127" s="1"/>
-      <c r="M127" s="1"/>
-      <c r="N127" s="1"/>
-      <c r="O127" s="1"/>
-      <c r="P127" s="1"/>
-      <c r="Q127" s="1"/>
-      <c r="R127" s="1"/>
-      <c r="S127" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="T127" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="U127" s="1"/>
+      <c r="A127" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C127" s="6"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="6"/>
+      <c r="I127" s="6"/>
+      <c r="J127" s="6"/>
+      <c r="K127" s="6"/>
+      <c r="L127" s="6"/>
+      <c r="M127" s="6"/>
+      <c r="N127" s="6"/>
+      <c r="O127" s="6"/>
+      <c r="P127" s="6"/>
+      <c r="Q127" s="6"/>
+      <c r="R127" s="6"/>
+      <c r="S127" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="T127" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="U127" s="7" t="s">
+        <v>266</v>
+      </c>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
       <c r="X127" s="2"/>
     </row>
     <row r="128" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
@@ -6286,13 +6463,13 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
       <c r="S128" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="T128" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="U128" s="1" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
@@ -6300,10 +6477,10 @@
     </row>
     <row r="129" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
@@ -6322,13 +6499,13 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
       <c r="S129" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="T129" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="U129" s="1" t="s">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
@@ -6336,10 +6513,10 @@
     </row>
     <row r="130" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
@@ -6358,13 +6535,13 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
       <c r="S130" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="T130" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="U130" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
@@ -6372,10 +6549,10 @@
     </row>
     <row r="131" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
@@ -6394,13 +6571,13 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="T131" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="U131" s="1" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
@@ -6408,10 +6585,10 @@
     </row>
     <row r="132" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
@@ -6430,13 +6607,13 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="T132" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="U132" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
@@ -6444,10 +6621,10 @@
     </row>
     <row r="133" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
@@ -6466,13 +6643,13 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="T133" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="U133" s="1" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
@@ -6480,19 +6657,19 @@
     </row>
     <row r="134" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
@@ -6516,19 +6693,19 @@
     </row>
     <row r="135" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
@@ -6552,10 +6729,10 @@
     </row>
     <row r="136" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
@@ -6571,13 +6748,13 @@
       <c r="N136" s="1"/>
       <c r="O136" s="1"/>
       <c r="P136" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="Q136" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="R136" s="1" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="S136" s="1"/>
       <c r="T136" s="1"/>
@@ -6588,10 +6765,10 @@
     </row>
     <row r="137" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
@@ -6607,13 +6784,13 @@
       <c r="N137" s="1"/>
       <c r="O137" s="1"/>
       <c r="P137" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="Q137" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="R137" s="1" t="s">
-        <v>156</v>
+        <v>71</v>
+      </c>
+      <c r="R137" s="5" t="s">
+        <v>276</v>
       </c>
       <c r="S137" s="1"/>
       <c r="T137" s="1"/>
@@ -6624,10 +6801,10 @@
     </row>
     <row r="138" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
@@ -6643,13 +6820,13 @@
       <c r="N138" s="1"/>
       <c r="O138" s="1"/>
       <c r="P138" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="Q138" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="S138" s="1"/>
       <c r="T138" s="1"/>
@@ -6660,10 +6837,10 @@
     </row>
     <row r="139" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
@@ -6679,13 +6856,13 @@
       <c r="N139" s="1"/>
       <c r="O139" s="1"/>
       <c r="P139" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="Q139" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
@@ -6696,10 +6873,10 @@
     </row>
     <row r="140" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
@@ -6715,13 +6892,13 @@
       <c r="N140" s="1"/>
       <c r="O140" s="1"/>
       <c r="P140" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="Q140" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="S140" s="1"/>
       <c r="T140" s="1"/>
@@ -6732,10 +6909,10 @@
     </row>
     <row r="141" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
@@ -6751,13 +6928,13 @@
       <c r="N141" s="1"/>
       <c r="O141" s="1"/>
       <c r="P141" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="Q141" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="R141" s="1" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="S141" s="1"/>
       <c r="T141" s="1"/>
@@ -6768,10 +6945,10 @@
     </row>
     <row r="142" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>110</v>
+        <v>234</v>
       </c>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
@@ -6783,16 +6960,16 @@
       <c r="J142" s="1"/>
       <c r="K142" s="1"/>
       <c r="L142" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
@@ -6806,10 +6983,10 @@
     </row>
     <row r="143" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
@@ -6821,16 +6998,16 @@
       <c r="J143" s="1"/>
       <c r="K143" s="1"/>
       <c r="L143" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
@@ -6844,10 +7021,10 @@
     </row>
     <row r="144" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>112</v>
+        <v>241</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
@@ -6859,16 +7036,16 @@
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
       <c r="L144" s="1" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="M144" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="P144" s="1"/>
       <c r="Q144" s="1"/>
@@ -6882,35 +7059,35 @@
     </row>
     <row r="145" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>113</v>
+        <v>243</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1" t="s">
-        <v>262</v>
+        <v>74</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
@@ -6928,32 +7105,32 @@
     </row>
     <row r="146" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>114</v>
+        <v>244</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G146" s="1"/>
       <c r="H146" s="1" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
@@ -6970,32 +7147,32 @@
     </row>
     <row r="147" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G147" s="1"/>
       <c r="H147" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="J147" s="1" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="M147" s="1"/>
       <c r="N147" s="1"/>
@@ -7012,36 +7189,36 @@
     </row>
     <row r="148" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>116</v>
+        <v>246</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="G148" s="1"/>
       <c r="H148" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="J148" s="1"/>
       <c r="K148" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="M148" s="1"/>
       <c r="N148" s="1"/>
@@ -7058,35 +7235,35 @@
     </row>
     <row r="149" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="L149" s="1"/>
       <c r="M149" s="1"/>
@@ -7104,10 +7281,10 @@
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
@@ -7118,7 +7295,7 @@
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
       <c r="K150" s="1" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="L150" s="1"/>
       <c r="M150" s="1"/>
@@ -7136,10 +7313,10 @@
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
@@ -7150,7 +7327,7 @@
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
       <c r="K151" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
@@ -7168,7 +7345,7 @@
     </row>
     <row r="152" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>24</v>
@@ -7184,13 +7361,13 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="P152" s="1"/>
       <c r="Q152" s="1"/>
@@ -7204,10 +7381,10 @@
     </row>
     <row r="153" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
@@ -7220,13 +7397,13 @@
       <c r="K153" s="1"/>
       <c r="L153" s="1"/>
       <c r="M153" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="P153" s="1"/>
       <c r="Q153" s="1"/>
@@ -7240,10 +7417,10 @@
     </row>
     <row r="154" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
@@ -7256,13 +7433,13 @@
       <c r="K154" s="1"/>
       <c r="L154" s="1"/>
       <c r="M154" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O154" s="1" t="s">
-        <v>213</v>
+        <v>58</v>
+      </c>
+      <c r="O154" s="5" t="s">
+        <v>283</v>
       </c>
       <c r="P154" s="1"/>
       <c r="Q154" s="1"/>
@@ -7276,10 +7453,10 @@
     </row>
     <row r="155" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
@@ -7292,13 +7469,13 @@
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
       <c r="M155" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="O155" s="1" t="s">
-        <v>213</v>
+        <v>35</v>
+      </c>
+      <c r="O155" s="5" t="s">
+        <v>284</v>
       </c>
       <c r="P155" s="1"/>
       <c r="Q155" s="1"/>
@@ -7312,36 +7489,36 @@
     </row>
     <row r="156" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
       <c r="H156" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>166</v>
+        <v>89</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="M156" s="1"/>
       <c r="N156" s="1"/>
@@ -7358,36 +7535,36 @@
     </row>
     <row r="157" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>109</v>
+        <v>220</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
       <c r="H157" s="1" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
@@ -7403,45 +7580,47 @@
       <c r="X157" s="2"/>
     </row>
     <row r="158" spans="1:24" ht="70" x14ac:dyDescent="0.25">
-      <c r="A158" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
-      <c r="E158" s="1"/>
-      <c r="F158" s="1"/>
-      <c r="G158" s="1"/>
-      <c r="H158" s="1"/>
-      <c r="I158" s="1"/>
-      <c r="J158" s="1"/>
-      <c r="K158" s="1"/>
-      <c r="L158" s="1"/>
-      <c r="M158" s="1"/>
-      <c r="N158" s="1"/>
-      <c r="O158" s="1"/>
-      <c r="P158" s="1"/>
-      <c r="Q158" s="1"/>
-      <c r="R158" s="1"/>
-      <c r="S158" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="T158" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="U158" s="1"/>
+      <c r="A158" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C158" s="6"/>
+      <c r="D158" s="6"/>
+      <c r="E158" s="6"/>
+      <c r="F158" s="6"/>
+      <c r="G158" s="6"/>
+      <c r="H158" s="6"/>
+      <c r="I158" s="6"/>
+      <c r="J158" s="6"/>
+      <c r="K158" s="6"/>
+      <c r="L158" s="6"/>
+      <c r="M158" s="6"/>
+      <c r="N158" s="6"/>
+      <c r="O158" s="6"/>
+      <c r="P158" s="6"/>
+      <c r="Q158" s="6"/>
+      <c r="R158" s="6"/>
+      <c r="S158" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="T158" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="U158" s="7" t="s">
+        <v>266</v>
+      </c>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
       <c r="X158" s="2"/>
     </row>
     <row r="159" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
@@ -7460,13 +7639,13 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
       <c r="S159" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="T159" s="1" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="U159" s="1" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
@@ -7474,10 +7653,10 @@
     </row>
     <row r="160" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
@@ -7496,13 +7675,13 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
       <c r="S160" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="T160" s="1" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="U160" s="1" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
@@ -7510,10 +7689,10 @@
     </row>
     <row r="161" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
@@ -7532,13 +7711,13 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
       <c r="S161" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="T161" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="U161" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
@@ -7546,10 +7725,10 @@
     </row>
     <row r="162" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
@@ -7568,13 +7747,13 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
       <c r="S162" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="T162" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="U162" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
@@ -7582,10 +7761,10 @@
     </row>
     <row r="163" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
@@ -7603,14 +7782,14 @@
       <c r="P163" s="1"/>
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
-      <c r="S163" s="1" t="s">
-        <v>134</v>
+      <c r="S163" s="5" t="s">
+        <v>267</v>
       </c>
       <c r="T163" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="U163" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
@@ -7618,10 +7797,10 @@
     </row>
     <row r="164" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
@@ -7640,33 +7819,33 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
       <c r="S164" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="T164" s="1" t="s">
-        <v>131</v>
+        <v>45</v>
+      </c>
+      <c r="T164" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="U164" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
       <c r="X164" s="2"/>
     </row>
-    <row r="165" spans="1:24" ht="98" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
@@ -7688,21 +7867,21 @@
       <c r="W165" s="1"/>
       <c r="X165" s="2"/>
     </row>
-    <row r="166" spans="1:24" ht="98" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E166" s="1" t="s">
-        <v>243</v>
+      <c r="E166" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
@@ -7726,10 +7905,10 @@
     </row>
     <row r="167" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
@@ -7745,13 +7924,13 @@
       <c r="N167" s="1"/>
       <c r="O167" s="1"/>
       <c r="P167" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="Q167" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="R167" s="1" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="S167" s="1"/>
       <c r="T167" s="1"/>
@@ -7762,10 +7941,10 @@
     </row>
     <row r="168" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
@@ -7781,13 +7960,13 @@
       <c r="N168" s="1"/>
       <c r="O168" s="1"/>
       <c r="P168" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="Q168" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="R168" s="1" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="S168" s="1"/>
       <c r="T168" s="1"/>
@@ -7798,10 +7977,10 @@
     </row>
     <row r="169" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
@@ -7817,13 +7996,13 @@
       <c r="N169" s="1"/>
       <c r="O169" s="1"/>
       <c r="P169" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="Q169" s="1" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="R169" s="1" t="s">
-        <v>156</v>
+        <v>68</v>
       </c>
       <c r="S169" s="1"/>
       <c r="T169" s="1"/>
@@ -7834,10 +8013,10 @@
     </row>
     <row r="170" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
@@ -7853,13 +8032,13 @@
       <c r="N170" s="1"/>
       <c r="O170" s="1"/>
       <c r="P170" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="Q170" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="R170" s="1" t="s">
-        <v>259</v>
+        <v>31</v>
+      </c>
+      <c r="R170" s="5" t="s">
+        <v>277</v>
       </c>
       <c r="S170" s="1"/>
       <c r="T170" s="1"/>
@@ -7870,10 +8049,10 @@
     </row>
     <row r="171" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
@@ -7889,13 +8068,13 @@
       <c r="N171" s="1"/>
       <c r="O171" s="1"/>
       <c r="P171" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="Q171" s="1" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="R171" s="1" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="S171" s="1"/>
       <c r="T171" s="1"/>
@@ -7906,10 +8085,10 @@
     </row>
     <row r="172" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
@@ -7925,13 +8104,13 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
       <c r="P172" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="R172" s="1" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="S172" s="1"/>
       <c r="T172" s="1"/>
@@ -7942,43 +8121,43 @@
     </row>
     <row r="173" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>110</v>
+        <v>234</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
       <c r="H173" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="M173" s="1"/>
       <c r="N173" s="1" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="O173" s="1" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="P173" s="1"/>
       <c r="Q173" s="1"/>
@@ -7992,43 +8171,43 @@
     </row>
     <row r="174" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="F174" s="1"/>
       <c r="G174" s="1"/>
       <c r="H174" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="M174" s="1"/>
       <c r="N174" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="O174" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="P174" s="1"/>
       <c r="Q174" s="1"/>
@@ -8042,40 +8221,40 @@
     </row>
     <row r="175" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>112</v>
+        <v>241</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
       <c r="H175" s="1" t="s">
-        <v>147</v>
+        <v>49</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="J175" s="1" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="M175" s="1"/>
       <c r="N175" s="1" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="O175" s="1"/>
       <c r="P175" s="1"/>
@@ -8090,10 +8269,10 @@
     </row>
     <row r="176" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>116</v>
+        <v>246</v>
       </c>
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
@@ -8101,13 +8280,13 @@
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
       <c r="H176" s="1" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
@@ -8126,10 +8305,10 @@
     </row>
     <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
@@ -8137,13 +8316,13 @@
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
       <c r="H177" s="1" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
@@ -8161,6 +8340,7 @@
       <c r="X177" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W177" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/2025-2026工程训练_0308.xlsx
+++ b/2025-2026工程训练_0308.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\工作\1实验教学部\排课\ClassSchedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C154D25B-D969-4DDE-B19E-95AF5E50DB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC722BD-D15C-4942-9862-6C57C88600D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4610" yWindow="3230" windowWidth="33130" windowHeight="15770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="排课表" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="291">
   <si>
     <t>教学班名称</t>
   </si>
@@ -411,15 +413,8 @@
 B焊5-7</t>
   </si>
   <si>
-    <t>理论1-4</t>
-  </si>
-  <si>
-    <t>铣m5-7</t>
-  </si>
-  <si>
     <t>理论1-4
-A激5-7
-B热5-7</t>
+铣m5-7</t>
   </si>
   <si>
     <t>A产1-4
@@ -428,6 +423,11 @@
 A智5-7</t>
   </si>
   <si>
+    <t>理论1-4
+A激5-7
+B热5-7</t>
+  </si>
+  <si>
     <t>机械设计制造及其自动化(国际综合1班)国际26+（一体化）14人</t>
   </si>
   <si>
@@ -438,6 +438,10 @@
   </si>
   <si>
     <t>机械设计制造及其自动化(国际综合2班)中德26+（一体化）14人</t>
+  </si>
+  <si>
+    <t>数c1-4（胡）
+数c5-7（胡）</t>
   </si>
   <si>
     <t>B压1-4
@@ -495,6 +499,9 @@
 A超6'-7</t>
   </si>
   <si>
+    <t>铣m5-7</t>
+  </si>
+  <si>
     <t>焊5-7</t>
   </si>
   <si>
@@ -505,6 +512,9 @@
   </si>
   <si>
     <t>钳5-7</t>
+  </si>
+  <si>
+    <t>理论1-4</t>
   </si>
   <si>
     <t>车1-4</t>
@@ -528,7 +538,7 @@
     <t>车5-7</t>
   </si>
   <si>
-    <t>数x5-7</t>
+    <t>数x5-7（棚）</t>
   </si>
   <si>
     <t>A柔5-6'
@@ -547,6 +557,12 @@
   </si>
   <si>
     <t>先t5-7</t>
+  </si>
+  <si>
+    <t>先t5-7（莫）</t>
+  </si>
+  <si>
+    <t>数x5-7</t>
   </si>
   <si>
     <t>周二</t>
@@ -626,14 +642,14 @@
 A焊5-7</t>
   </si>
   <si>
-    <t>B装1-4
+    <t>B装1-4（曦）
 A五1-4
-钳5-7</t>
+钳5-7（曦）</t>
   </si>
   <si>
     <t>A柔1-4
 B机1-4
-铣m5-7</t>
+铣m5-7（棚）</t>
   </si>
   <si>
     <t>A产1-4
@@ -660,6 +676,12 @@
 项目（3）5-7</t>
   </si>
   <si>
+    <t>铸1-4（标）</t>
+  </si>
+  <si>
+    <t>车1-4（邓）</t>
+  </si>
+  <si>
     <t>周三</t>
   </si>
   <si>
@@ -882,6 +904,10 @@
 B焊5-7</t>
   </si>
   <si>
+    <t>数x1-4（杰）
+数x5-7（杰）</t>
+  </si>
+  <si>
     <t>铣m1-4
 A柔5-7
 B机5-7</t>
@@ -916,11 +942,11 @@
 B压1-2
 B智3-4
 A压3-4
-钳5-8</t>
+钳5-8（曦）</t>
   </si>
   <si>
     <t>焊1-4
-数c5-7
+数c5-7（胡）
 考8</t>
   </si>
   <si>
@@ -935,10 +961,10 @@
   </si>
   <si>
     <t>焊1-4
-先d5-8</t>
-  </si>
-  <si>
-    <t>数c1-4
+先d5-8（张）</t>
+  </si>
+  <si>
+    <t>数c1-4（胡）
 钳5-7
 考8</t>
   </si>
@@ -1040,7 +1066,15 @@
   <si>
     <t>B柔1-4
 A机1-4
-数c5-7</t>
+数c5-7（胡）</t>
+  </si>
+  <si>
+    <t>先t1-4（杰）
+先t5-7（杰）</t>
+  </si>
+  <si>
+    <t>数c1-4（胡）
+钳5-7（曦）</t>
   </si>
   <si>
     <t>A超1-2
@@ -1100,6 +1134,52 @@
 A激5-7</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">先d1-4
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>焊5-7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">钳1-4
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>先d5-7</t>
+    </r>
+  </si>
+  <si>
     <t>B热1-4
 A齿1-4
 B柔5-7
@@ -1157,13 +1237,13 @@
 B热5-7</t>
   </si>
   <si>
-    <t>先d1-4
-钳5-6
+    <t>先d1-4（张）
+钳5-6（曦）
 考7</t>
   </si>
   <si>
-    <t>钳1-4
-先d5-6
+    <t>钳1-4（曦）
+先d5-6（张）
 考7</t>
   </si>
   <si>
@@ -1210,17 +1290,26 @@
 铣m5-7</t>
   </si>
   <si>
+    <t>焊1-4
+B压5-7
+A激5-7</t>
+  </si>
+  <si>
     <t>A柔1-4
 B机1-4
 A热5-7
 B齿5-7</t>
+  </si>
+  <si>
+    <t>A压1-4
+B激1-4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1229,17 +1318,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF0070C0"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1274,28 +1370,31 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1716,7 +1815,7 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
-      <c r="X2" s="2"/>
+      <c r="X2" s="6"/>
     </row>
     <row r="3" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1752,7 +1851,7 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
-      <c r="X3" s="2"/>
+      <c r="X3" s="6"/>
     </row>
     <row r="4" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1788,7 +1887,7 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
-      <c r="X4" s="2"/>
+      <c r="X4" s="6"/>
     </row>
     <row r="5" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1824,31 +1923,31 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
-      <c r="X5" s="2"/>
+      <c r="X5" s="6"/>
     </row>
     <row r="6" spans="1:24" ht="42" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
       <c r="S6" s="5" t="s">
         <v>82</v>
       </c>
@@ -1860,7 +1959,7 @@
       </c>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
-      <c r="X6" s="2"/>
+      <c r="X6" s="6"/>
     </row>
     <row r="7" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -1896,7 +1995,7 @@
       </c>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
-      <c r="X7" s="2"/>
+      <c r="X7" s="6"/>
     </row>
     <row r="8" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1932,7 +2031,7 @@
       </c>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
-      <c r="X8" s="2"/>
+      <c r="X8" s="6"/>
     </row>
     <row r="9" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -1968,7 +2067,7 @@
       </c>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
-      <c r="X9" s="2"/>
+      <c r="X9" s="6"/>
     </row>
     <row r="10" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -2004,9 +2103,9 @@
       </c>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
-      <c r="X10" s="2"/>
-    </row>
-    <row r="11" spans="1:24" ht="42" x14ac:dyDescent="0.25">
+      <c r="X10" s="6"/>
+    </row>
+    <row r="11" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>80</v>
       </c>
@@ -2029,18 +2128,18 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
-      <c r="S11" s="1" t="s">
+      <c r="S11" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="T11" s="1" t="s">
+      <c r="T11" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
-      <c r="X11" s="2"/>
+      <c r="X11" s="6"/>
     </row>
     <row r="12" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -2071,19 +2170,19 @@
       <c r="T12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>106</v>
+      <c r="U12" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
-      <c r="X12" s="2"/>
+      <c r="X12" s="6"/>
     </row>
     <row r="13" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>84</v>
@@ -2092,7 +2191,7 @@
         <v>88</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -2112,20 +2211,20 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
-      <c r="X13" s="2"/>
+      <c r="X13" s="6"/>
     </row>
     <row r="14" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>110</v>
@@ -2148,7 +2247,7 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
-      <c r="X14" s="2"/>
+      <c r="X14" s="6"/>
     </row>
     <row r="15" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -2184,7 +2283,7 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
-      <c r="X15" s="2"/>
+      <c r="X15" s="6"/>
     </row>
     <row r="16" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -2220,7 +2319,7 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
-      <c r="X16" s="2"/>
+      <c r="X16" s="6"/>
     </row>
     <row r="17" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -2256,7 +2355,7 @@
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
-      <c r="X17" s="2"/>
+      <c r="X17" s="6"/>
     </row>
     <row r="18" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2285,14 +2384,14 @@
         <v>92</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
-      <c r="X18" s="2"/>
+      <c r="X18" s="6"/>
     </row>
     <row r="19" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -2328,7 +2427,7 @@
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
-      <c r="X19" s="2"/>
+      <c r="X19" s="6"/>
     </row>
     <row r="20" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -2364,7 +2463,7 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
-      <c r="X20" s="2"/>
+      <c r="X20" s="6"/>
     </row>
     <row r="21" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -2387,20 +2486,20 @@
         <v>119</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -2410,7 +2509,7 @@
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
-      <c r="X21" s="2"/>
+      <c r="X21" s="6"/>
     </row>
     <row r="22" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -2433,20 +2532,20 @@
         <v>118</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="N22" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
@@ -2456,7 +2555,7 @@
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
-      <c r="X22" s="2"/>
+      <c r="X22" s="6"/>
     </row>
     <row r="23" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -2473,23 +2572,23 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -2498,7 +2597,7 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
-      <c r="X23" s="2"/>
+      <c r="X23" s="6"/>
     </row>
     <row r="24" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -2515,23 +2614,23 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="P24" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -2540,7 +2639,7 @@
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
-      <c r="X24" s="2"/>
+      <c r="X24" s="6"/>
     </row>
     <row r="25" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -2553,26 +2652,26 @@
         <v>117</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2586,7 +2685,7 @@
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
-      <c r="X25" s="2"/>
+      <c r="X25" s="6"/>
     </row>
     <row r="26" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -2603,22 +2702,22 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="K26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -2628,7 +2727,7 @@
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
-      <c r="X26" s="2"/>
+      <c r="X26" s="6"/>
     </row>
     <row r="27" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -2638,23 +2737,23 @@
         <v>35</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2670,7 +2769,7 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
-      <c r="X27" s="2"/>
+      <c r="X27" s="6"/>
     </row>
     <row r="28" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -2680,23 +2779,23 @@
         <v>36</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="G28" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2712,7 +2811,7 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
-      <c r="X28" s="2"/>
+      <c r="X28" s="6"/>
     </row>
     <row r="29" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -2725,26 +2824,26 @@
         <v>117</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2758,7 +2857,7 @@
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
-      <c r="X29" s="2"/>
+      <c r="X29" s="6"/>
     </row>
     <row r="30" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -2771,26 +2870,26 @@
         <v>117</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="G30" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2804,7 +2903,7 @@
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
-      <c r="X30" s="2"/>
+      <c r="X30" s="6"/>
     </row>
     <row r="31" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -2817,23 +2916,23 @@
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -2846,7 +2945,7 @@
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
-      <c r="X31" s="2"/>
+      <c r="X31" s="6"/>
     </row>
     <row r="32" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -2859,23 +2958,23 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -2888,11 +2987,11 @@
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
-      <c r="X32" s="2"/>
+      <c r="X32" s="6"/>
     </row>
     <row r="33" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>27</v>
@@ -2901,22 +3000,22 @@
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -2930,11 +3029,11 @@
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
-      <c r="X33" s="2"/>
+      <c r="X33" s="6"/>
     </row>
     <row r="34" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>28</v>
@@ -2943,22 +3042,22 @@
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H34" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="J34" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -2972,11 +3071,11 @@
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
-      <c r="X34" s="2"/>
+      <c r="X34" s="6"/>
     </row>
     <row r="35" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>55</v>
@@ -2998,7 +3097,7 @@
         <v>92</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
@@ -3008,11 +3107,11 @@
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
-      <c r="X35" s="2"/>
+      <c r="X35" s="6"/>
     </row>
     <row r="36" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>54</v>
@@ -3034,7 +3133,7 @@
         <v>83</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -3044,11 +3143,11 @@
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
-      <c r="X36" s="2"/>
+      <c r="X36" s="6"/>
     </row>
     <row r="37" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>46</v>
@@ -3070,7 +3169,7 @@
         <v>90</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -3080,11 +3179,11 @@
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
-      <c r="X37" s="2"/>
+      <c r="X37" s="6"/>
     </row>
     <row r="38" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>45</v>
@@ -3116,35 +3215,35 @@
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
-      <c r="X38" s="2"/>
+      <c r="X38" s="6"/>
     </row>
     <row r="39" spans="1:24" ht="42" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B39" s="4" t="s">
+      <c r="A39" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4" t="s">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="T39" s="4" t="s">
+      <c r="T39" s="2" t="s">
         <v>96</v>
       </c>
       <c r="U39" s="5" t="s">
@@ -3152,11 +3251,11 @@
       </c>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
-      <c r="X39" s="2"/>
+      <c r="X39" s="6"/>
     </row>
     <row r="40" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>48</v>
@@ -3184,15 +3283,15 @@
         <v>82</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
-      <c r="X40" s="2"/>
+      <c r="X40" s="6"/>
     </row>
     <row r="41" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>47</v>
@@ -3220,15 +3319,15 @@
         <v>99</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
-      <c r="X41" s="2"/>
+      <c r="X41" s="6"/>
     </row>
     <row r="42" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>50</v>
@@ -3256,15 +3355,15 @@
         <v>90</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
-      <c r="X42" s="2"/>
+      <c r="X42" s="6"/>
     </row>
     <row r="43" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>49</v>
@@ -3292,15 +3391,15 @@
         <v>88</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
-      <c r="X43" s="2"/>
+      <c r="X43" s="6"/>
     </row>
     <row r="44" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>57</v>
@@ -3325,18 +3424,18 @@
         <v>96</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
-      <c r="X44" s="2"/>
+      <c r="X44" s="6"/>
     </row>
     <row r="45" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>56</v>
@@ -3364,18 +3463,18 @@
         <v>101</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
-      <c r="X45" s="2"/>
+      <c r="X45" s="6"/>
     </row>
     <row r="46" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>92</v>
@@ -3384,7 +3483,7 @@
         <v>99</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -3404,14 +3503,14 @@
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
-      <c r="X46" s="2"/>
+      <c r="X46" s="6"/>
     </row>
     <row r="47" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>90</v>
@@ -3420,7 +3519,7 @@
         <v>82</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -3440,11 +3539,11 @@
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
-      <c r="X47" s="2"/>
+      <c r="X47" s="6"/>
     </row>
     <row r="48" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>42</v>
@@ -3469,18 +3568,18 @@
         <v>101</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
-      <c r="X48" s="2"/>
+      <c r="X48" s="6"/>
     </row>
     <row r="49" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>41</v>
@@ -3505,18 +3604,18 @@
         <v>88</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
-      <c r="X49" s="2"/>
+      <c r="X49" s="6"/>
     </row>
     <row r="50" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>44</v>
@@ -3548,11 +3647,11 @@
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
-      <c r="X50" s="2"/>
+      <c r="X50" s="6"/>
     </row>
     <row r="51" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>43</v>
@@ -3577,18 +3676,18 @@
         <v>99</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
-      <c r="X51" s="2"/>
+      <c r="X51" s="6"/>
     </row>
     <row r="52" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>52</v>
@@ -3613,18 +3712,18 @@
         <v>86</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
-      <c r="X52" s="2"/>
+      <c r="X52" s="6"/>
     </row>
     <row r="53" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>51</v>
@@ -3656,11 +3755,11 @@
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
-      <c r="X53" s="2"/>
+      <c r="X53" s="6"/>
     </row>
     <row r="54" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>4</v>
@@ -3675,19 +3774,19 @@
         <v>118</v>
       </c>
       <c r="F54" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H54" s="1" t="s">
+      <c r="I54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J54" s="1" t="s">
         <v>122</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -3702,11 +3801,11 @@
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
-      <c r="X54" s="2"/>
+      <c r="X54" s="6"/>
     </row>
     <row r="55" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>5</v>
@@ -3721,19 +3820,19 @@
         <v>119</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H55" s="1" t="s">
+      <c r="I55" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="J55" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -3748,32 +3847,32 @@
       <c r="U55" s="1"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
-      <c r="X55" s="2"/>
+      <c r="X55" s="6"/>
     </row>
     <row r="56" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -3790,32 +3889,32 @@
       <c r="U56" s="1"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
-      <c r="X56" s="2"/>
+      <c r="X56" s="6"/>
     </row>
     <row r="57" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="H57" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -3832,11 +3931,11 @@
       <c r="U57" s="1"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
-      <c r="X57" s="2"/>
+      <c r="X57" s="6"/>
     </row>
     <row r="58" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>8</v>
@@ -3845,22 +3944,22 @@
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -3874,11 +3973,11 @@
       <c r="U58" s="1"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
-      <c r="X58" s="2"/>
+      <c r="X58" s="6"/>
     </row>
     <row r="59" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>9</v>
@@ -3887,22 +3986,22 @@
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J59" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J59" s="1" t="s">
+      <c r="K59" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -3916,11 +4015,11 @@
       <c r="U59" s="1"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
-      <c r="X59" s="2"/>
+      <c r="X59" s="6"/>
     </row>
     <row r="60" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>17</v>
@@ -3936,33 +4035,33 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
       <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
-      <c r="X60" s="2"/>
+      <c r="X60" s="6"/>
     </row>
     <row r="61" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>18</v>
@@ -3978,43 +4077,43 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="O61" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="R61" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
-      <c r="X61" s="2"/>
+      <c r="X61" s="6"/>
     </row>
     <row r="62" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="6" t="s">
-        <v>158</v>
+      <c r="G62" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -4032,14 +4131,14 @@
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
-      <c r="X62" s="2"/>
+      <c r="X62" s="6"/>
     </row>
     <row r="63" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -4047,8 +4146,8 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="6" t="s">
-        <v>158</v>
+      <c r="I63" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -4064,14 +4163,14 @@
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
-      <c r="X63" s="2"/>
+      <c r="X63" s="6"/>
     </row>
     <row r="64" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -4080,8 +4179,8 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-      <c r="J64" s="6" t="s">
-        <v>158</v>
+      <c r="J64" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -4096,14 +4195,14 @@
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
-      <c r="X64" s="2"/>
+      <c r="X64" s="6"/>
     </row>
     <row r="65" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -4113,8 +4212,8 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
-      <c r="K65" s="6" t="s">
-        <v>158</v>
+      <c r="K65" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
@@ -4128,14 +4227,14 @@
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
-      <c r="X65" s="2"/>
+      <c r="X65" s="6"/>
     </row>
     <row r="66" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -4150,8 +4249,8 @@
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
-      <c r="P66" s="6" t="s">
-        <v>158</v>
+      <c r="P66" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
@@ -4160,14 +4259,14 @@
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
       <c r="W66" s="1"/>
-      <c r="X66" s="2"/>
+      <c r="X66" s="6"/>
     </row>
     <row r="67" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -4183,8 +4282,8 @@
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
-      <c r="Q67" s="6" t="s">
-        <v>158</v>
+      <c r="Q67" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
@@ -4192,14 +4291,14 @@
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
-      <c r="X67" s="2"/>
+      <c r="X67" s="6"/>
     </row>
     <row r="68" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -4216,22 +4315,22 @@
       <c r="O68" s="1"/>
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
-      <c r="R68" s="6" t="s">
-        <v>158</v>
+      <c r="R68" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
       <c r="W68" s="1"/>
-      <c r="X68" s="2"/>
+      <c r="X68" s="6"/>
     </row>
     <row r="69" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -4249,21 +4348,21 @@
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
-      <c r="S69" s="6" t="s">
-        <v>158</v>
+      <c r="S69" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
-      <c r="X69" s="2"/>
+      <c r="X69" s="6"/>
     </row>
     <row r="70" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -4282,20 +4381,20 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
-      <c r="T70" s="6" t="s">
-        <v>158</v>
+      <c r="T70" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
-      <c r="X70" s="2"/>
+      <c r="X70" s="6"/>
     </row>
     <row r="71" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -4306,8 +4405,8 @@
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
-      <c r="L71" s="6" t="s">
-        <v>158</v>
+      <c r="L71" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
@@ -4320,14 +4419,14 @@
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
-      <c r="X71" s="2"/>
+      <c r="X71" s="6"/>
     </row>
     <row r="72" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -4339,8 +4438,8 @@
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
-      <c r="M72" s="6" t="s">
-        <v>158</v>
+      <c r="M72" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
@@ -4352,14 +4451,14 @@
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
       <c r="W72" s="1"/>
-      <c r="X72" s="2"/>
+      <c r="X72" s="6"/>
     </row>
     <row r="73" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -4372,8 +4471,8 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
-      <c r="N73" s="6" t="s">
-        <v>158</v>
+      <c r="N73" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
@@ -4384,14 +4483,14 @@
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
-      <c r="X73" s="2"/>
+      <c r="X73" s="6"/>
     </row>
     <row r="74" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -4405,8 +4504,8 @@
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
-      <c r="O74" s="6" t="s">
-        <v>158</v>
+      <c r="O74" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
@@ -4416,14 +4515,14 @@
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
-      <c r="X74" s="2"/>
+      <c r="X74" s="6"/>
     </row>
     <row r="75" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -4435,8 +4534,8 @@
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
-      <c r="M75" s="6" t="s">
-        <v>172</v>
+      <c r="M75" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
@@ -4448,14 +4547,14 @@
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
-      <c r="X75" s="2"/>
+      <c r="X75" s="6"/>
     </row>
     <row r="76" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -4466,8 +4565,8 @@
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
-      <c r="L76" s="6" t="s">
-        <v>172</v>
+      <c r="L76" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
@@ -4480,14 +4579,14 @@
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
-      <c r="X76" s="2"/>
+      <c r="X76" s="6"/>
     </row>
     <row r="77" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -4496,8 +4595,8 @@
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="6" t="s">
-        <v>172</v>
+      <c r="J77" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -4512,14 +4611,14 @@
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
       <c r="W77" s="1"/>
-      <c r="X77" s="2"/>
+      <c r="X77" s="6"/>
     </row>
     <row r="78" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -4527,8 +4626,8 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
-      <c r="I78" s="6" t="s">
-        <v>172</v>
+      <c r="I78" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -4544,14 +4643,14 @@
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
-      <c r="X78" s="2"/>
+      <c r="X78" s="6"/>
     </row>
     <row r="79" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -4564,8 +4663,8 @@
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
-      <c r="N79" s="6" t="s">
-        <v>172</v>
+      <c r="N79" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
@@ -4576,14 +4675,14 @@
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
-      <c r="X79" s="2"/>
+      <c r="X79" s="6"/>
     </row>
     <row r="80" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -4593,8 +4692,8 @@
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
-      <c r="K80" s="6" t="s">
-        <v>172</v>
+      <c r="K80" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
@@ -4608,14 +4707,14 @@
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
-      <c r="X80" s="2"/>
+      <c r="X80" s="6"/>
     </row>
     <row r="81" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -4630,10 +4729,10 @@
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
-      <c r="P81" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q81" s="6" t="s">
+      <c r="P81" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q81" s="4" t="s">
         <v>82</v>
       </c>
       <c r="R81" s="1"/>
@@ -4642,14 +4741,14 @@
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
-      <c r="X81" s="2"/>
+      <c r="X81" s="6"/>
     </row>
     <row r="82" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -4665,10 +4764,10 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
-      <c r="Q82" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="R82" s="6" t="s">
+      <c r="Q82" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="R82" s="4" t="s">
         <v>82</v>
       </c>
       <c r="S82" s="1"/>
@@ -4676,14 +4775,14 @@
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
-      <c r="X82" s="2"/>
+      <c r="X82" s="6"/>
     </row>
     <row r="83" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -4700,24 +4799,24 @@
       <c r="O83" s="1"/>
       <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
-      <c r="R83" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="S83" s="6" t="s">
+      <c r="R83" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="S83" s="4" t="s">
         <v>82</v>
       </c>
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
-      <c r="X83" s="2"/>
+      <c r="X83" s="6"/>
     </row>
     <row r="84" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -4736,22 +4835,22 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
-      <c r="T84" s="6" t="s">
+      <c r="T84" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="U84" s="6" t="s">
-        <v>158</v>
+      <c r="U84" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
-      <c r="X84" s="2"/>
+      <c r="X84" s="6"/>
     </row>
     <row r="85" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -4771,21 +4870,21 @@
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
       <c r="T85" s="1"/>
-      <c r="U85" s="6" t="s">
+      <c r="U85" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="V85" s="6" t="s">
-        <v>158</v>
+      <c r="V85" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="W85" s="1"/>
-      <c r="X85" s="2"/>
+      <c r="X85" s="6"/>
     </row>
     <row r="86" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -4800,10 +4899,10 @@
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
-      <c r="P86" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q86" s="6" t="s">
+      <c r="P86" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q86" s="4" t="s">
         <v>82</v>
       </c>
       <c r="R86" s="1"/>
@@ -4812,14 +4911,14 @@
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
-      <c r="X86" s="2"/>
+      <c r="X86" s="6"/>
     </row>
     <row r="87" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -4834,11 +4933,11 @@
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
-      <c r="P87" s="6" t="s">
+      <c r="P87" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="Q87" s="6" t="s">
-        <v>185</v>
+      <c r="Q87" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
@@ -4846,14 +4945,14 @@
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
-      <c r="X87" s="2"/>
+      <c r="X87" s="6"/>
     </row>
     <row r="88" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
@@ -4870,24 +4969,24 @@
       <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
-      <c r="R88" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="S88" s="6" t="s">
+      <c r="R88" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="S88" s="4" t="s">
         <v>82</v>
       </c>
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
-      <c r="X88" s="2"/>
+      <c r="X88" s="6"/>
     </row>
     <row r="89" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
@@ -4904,24 +5003,24 @@
       <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
-      <c r="R89" s="6" t="s">
+      <c r="R89" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="S89" s="6" t="s">
-        <v>185</v>
+      <c r="S89" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
-      <c r="X89" s="2"/>
+      <c r="X89" s="6"/>
     </row>
     <row r="90" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -4940,22 +5039,22 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
-      <c r="T90" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="U90" s="6" t="s">
+      <c r="T90" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="U90" s="4" t="s">
         <v>82</v>
       </c>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
-      <c r="X90" s="2"/>
+      <c r="X90" s="6"/>
     </row>
     <row r="91" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -4974,19 +5073,19 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
-      <c r="T91" s="6" t="s">
+      <c r="T91" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="U91" s="6" t="s">
-        <v>185</v>
+      <c r="U91" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
-      <c r="X91" s="2"/>
+      <c r="X91" s="6"/>
     </row>
     <row r="92" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>26</v>
@@ -4995,22 +5094,22 @@
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
@@ -5024,11 +5123,11 @@
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
-      <c r="X92" s="2"/>
+      <c r="X92" s="6"/>
     </row>
     <row r="93" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>23</v>
@@ -5037,22 +5136,22 @@
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
@@ -5066,11 +5165,11 @@
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
-      <c r="X93" s="2"/>
+      <c r="X93" s="6"/>
     </row>
     <row r="94" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>24</v>
@@ -5078,26 +5177,26 @@
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
-      <c r="F94" s="4" t="s">
-        <v>192</v>
+      <c r="F94" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
@@ -5110,11 +5209,11 @@
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
-      <c r="X94" s="2"/>
+      <c r="X94" s="6"/>
     </row>
     <row r="95" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>25</v>
@@ -5123,25 +5222,25 @@
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
@@ -5154,11 +5253,11 @@
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
-      <c r="X95" s="2"/>
+      <c r="X95" s="6"/>
     </row>
     <row r="96" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>55</v>
@@ -5177,10 +5276,10 @@
         <v>101</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="P96" s="1"/>
       <c r="Q96" s="1"/>
@@ -5190,11 +5289,11 @@
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
-      <c r="X96" s="2"/>
+      <c r="X96" s="6"/>
     </row>
     <row r="97" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>54</v>
@@ -5216,7 +5315,7 @@
         <v>92</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
@@ -5226,11 +5325,11 @@
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
-      <c r="X97" s="2"/>
+      <c r="X97" s="6"/>
     </row>
     <row r="98" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>46</v>
@@ -5252,7 +5351,7 @@
         <v>96</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
@@ -5262,11 +5361,11 @@
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
-      <c r="X98" s="2"/>
+      <c r="X98" s="6"/>
     </row>
     <row r="99" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>45</v>
@@ -5288,7 +5387,7 @@
         <v>88</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
@@ -5298,35 +5397,35 @@
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
-      <c r="X99" s="2"/>
+      <c r="X99" s="6"/>
     </row>
     <row r="100" spans="1:24" ht="42" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B100" s="4" t="s">
+      <c r="A100" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
-      <c r="N100" s="4"/>
-      <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
-      <c r="Q100" s="4"/>
-      <c r="R100" s="4"/>
-      <c r="S100" s="4" t="s">
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2"/>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" s="2"/>
+      <c r="Q100" s="2"/>
+      <c r="R100" s="2"/>
+      <c r="S100" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="T100" s="4" t="s">
+      <c r="T100" s="2" t="s">
         <v>88</v>
       </c>
       <c r="U100" s="5" t="s">
@@ -5334,11 +5433,11 @@
       </c>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
-      <c r="X100" s="2"/>
+      <c r="X100" s="6"/>
     </row>
     <row r="101" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>48</v>
@@ -5366,15 +5465,15 @@
         <v>101</v>
       </c>
       <c r="U101" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
-      <c r="X101" s="2"/>
+      <c r="X101" s="6"/>
     </row>
     <row r="102" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>47</v>
@@ -5399,18 +5498,18 @@
         <v>88</v>
       </c>
       <c r="T102" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="U102" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
-      <c r="X102" s="2"/>
+      <c r="X102" s="6"/>
     </row>
     <row r="103" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>50</v>
@@ -5435,18 +5534,18 @@
         <v>86</v>
       </c>
       <c r="T103" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="U103" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
-      <c r="X103" s="2"/>
+      <c r="X103" s="6"/>
     </row>
     <row r="104" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>49</v>
@@ -5474,15 +5573,15 @@
         <v>92</v>
       </c>
       <c r="U104" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
-      <c r="X104" s="2"/>
+      <c r="X104" s="6"/>
     </row>
     <row r="105" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>57</v>
@@ -5510,15 +5609,15 @@
         <v>99</v>
       </c>
       <c r="U105" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
-      <c r="X105" s="2"/>
+      <c r="X105" s="6"/>
     </row>
     <row r="106" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>56</v>
@@ -5546,27 +5645,27 @@
         <v>90</v>
       </c>
       <c r="U106" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
-      <c r="X106" s="2"/>
+      <c r="X106" s="6"/>
     </row>
     <row r="107" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
@@ -5586,14 +5685,14 @@
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
-      <c r="X107" s="2"/>
+      <c r="X107" s="6"/>
     </row>
     <row r="108" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>92</v>
@@ -5602,7 +5701,7 @@
         <v>96</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
@@ -5622,11 +5721,11 @@
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
-      <c r="X108" s="2"/>
+      <c r="X108" s="6"/>
     </row>
     <row r="109" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>42</v>
@@ -5651,18 +5750,18 @@
         <v>92</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="S109" s="1"/>
       <c r="T109" s="1"/>
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
-      <c r="X109" s="2"/>
+      <c r="X109" s="6"/>
     </row>
     <row r="110" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>41</v>
@@ -5687,18 +5786,18 @@
         <v>89</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="S110" s="1"/>
       <c r="T110" s="1"/>
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
-      <c r="X110" s="2"/>
+      <c r="X110" s="6"/>
     </row>
     <row r="111" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>44</v>
@@ -5723,18 +5822,18 @@
         <v>86</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="S111" s="1"/>
       <c r="T111" s="1"/>
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
-      <c r="X111" s="2"/>
+      <c r="X111" s="6"/>
     </row>
     <row r="112" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>43</v>
@@ -5759,18 +5858,18 @@
         <v>101</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="S112" s="1"/>
       <c r="T112" s="1"/>
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
-      <c r="X112" s="2"/>
+      <c r="X112" s="6"/>
     </row>
     <row r="113" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>52</v>
@@ -5795,18 +5894,18 @@
         <v>88</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="S113" s="1"/>
       <c r="T113" s="1"/>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
-      <c r="X113" s="2"/>
+      <c r="X113" s="6"/>
     </row>
     <row r="114" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>51</v>
@@ -5838,23 +5937,23 @@
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
-      <c r="X114" s="2"/>
+      <c r="X114" s="6"/>
     </row>
     <row r="115" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
@@ -5874,23 +5973,23 @@
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
-      <c r="X115" s="2"/>
+      <c r="X115" s="6"/>
     </row>
     <row r="116" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
@@ -5910,11 +6009,11 @@
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
-      <c r="X116" s="2"/>
+      <c r="X116" s="6"/>
     </row>
     <row r="117" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>19</v>
@@ -5926,26 +6025,26 @@
         <v>117</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="M117" s="1"/>
       <c r="N117" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="O117" s="1"/>
       <c r="P117" s="1"/>
@@ -5956,11 +6055,11 @@
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
-      <c r="X117" s="2"/>
+      <c r="X117" s="6"/>
     </row>
     <row r="118" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>20</v>
@@ -5972,26 +6071,26 @@
         <v>117</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M118" s="1"/>
       <c r="N118" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="O118" s="1"/>
       <c r="P118" s="1"/>
@@ -6002,11 +6101,11 @@
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
-      <c r="X118" s="2"/>
+      <c r="X118" s="6"/>
     </row>
     <row r="119" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>29</v>
@@ -6015,20 +6114,20 @@
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="L119" s="1"/>
       <c r="M119" s="1"/>
@@ -6042,11 +6141,11 @@
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
-      <c r="X119" s="2"/>
+      <c r="X119" s="6"/>
     </row>
     <row r="120" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>30</v>
@@ -6055,20 +6154,20 @@
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="J120" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K120" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="K120" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
@@ -6082,11 +6181,11 @@
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
-      <c r="X120" s="2"/>
+      <c r="X120" s="6"/>
     </row>
     <row r="121" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>55</v>
@@ -6105,10 +6204,10 @@
         <v>96</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="O121" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
@@ -6118,11 +6217,11 @@
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
-      <c r="X121" s="2"/>
+      <c r="X121" s="6"/>
     </row>
     <row r="122" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>54</v>
@@ -6144,7 +6243,7 @@
         <v>90</v>
       </c>
       <c r="O122" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
@@ -6154,11 +6253,11 @@
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
-      <c r="X122" s="2"/>
+      <c r="X122" s="6"/>
     </row>
     <row r="123" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>46</v>
@@ -6177,10 +6276,10 @@
         <v>101</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O123" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
@@ -6190,11 +6289,11 @@
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
-      <c r="X123" s="2"/>
+      <c r="X123" s="6"/>
     </row>
     <row r="124" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>45</v>
@@ -6213,10 +6312,10 @@
         <v>92</v>
       </c>
       <c r="N124" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
@@ -6226,39 +6325,39 @@
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
-      <c r="X124" s="2"/>
+      <c r="X124" s="6"/>
     </row>
     <row r="125" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B125" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>117</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="G125" s="1"/>
       <c r="H125" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J125" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
@@ -6272,39 +6371,39 @@
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
-      <c r="X125" s="2"/>
+      <c r="X125" s="6"/>
     </row>
     <row r="126" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B126" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>117</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G126" s="1"/>
       <c r="H126" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
@@ -6318,47 +6417,47 @@
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
-      <c r="X126" s="2"/>
+      <c r="X126" s="6"/>
     </row>
     <row r="127" spans="1:24" ht="70" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B127" s="4" t="s">
+      <c r="A127" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-      <c r="E127" s="4"/>
-      <c r="F127" s="4"/>
-      <c r="G127" s="4"/>
-      <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-      <c r="J127" s="4"/>
-      <c r="K127" s="4"/>
-      <c r="L127" s="4"/>
-      <c r="M127" s="4"/>
-      <c r="N127" s="4"/>
-      <c r="O127" s="4"/>
-      <c r="P127" s="4"/>
-      <c r="Q127" s="4"/>
-      <c r="R127" s="4"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
+      <c r="J127" s="2"/>
+      <c r="K127" s="2"/>
+      <c r="L127" s="2"/>
+      <c r="M127" s="2"/>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" s="2"/>
+      <c r="Q127" s="2"/>
+      <c r="R127" s="2"/>
       <c r="S127" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="T127" s="5" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="U127" s="5" t="s">
         <v>93</v>
       </c>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
-      <c r="X127" s="2"/>
+      <c r="X127" s="6"/>
     </row>
     <row r="128" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>48</v>
@@ -6386,15 +6485,15 @@
         <v>96</v>
       </c>
       <c r="U128" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
-      <c r="X128" s="2"/>
+      <c r="X128" s="6"/>
     </row>
     <row r="129" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>47</v>
@@ -6426,11 +6525,11 @@
       </c>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
-      <c r="X129" s="2"/>
+      <c r="X129" s="6"/>
     </row>
     <row r="130" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>50</v>
@@ -6458,15 +6557,15 @@
         <v>82</v>
       </c>
       <c r="U130" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
-      <c r="X130" s="2"/>
+      <c r="X130" s="6"/>
     </row>
     <row r="131" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
@@ -6491,18 +6590,18 @@
         <v>82</v>
       </c>
       <c r="T131" s="1" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="U131" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
-      <c r="X131" s="2"/>
+      <c r="X131" s="6"/>
     </row>
     <row r="132" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>57</v>
@@ -6530,15 +6629,15 @@
         <v>90</v>
       </c>
       <c r="U132" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
-      <c r="X132" s="2"/>
+      <c r="X132" s="6"/>
     </row>
     <row r="133" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>56</v>
@@ -6563,30 +6662,30 @@
         <v>99</v>
       </c>
       <c r="T133" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="U133" s="1" t="s">
         <v>114</v>
       </c>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
-      <c r="X133" s="2"/>
+      <c r="X133" s="6"/>
     </row>
     <row r="134" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
@@ -6606,23 +6705,23 @@
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
-      <c r="X134" s="2"/>
+      <c r="X134" s="6"/>
     </row>
     <row r="135" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>99</v>
+        <v>253</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>201</v>
+        <v>254</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
@@ -6642,11 +6741,11 @@
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
-      <c r="X135" s="2"/>
+      <c r="X135" s="6"/>
     </row>
     <row r="136" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>42</v>
@@ -6668,21 +6767,21 @@
         <v>96</v>
       </c>
       <c r="Q136" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="R136" s="1" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="S136" s="1"/>
       <c r="T136" s="1"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
-      <c r="X136" s="2"/>
+      <c r="X136" s="6"/>
     </row>
     <row r="137" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>41</v>
@@ -6707,18 +6806,18 @@
         <v>116</v>
       </c>
       <c r="R137" s="3" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="S137" s="1"/>
       <c r="T137" s="1"/>
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
-      <c r="X137" s="2"/>
+      <c r="X137" s="6"/>
     </row>
     <row r="138" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>44</v>
@@ -6743,18 +6842,18 @@
         <v>82</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="S138" s="1"/>
       <c r="T138" s="1"/>
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
-      <c r="X138" s="2"/>
+      <c r="X138" s="6"/>
     </row>
     <row r="139" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>43</v>
@@ -6776,21 +6875,21 @@
         <v>82</v>
       </c>
       <c r="Q139" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
-      <c r="X139" s="2"/>
+      <c r="X139" s="6"/>
     </row>
     <row r="140" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>52</v>
@@ -6815,18 +6914,18 @@
         <v>99</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="S140" s="1"/>
       <c r="T140" s="1"/>
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
-      <c r="X140" s="2"/>
+      <c r="X140" s="6"/>
     </row>
     <row r="141" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>51</v>
@@ -6848,7 +6947,7 @@
         <v>99</v>
       </c>
       <c r="Q141" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="R141" s="1" t="s">
         <v>114</v>
@@ -6858,11 +6957,11 @@
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
-      <c r="X141" s="2"/>
+      <c r="X141" s="6"/>
     </row>
     <row r="142" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>1</v>
@@ -6880,13 +6979,13 @@
         <v>82</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
@@ -6896,11 +6995,11 @@
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
-      <c r="X142" s="2"/>
+      <c r="X142" s="6"/>
     </row>
     <row r="143" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>2</v>
@@ -6918,13 +7017,13 @@
         <v>92</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
@@ -6934,11 +7033,11 @@
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
-      <c r="X143" s="2"/>
+      <c r="X143" s="6"/>
     </row>
     <row r="144" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>3</v>
@@ -6953,16 +7052,16 @@
       <c r="J144" s="1"/>
       <c r="K144" s="1"/>
       <c r="L144" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="M144" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="N144" s="1" t="s">
-        <v>139</v>
+        <v>104</v>
+      </c>
+      <c r="M144" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="N144" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="P144" s="1"/>
       <c r="Q144" s="1"/>
@@ -6972,11 +7071,11 @@
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
-      <c r="X144" s="2"/>
+      <c r="X144" s="6"/>
     </row>
     <row r="145" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>14</v>
@@ -6985,26 +7084,26 @@
         <v>117</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>119</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1" t="s">
         <v>118</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
@@ -7018,11 +7117,11 @@
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
-      <c r="X145" s="2"/>
+      <c r="X145" s="6"/>
     </row>
     <row r="146" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>21</v>
@@ -7031,23 +7130,23 @@
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G146" s="1"/>
       <c r="H146" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
@@ -7060,11 +7159,11 @@
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
-      <c r="X146" s="2"/>
+      <c r="X146" s="6"/>
     </row>
     <row r="147" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>22</v>
@@ -7073,23 +7172,23 @@
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="G147" s="1"/>
       <c r="H147" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I147" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I147" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="J147" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M147" s="1"/>
       <c r="N147" s="1"/>
@@ -7102,40 +7201,42 @@
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
-      <c r="X147" s="2"/>
+      <c r="X147" s="6"/>
     </row>
     <row r="148" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="G148" s="1"/>
-      <c r="H148" s="1" t="s">
+      <c r="H148" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I148" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="I148" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J148" s="1"/>
+      <c r="J148" s="7" t="s">
+        <v>128</v>
+      </c>
       <c r="K148" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="M148" s="1"/>
       <c r="N148" s="1"/>
@@ -7148,41 +7249,43 @@
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
-      <c r="X148" s="2"/>
+      <c r="X148" s="6"/>
     </row>
     <row r="149" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>126</v>
+        <v>269</v>
+      </c>
+      <c r="F149" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J149" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L149" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="K149" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="L149" s="1"/>
       <c r="M149" s="1"/>
       <c r="N149" s="1"/>
       <c r="O149" s="1"/>
@@ -7194,11 +7297,11 @@
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
-      <c r="X149" s="2"/>
+      <c r="X149" s="6"/>
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>29</v>
@@ -7212,7 +7315,7 @@
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
       <c r="K150" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L150" s="1"/>
       <c r="M150" s="1"/>
@@ -7226,11 +7329,11 @@
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
-      <c r="X150" s="2"/>
+      <c r="X150" s="6"/>
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>30</v>
@@ -7244,7 +7347,7 @@
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
       <c r="K151" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
@@ -7258,11 +7361,11 @@
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
-      <c r="X151" s="2"/>
+      <c r="X151" s="6"/>
     </row>
     <row r="152" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>55</v>
@@ -7284,7 +7387,7 @@
         <v>88</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="P152" s="1"/>
       <c r="Q152" s="1"/>
@@ -7294,11 +7397,11 @@
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
-      <c r="X152" s="2"/>
+      <c r="X152" s="6"/>
     </row>
     <row r="153" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>54</v>
@@ -7320,7 +7423,7 @@
         <v>82</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
@@ -7329,11 +7432,11 @@
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
-      <c r="X153" s="2"/>
+      <c r="X153" s="6"/>
     </row>
     <row r="154" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>46</v>
@@ -7352,10 +7455,10 @@
         <v>92</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O154" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="P154" s="1"/>
       <c r="Q154" s="1"/>
@@ -7365,11 +7468,11 @@
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
-      <c r="X154" s="2"/>
+      <c r="X154" s="6"/>
     </row>
     <row r="155" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>45</v>
@@ -7391,7 +7494,7 @@
         <v>89</v>
       </c>
       <c r="O155" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="P155" s="1"/>
       <c r="Q155" s="1"/>
@@ -7401,40 +7504,40 @@
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
-      <c r="X155" s="2"/>
+      <c r="X155" s="6"/>
     </row>
     <row r="156" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
       <c r="H156" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M156" s="1"/>
       <c r="N156" s="1"/>
@@ -7447,40 +7550,40 @@
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
-      <c r="X156" s="2"/>
+      <c r="X156" s="6"/>
     </row>
     <row r="157" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
       <c r="H157" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
@@ -7493,33 +7596,33 @@
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
-      <c r="X157" s="2"/>
+      <c r="X157" s="6"/>
     </row>
     <row r="158" spans="1:24" ht="70" x14ac:dyDescent="0.25">
-      <c r="A158" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B158" s="4" t="s">
+      <c r="A158" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C158" s="4"/>
-      <c r="D158" s="4"/>
-      <c r="E158" s="4"/>
-      <c r="F158" s="4"/>
-      <c r="G158" s="4"/>
-      <c r="H158" s="4"/>
-      <c r="I158" s="4"/>
-      <c r="J158" s="4"/>
-      <c r="K158" s="4"/>
-      <c r="L158" s="4"/>
-      <c r="M158" s="4"/>
-      <c r="N158" s="4"/>
-      <c r="O158" s="4"/>
-      <c r="P158" s="4"/>
-      <c r="Q158" s="4"/>
-      <c r="R158" s="4"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2"/>
+      <c r="H158" s="2"/>
+      <c r="I158" s="2"/>
+      <c r="J158" s="2"/>
+      <c r="K158" s="2"/>
+      <c r="L158" s="2"/>
+      <c r="M158" s="2"/>
+      <c r="N158" s="2"/>
+      <c r="O158" s="2"/>
+      <c r="P158" s="2"/>
+      <c r="Q158" s="2"/>
+      <c r="R158" s="2"/>
       <c r="S158" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T158" s="5" t="s">
         <v>101</v>
@@ -7529,11 +7632,11 @@
       </c>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
-      <c r="X158" s="2"/>
+      <c r="X158" s="6"/>
     </row>
     <row r="159" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>48</v>
@@ -7558,18 +7661,18 @@
         <v>99</v>
       </c>
       <c r="T159" s="1" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="U159" s="1" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
-      <c r="X159" s="2"/>
+      <c r="X159" s="6"/>
     </row>
     <row r="160" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>47</v>
@@ -7594,18 +7697,18 @@
         <v>101</v>
       </c>
       <c r="T160" s="1" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="U160" s="1" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
-      <c r="X160" s="2"/>
+      <c r="X160" s="6"/>
     </row>
     <row r="161" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>50</v>
@@ -7633,15 +7736,15 @@
         <v>92</v>
       </c>
       <c r="U161" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
-      <c r="X161" s="2"/>
+      <c r="X161" s="6"/>
     </row>
     <row r="162" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>49</v>
@@ -7666,18 +7769,18 @@
         <v>90</v>
       </c>
       <c r="T162" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="U162" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
-      <c r="X162" s="2"/>
+      <c r="X162" s="6"/>
     </row>
     <row r="163" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>57</v>
@@ -7705,15 +7808,15 @@
         <v>82</v>
       </c>
       <c r="U163" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
-      <c r="X163" s="2"/>
+      <c r="X163" s="6"/>
     </row>
     <row r="164" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>56</v>
@@ -7741,27 +7844,27 @@
         <v>83</v>
       </c>
       <c r="U164" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
-      <c r="X164" s="2"/>
+      <c r="X164" s="6"/>
     </row>
     <row r="165" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
@@ -7781,23 +7884,23 @@
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
-      <c r="X165" s="2"/>
+      <c r="X165" s="6"/>
     </row>
     <row r="166" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
@@ -7817,11 +7920,11 @@
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
-      <c r="X166" s="2"/>
+      <c r="X166" s="6"/>
     </row>
     <row r="167" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>42</v>
@@ -7843,21 +7946,21 @@
         <v>99</v>
       </c>
       <c r="Q167" s="1" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="R167" s="1" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="S167" s="1"/>
       <c r="T167" s="1"/>
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
-      <c r="X167" s="2"/>
+      <c r="X167" s="6"/>
     </row>
     <row r="168" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>41</v>
@@ -7882,18 +7985,18 @@
         <v>82</v>
       </c>
       <c r="R168" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S168" s="1"/>
       <c r="T168" s="1"/>
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
-      <c r="X168" s="2"/>
+      <c r="X168" s="6"/>
     </row>
     <row r="169" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>44</v>
@@ -7915,21 +8018,21 @@
         <v>90</v>
       </c>
       <c r="Q169" s="1" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="R169" s="1" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="S169" s="1"/>
       <c r="T169" s="1"/>
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
-      <c r="X169" s="2"/>
+      <c r="X169" s="6"/>
     </row>
     <row r="170" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>43</v>
@@ -7954,18 +8057,18 @@
         <v>86</v>
       </c>
       <c r="R170" s="3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="S170" s="1"/>
       <c r="T170" s="1"/>
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
-      <c r="X170" s="2"/>
+      <c r="X170" s="6"/>
     </row>
     <row r="171" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>52</v>
@@ -7987,21 +8090,21 @@
         <v>82</v>
       </c>
       <c r="Q171" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="R171" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="S171" s="1"/>
       <c r="T171" s="1"/>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
-      <c r="X171" s="2"/>
+      <c r="X171" s="6"/>
     </row>
     <row r="172" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>51</v>
@@ -8020,24 +8123,24 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
       <c r="P172" s="1" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="R172" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="S172" s="1"/>
       <c r="T172" s="1"/>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
-      <c r="X172" s="2"/>
+      <c r="X172" s="6"/>
     </row>
     <row r="173" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>1</v>
@@ -8066,14 +8169,14 @@
         <v>96</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="M173" s="1"/>
       <c r="N173" s="1" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="O173" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="P173" s="1"/>
       <c r="Q173" s="1"/>
@@ -8083,20 +8186,20 @@
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
-      <c r="X173" s="2"/>
+      <c r="X173" s="6"/>
     </row>
     <row r="174" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>96</v>
@@ -8116,14 +8219,14 @@
         <v>90</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="M174" s="1"/>
       <c r="N174" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="O174" s="1" t="s">
-        <v>138</v>
+        <v>262</v>
+      </c>
+      <c r="O174" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="P174" s="1"/>
       <c r="Q174" s="1"/>
@@ -8133,23 +8236,23 @@
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
-      <c r="X174" s="2"/>
+      <c r="X174" s="6"/>
     </row>
     <row r="175" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
@@ -8165,14 +8268,16 @@
       <c r="K175" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="L175" s="1" t="s">
-        <v>255</v>
+      <c r="L175" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="M175" s="1"/>
       <c r="N175" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="O175" s="1"/>
+        <v>289</v>
+      </c>
+      <c r="O175" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="P175" s="1"/>
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
@@ -8181,11 +8286,11 @@
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
-      <c r="X175" s="2"/>
+      <c r="X175" s="6"/>
     </row>
     <row r="176" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>15</v>
@@ -8196,13 +8301,13 @@
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
       <c r="H176" s="1" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
@@ -8217,11 +8322,11 @@
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
-      <c r="X176" s="2"/>
+      <c r="X176" s="6"/>
     </row>
     <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>16</v>
@@ -8232,13 +8337,13 @@
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
       <c r="H177" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
@@ -8253,11 +8358,11 @@
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
-      <c r="X177" s="2"/>
+      <c r="X177" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W177" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
